--- a/Lorinna_Master_Veri.xlsx
+++ b/Lorinna_Master_Veri.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F307"/>
+  <dimension ref="A1:D307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,20 +441,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Ansiklopedide_Bulunan_Ad</t>
+          <t>Notalar_KULLANMAK</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Benzerlik_Yuzdesi</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Notalar_KULLANMAK</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Parfum_Tanimi</t>
         </is>
@@ -473,22 +463,10 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Black Oudh Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>86</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>['odunsu', 'pudramsı', 'misk', 'kehribar', 'paçuli', 'vanilya', 'yeşil', 'sıcak baharatlı', 'balzamik', 'hayvansal']</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Black OudhbyAl Haramain Perfumesis, kadınlar ve erkekler için Amber-Woody bir kokudur. Üst notalarda Misk; orta notalarda Sedir ve Bitkisel Notalar; alt notalarda Amber, Paçuli ve Vanilya bulunur.</t>
-        </is>
-      </c>
+          <t>['gül', 'turunçgil', 'misk', 'pudramsı', 'çiçeksi', 'kehribar', 'paçuli', 'menekşe', 'odunsu', 'aromatik']</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -503,20 +481,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Naseej Al Kiswah Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>86</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>['odunsu', 'kehribar', 'deri', 'ud', 'paçuli', 'hayvansal', 'vanilya', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Naseej Al KiswahbyAfnani, Kadınlar ve Erkekler için Amber Woody Kokusudur. orta notalarda Woodsy Notes ve Sedir; temel notalar Amber, Deri ve Agarwood'dur (Ud).</t>
+          <t>['taze baharatlı', 'aromatik', 'odunsu', 'sıcak baharatlı', 'kehribar', 'balzamik', 'hafif baharatlı', 'dumanlı', 'misk', 'topraksı']</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Honour Manby Amouage, erkekler için odunsu ve baharatlı bir kokudur. Honour Man, 2011 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki burun Nathalie Feisthauer'dır. Üst notalarda pembe biber ve biber; orta notalarda sardunya, elemi ve hindistan cevizi; alt notalarda tütsü, vetiver, Virginia sediri, misk, tonka fasulyesi ve paçuli bulunur.</t>
         </is>
       </c>
     </row>
@@ -533,20 +503,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Club de Nuit Intense Man Armaffor men</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>86</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'meyvemsi', 'deri', 'dumanlı', 'odunsu', 'aromatik', 'tatlı', 'taze', 'misk']</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Club de Nuit Intense ManbyArmafis erkekler için odunsu baharatlı bir koku. Club de Nuit Intense Man 2015 yılında piyasaya sürüldü. Üst notalarda Limon, Ananas, Bergamot, Siyah Frenk Üzümü ve Elma; orta notalarda Huş Ağacı, Yasemin ve Gül; alt notalarda Misk, Ambergris, Paçuli ve Vanilya bulunmaktadır.</t>
+          <t>['kehribar', 'balzamik', 'taze baharatlı', 'dumanlı', 'sıcak baharatlı', 'odunsu']</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Interlude Manby Amouage, erkekler için Amber Woody bir kokudur. Interlude Man, 2012 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Pierre Negrin. Üst notalarda Kekik, Biber ve Bergamot; orta notalarda Tütsü, Opoponax, Amber ve Laden; alt notalarda Agarwood (Ud), Deri, Sandal Ağacı ve Paçuli bulunur.</t>
         </is>
       </c>
     </row>
@@ -563,20 +525,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thohfa Attar Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>86</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>['odunsu', 'kehribar', 'çiçeksi', 'pudramsı', 'sıcak baharatlı', 'ud', 'misk', 'vanilya', 'metalik']</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Thohfa AttarbyAl Haramain Perfumesis kadınlar ve erkekler için bir Amber kokusu.</t>
+          <t>['meyvemsi', 'çiçeksi', 'tatlı', 'tütün', 'beyaz çiçeksi', 'pudramsı', 'misk', 'kehribar', 'sümbülteber', 'laktonik']</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Queen of Shebaby Attar Koleksiyonu, kadınlar için bir Amber kokusudur. Queen of Sheba 2015 yılında piyasaya sürülmüştür. Üst notalarda Şeftali, Osmanthus, Tütün Yaprağı ve Tütsü; orta notalarda Sümbülteber, Yasemin, Turunçgiller ve Kırmızı Gül; temel notalarda Beyaz Misk ve Amber bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -593,20 +547,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Venetian Girl From Venice With Love Armaffor women</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>86</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>['çiçeksi', 'taze', 'gül', 'meyvemsi', 'turunçgil', 'aromatik', 'beyaz çiçeksi', 'misk', 'yeşil', 'odunsu']</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Venetian Girl From Venice With LovebyArmafis kadınlara yönelik bir parfüm. Bu yeni bir parfüm. Venice With Love'dan Venetian Girl, 2023 yılında piyasaya sürüldü. Üst notalarda Bergamot, Litchi ve Armut; orta notalarda Çiçeksi Notalar, Şakayık, Gül ve Vadi Zambağı; alt notalarda Vetiver ve Misk bulunmaktadır.</t>
+          <t>['beyaz çiçeksi', 'çiçeksi', 'sarı çiçeksi', 'sümbülteber', 'meyvemsi', 'kehribar', 'odunsu', 'yeşil', 'hayvansal']</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>By Kilian'ın Good Girl Gone Bad Anniversary Edition'ı, kadınlar için çiçeksi bir koku. Bu yeni bir koku. Good Girl Gone Bad Anniversary Edition, 2022'de piyasaya sürüldü. Bu kokunun arkasındaki isim Alberto Morillas. Üst notalarda Osmanthus, Portakal Çiçeği ve Mayıs Gülü; orta notalarda Nergis, Yasemin ve Hint Zambak; alt notalarda ise Kehribar ve Sedir bulunuyor.</t>
         </is>
       </c>
     </row>
@@ -623,20 +569,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>For You by One Direction Avonfor women</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>86</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>['tatlı', 'meyveli', 'çiçeksi', 'odunsu', 'taze', 'ekşi', 'çikolatalı', 'pudramsı', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>One Direction by Avoni'nin For You'su kadınlar için çiçeksi meyveli bir gurme kokusudur. One Direction by Avoni'nin For You'su 2014 yılında piyasaya sürülmüştür. Üst notasında Kırmızı Meyveler; orta notasında Çiçeksi Notalar; alt notalarında Beyaz Çikolata ve Sandal Ağacı bulunmaktadır.</t>
+          <t>['aromatik', 'turunçgil', 'odunsu', 'çiçeksi', 'taze baharatlı', 'pudramsı', 'beyaz çiçeksi', 'meyvemsi', 'tatlı', 'topraksı']</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bal d'AfriquebyByredo, kadınlar ve erkekler için Amber Woody bir kokudur. Bal d'Afrique, 2009 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki burun Jérôme Epinette'dir. Üst notalarda Amalfi Limonu, Tagetes, Siyah Frenk Üzümü, Bergamot ve Afrika Portakal Çiçeği; orta notalarda Menekşe, Siklamen ve Yasemin; alt notalarda Vetiver, Misk, Amber ve Virginia Sediri bulunur.</t>
         </is>
       </c>
     </row>
@@ -653,22 +591,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cologne 1888 Miller Harrisfor women and men</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>86</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>['aromatik', 'taze baharatlı', 'turunçgil', 'bitkisel', 'kehribar', 'odunsu', 'taze']</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Miller Harris'in Cologne 1888 parfümü, kadınlar ve erkekler için narenciye aromalı bir kokudur. Cologne 1888, 2008 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Lyn Harris'tir.</t>
-        </is>
-      </c>
+          <t>['sıcak baharatlı', 'odunsu', 'kehribar', 'çiçeksi', 'aromatik', 'sarı çiçeksi', 'taze baharatlı', 'deri', 'pudramsı', 'gül']</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -683,18 +609,10 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Creed Pour Enfants Creedfor women and men</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>86</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
           <t>['meyvemsi', 'turunçgil', 'taze', 'gül', 'yeşil', 'taze baharatlı', 'tatlı', 'aromatik']</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Creed Pour Enfantsby Creed, kadınlar ve erkekler için çiçeksi ve meyveli bir kokudur. Creed Pour Enfants, 2015 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Julien Rasquinet'tir. Üst notalarda Greyfurt ve Limon; orta notalarda Elma ve Gül; alt notalarda Erik bulunur.</t>
         </is>
@@ -713,18 +631,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>J'ose Eisenbergfor women</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>86</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>['aromatik', 'lavanta', 'sıcak baharatlı', 'kahve', 'odunsu', 'kehribar', 'taze baharatlı', 'pudramsı', 'bitkisel', 'vanilya']</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>Bilgi Yok</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bilgi Yok</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -739,20 +653,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Soft Musk Delice Fleur de Chocolate Avonfor women</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>86</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>['çikolata', 'vanilya', 'tatlı', 'sıcak baharatlı', 'kakao', 'turunçgil', 'çiçeksi', 'pudramsı']</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Avoni Soft Musk Delice Fleur de Chocolate, kadınlar için Amber Vanilya kokusudur. Soft Musk Delice Fleur de Chocolate, 2019 yılında piyasaya sürülmüştür. Üst notasında Mandalina; orta notalarında Çikolata ve Çikolata Çiçeği; alt notasında Vanilya bulunmaktadır.</t>
+          <t>['beyaz çiçeksi', 'çiçeksi', 'taze', 'meyveli', 'turunçgil', 'misk', 'tropikal', 'pudramsı', 'gül', 'odunsu']</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ex Nihilo'dan Fleur Narcotique, kadınlar ve erkekler için çiçeksi ve meyveli bir kokudur. Fleur Narcotique, 2014 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Quentin Bisch'tir. Üst notalarda Litchi, Bergamot ve Şeftali; orta notalarda Şakayık, Portakal Çiçeği, Yasemin ve Petalia; alt notalarda Misk, Yosun ve Odunsu Notalar bulunur.</t>
         </is>
       </c>
     </row>
@@ -769,18 +675,10 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bamboo America Franck Olivierfor men</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>86</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>['odunsu', 'pudramsı', 'turunçgil', 'süsen', 'ozonik', 'sucul', 'taze baharatlı', 'yeşil', 'çiçeksi', 'meyvemsi']</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>['kehribar', 'odunsu', 'turunçgil', 'paçuli', 'vanilya', 'pudramsı', 'topraksı', 'balzamik', 'sıcak baharatlı', 'aromatik']</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -795,20 +693,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portfolio Portrait Sandal Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>86</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>['odunsu', 'sıcak baharatlı', 'taze baharatlı', 'topraksı', 'kehribar', 'tarçın', 'gül', 'hayvansal', 'deri', 'balzamik']</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Portfolio Portrait SandalbyAl Haramain Perfumesis, kadınlar ve erkekler için bir Deri kokusudur. Portfolio Portrait Sandal, 2019 yılında piyasaya sürüldü. Üst notalarda Karabiber ve Portakal Çiçeği; orta notalarda Kıbrıs Yağı veya Nagarmotha, Gül, Tarçın, Deri ve Ylang-Ylang; temel notalarda Ambergris, Sandal Ağacı, Vanilya ve Tonka Fasulyesi bulunur.</t>
+          <t>['sıcak baharatlı', 'kehribar', 'gül', 'odunsu', 'paçuli', 'balzamik', 'meyvemsi', 'dumanlı', 'çiçeksi', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Portrait of a Lady by Frederic Malle, kadınlar için Amber Floral bir parfümdür. Portrait of a Lady, 2010 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Dominique Ropion'dur. Üst notalarda Gül, Karanfil, Ahududu, Siyah Frenk Üzümü ve Tarçın; orta notalarda Paçuli, Tütsü ve Sandal Ağacı; alt notalarda Misk, Benzoin ve Amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -825,20 +715,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Soie Rouge Avonfor women</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>86</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>['odunsu', 'gül', 'taze baharatlı', 'paçuli', 'misk', 'sıcak baharatlı', 'beyaz çiçeksi', 'topraksı', 'kehribar', 'sarı çiçeksi']</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Soie RougebyAvon, kadınlar için bir Chypre Floral parfümüdür. Soie Rouge, 1993 yılında piyasaya sürülmüştür. Parfümün arkasındaki isim Jean-Pierre Subrenat'tır. Üst notalarda Biber, Kaşmir Ağacı ve Portakal; orta notalarda Gül, Ylang-Ylang, Vadi Zambağı ve Yasemin; alt notalarda Paçuli, Vetiver, Misk ve Amber bulunur.</t>
+          <t>['odunsu', 'kehribar', 'sıcak baharatlı', 'taze baharatlı', 'aromatik', 'metalik', 'beyaz çiçeksi', 'hayvansal']</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Baccarat Rouge 540 by Maison Francis Kurkdjian, kadınlar ve erkekler için Amber Floral bir kokudur. Baccarat Rouge 540, 2015 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Francis Kurkdjian'dır. Üst notalarda Safran ve Yasemin; orta notalarda Amber Ağacı ve Ambergris; alt notalarda Köknar Reçinesi ve Sedir bulunur.</t>
         </is>
       </c>
     </row>
@@ -855,20 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Absolute by Exclusive Avonfor men</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>86</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>['ud', 'kehribar', 'odunsu', 'sıcak baharatlı', 'taze baharatlı', 'aromatik', 'dumanlı', 'paçuli', 'balzamik', 'turunçgil']</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ExclusivebyAvon'dan Absolute, erkekler için odunsu aromatik bir kokudur. Absolute by Exclusive, 2020 yılında piyasaya sürüldü. Absolute by Exclusive, Marion Costero ve Stephen Nilsen tarafından yaratıldı. Üst notalarda Sicilya Limonu, Lavanta ve Afrika Sardunyası; orta notalarda Agar Ağacı (Ud), Teksas Sediri, Tütsü ve Safralein; alt notalarda Kehribar, Endonezya Paçuli Yaprağı ve Ambrein bulunur.</t>
+          <t>Bilgi Yok</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bilgi Yok</t>
         </is>
       </c>
     </row>
@@ -885,20 +759,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Leather Oudh Al Haramain Perfumesfor women</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>86</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>['odunsu', 'meyveli', 'deri', 'tatlı', 'kehribar', 'hayvansal', 'dumanlı', 'misk', 'aromatik', 'balzamik']</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Leather OudhbyAl Haramain Perfumesis kadınlara yönelik bir parfümdür. Leather Oudh 2016 yılında piyasaya sürülmüştür. Üst notalarda Ahududu ve Kekik; orta notalarda Odunsu Notalar, Tütsü, Kaşmir Ağacı ve Yasemin; alt notalarda Deri, Sedir, Amber ve Misk bulunmaktadır.</t>
+          <t>['aromatik', 'taze baharatlı', 'deri', 'odunsu', 'hayvansal', 'kehribar']</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Irish LeatherbyMemo Paris, kadınlar ve erkekler için bir deri kokusudur. Irish Leather, 2013 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Alienor Massenet'tir.</t>
         </is>
       </c>
     </row>
@@ -915,20 +781,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Red African Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>86</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>['taze baharatlı', 'karamel', 'tatlı', 'kehribar', 'balzamik', 'vanilya', 'pudramsı', 'hayvansal', 'odunsu']</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Al Haramain Perfumesi'nin Red African'ı kadınlar ve erkekler için Amber Woody bir kokudur. Red African 2017 yılında piyasaya sürülmüştür. Üst notalarda Brezilya Gül Ağacı; orta notalarda Hindistan Cevizi ve Karamel; alt notalarda Ambergris, Vanilya ve Misk bulunmaktadır.</t>
+          <t>['sıcak baharatlı', 'aromatik', 'taze baharatlı', 'deri', 'odunsu', 'hayvansal', 'topraksı', 'paçuli', 'ud']</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Memo Paris'in African Leather'ı kadın ve erkeklere yönelik bir deri kokusudur. African Leather 2015 yılında piyasaya sürülmüştür.</t>
         </is>
       </c>
     </row>
@@ -945,20 +803,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>9pm Afnanfor men</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>86</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>['vanilya', 'kehribar', 'sıcak baharatlı', 'tarçın', 'tatlı', 'meyvemsi', 'pudramsı', 'lavanta', 'aromatik', 'taze']</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>9pmbyAfnani erkekler için Amber Vanilya kokusu. 9pm, 2020 yılında piyasaya sürüldü. Üst notalarda Elma, Tarçın, Yabani Lavanta ve Bergamot; orta notalarda Portakal Çiçeği ve Vadi Zambağı; alt notalarda Vanilya, Tonka Fasulyesi, Amber ve Paçuli bulunuyor.</t>
+          <t>Bilgi Yok</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bilgi Yok</t>
         </is>
       </c>
     </row>
@@ -975,20 +825,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Senses Sparkling Grapefruit &amp; Orange Blossom Avonfor women</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>86</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>['beyaz çiçeksi', 'turunçgil', 'meyveli', 'tatlı']</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Senses Sparkling Greyfurt ve Portakal ÇiçeğiAvon, kadınlar için narenciye aromalı bir kokudur. Senses Sparkling Greyfurt ve Portakal Çiçeği, 2020 yılında piyasaya sürülmüştür.</t>
+          <t>['turunçgil', 'beyaz çiçeksi', 'misk', 'pudramsı', 'taze']</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Yessamin OrangebyAvon, kadınlara yönelik çiçeksi bir kokudur. Yessamin Orange, 2001 yılında piyasaya sürülmüştür.</t>
         </is>
       </c>
     </row>
@@ -1005,20 +847,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Musk Al Ghazal Eau de Parfum Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>86</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>['misk', 'sıcak baharatlı', 'taze baharatlı', 'tatlı', 'anason', 'pudramsı', 'çikolata', 'hafif baharatlı', 'aromatik', 'vanilya']</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Musk Al Ghazal Eau de ParfumbyAl Haramain Perfumesis, kadınlar ve erkekler için bir Amber kokusudur. Üst notalarda kimyon ve anason; orta notalarda misk; alt notalarda baharatlar, bitter çikolata, odunsu notalar ve vanilya bulunur.</t>
+          <t>['gül', 'misk', 'kehribar', 'pudramsı', 'çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Intense Roses MuskbyMontale, kadınlar için çiçeksi bir kokudur. Intense Roses Musk, 2015 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki burun Pierre Montale'dir.</t>
         </is>
       </c>
     </row>
@@ -1035,20 +869,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>L'Aventure Intense Al Haramain Perfumesfor men</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>86</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'odunsu', 'aromatik', 'taze baharatlı', 'misk']</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Al Haramain Perfumesi tarafından üretilen L'Aventure Intense, erkekler için Chypre Floral bir kokudur. L'Aventure Intense, 2019 yılında piyasaya sürülmüştür. Üst notalarda Bergamot, Limon ve Elemi; orta notalarda Odunsu Notalar, Yasemin ve Vadi Zambağı; alt notalarda Misk, Amber ve Paçuli bulunmaktadır.</t>
+          <t>['gül', 'vanilya', 'kahve', 'çiçeksi', 'pudramsı', 'misk', 'sıcak baharatlı', 'kehribar', 'tatlı']</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Intense CafebyMontale, kadınlar ve erkekler için Amber Vanilya aromalı bir parfümdür. Intense Cafe, 2013 yılında piyasaya sürülmüştür. Parfümün arkasındaki isim Pierre Montale'dir. Üst notalarda Çiçeksi Notalar; orta notalarda Gül ve Kahve; alt notalarda Vanilya, Beyaz Misk ve Amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -1065,22 +891,10 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Black Oudh Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>86</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>['odunsu', 'pudramsı', 'misk', 'kehribar', 'paçuli', 'vanilya', 'yeşil', 'sıcak baharatlı', 'balzamik', 'hayvansal']</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Black OudhbyAl Haramain Perfumesis, kadınlar ve erkekler için Amber-Woody bir kokudur. Üst notalarda Misk; orta notalarda Sedir ve Bitkisel Notalar; alt notalarda Amber, Paçuli ve Vanilya bulunur.</t>
-        </is>
-      </c>
+          <t>['kehribar', 'dumanlı', 'ud', 'odunsu', 'esrar', 'balzamik', 'yeşil', 'aromatik', 'tütün', 'sıcak baharatlı']</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1095,20 +909,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scent Essence - Blooming Lotus Avonfor women</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>86</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>['çiçeksi', 'misk', 'su', 'ozonik', 'pudramsı']</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Scent Essence - Blooming Lotus by Avoni, kadınlara yönelik çiçeksi bir kokudur. Scent Essence - Blooming Lotus, 2015 yılında piyasaya sürülmüştür. Üst notasında Frezya; orta notasında Lotus; alt notasında Misk bulunmaktadır.</t>
+          <t>['meyvemsi', 'tatlı', 'misk', 'pudramsı', 'taze', 'tropikal', 'odunsu']</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>KirkebyTiziana Terenzi, kadınlar ve erkekler için Chypre Fruity kokusudur. Kirkeby, 2015 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Paolo Terenzi'dir. Üst notalarda Çarkıfelek Meyvesi, Şeftali, Armut, Ahududu, Frenk Üzümü ve Kum; orta notalarda Vadi Zambağı; alt notalarda Misk, Sandal Ağacı, Vanilya, Paçuli ve Kediotu bulunur.</t>
         </is>
       </c>
     </row>
@@ -1125,20 +931,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Afrodite Tiziana Terenzifor women and men</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>86</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>['çiçeksi', 'taze', 'tatlı', 'meyvemsi', 'misk', 'beyaz çiçeksi', 'hafif baharatlı', 'pudramsı', 'odunsu', 'yeşil']</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Afrodite by Tiziana Terenzi, kadınlar ve erkekler için Amber Floral bir kokudur. Afrodite, 2018 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Paolo Terenzi. Üst notalarda Leylak, Beyaz Frenk Üzümü, Beyaz Şeftali, Pembe Biber ve Vanilya Özü; orta notalarda Vadi Zambağı, Portakal Çiçeği, Sardunya, Sümbülteber ve Süsen; alt notalarda Beyaz Misk, Ambergris, Abanoz, Paçuli ve Sandal Ağacı bulunur.</t>
+          <t>['odunsu', 'tatlı', 'vanilya', 'beyaz çiçeksi', 'meyveli', 'kehribar', 'çiçeksi', 'pudramsı', 'sarı çiçeksi', 'yeşil']</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AndromedabyTiziana Terenzi, kadınlar ve erkekler için Amber Floral bir kokudur. Andromeda, 2015 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Paolo Terenzi'dir. Üst notalarda Ylang-Ylang, Su Yasemini, Bergamot ve Çimen; orta notalarda Şeftali, Armut Çiçeği, Zambak, Beyaz Heliotrope, Şam Gülü ve Menekşe Yaprağı; alt notalarda Kaşmir Ağacı, Abanoz, Amber, Tonka Fasulyesi, Vanilya, Hindistan Cevizi ve Şeker bulunur.</t>
         </is>
       </c>
     </row>
@@ -1155,20 +953,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Black Oudh Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>86</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>['odunsu', 'pudramsı', 'misk', 'kehribar', 'paçuli', 'vanilya', 'yeşil', 'sıcak baharatlı', 'balzamik', 'hayvansal']</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Black OudhbyAl Haramain Perfumesis, kadınlar ve erkekler için Amber-Woody bir kokudur. Üst notalarda Misk; orta notalarda Sedir ve Bitkisel Notalar; alt notalarda Amber, Paçuli ve Vanilya bulunur.</t>
+          <t>['sıcak baharatlı', 'topraksı', 'odunsu', 'tatlı', 'kehribar', 'paçuli', 'çikolata', 'çiçeksi', 'balzamik', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Tom Ford'un Black Orchid adlı parfümü, kadınlar için Amber Floral bir kokudur. Black Orchid, 2006 yılında piyasaya sürülmüştür. David Apel ve Pierre Negrin tarafından yaratılmıştır. Üst notalarda Trüf Mantarı, Gardenya, Siyah Frenk Üzümü, Ylang-Ylang, Yasemin, Bergamot, Mandalina ve Amalfi Limonu; orta notalarda Orkide, Baharatlar, Gardenya, Meyveli Notalar, Ylang-Ylang, Yasemin ve Lotus; alt notalarda Meksika Çikolatası, Paçuli, Vanilya, Tütsü, Amber, Sandal Ağacı, Vetiver ve Beyaz Misk bulunur.</t>
         </is>
       </c>
     </row>
@@ -1185,20 +975,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Amber Oud Tobacco Edition Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>86</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>['sıcak baharatlı', 'tatlı', 'vanilya', 'tütün', 'tarçın', 'meyvemsi', 'hafif baharatlı', 'anason', 'odunsu', 'pudramsı']</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Al Haramain Perfumesi tarafından üretilen Amber Oud Tobacco Edition, kadınlar ve erkekler için Amber Baharatlı bir kokudur. Amber Oud Tobacco Edition, 2019 yılında piyasaya sürülmüştür. Üst notalarda Tütün Yaprağı, Tarçın, Karabiber ve Zencefil; orta notalarda Vanilya, Karanfil, Yıldız Anason, Kakao, Tonka Fasulyesi ve Tütsü; temel notalarda Tütün, Kurutulmuş Meyveler ve Odunsu Notalar bulunur.</t>
+          <t>['vanilya', 'tatlı', 'tütün', 'sıcak baharatlı', 'meyvemsi', 'odunsu', 'kakao', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Tom Ford'un Tobacco Vanille'i kadınlar ve erkekler için Amber baharatlı bir kokudur. Tobacco Vanille, 2007 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Olivier Gillotin'dir. Üst notalarda Tütün Yaprağı ve Baharatlı Notalar; orta notalarda Vanilya, Kakao, Tonka Fasulyesi ve Tütün Çiçeği; alt notalarda Kurutulmuş Meyveler ve Odunsu Notalar bulunur.</t>
         </is>
       </c>
     </row>
@@ -1215,18 +997,10 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Amber Oud Gold Edition Extreme Pure Perfume Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>86</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
           <t>['tatlı', 'meyveli', 'odunsu', 'kehribar', 'ozonik', 'pudramsı', 'taze', 'vanilya', 'misk', 'su']</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Al Haramain Perfumesi'nin Amber Oud Gold Edition Extreme Pure Parfümü, kadınlar ve erkekler için Amber Woody bir kokudur. Bu yeni bir parfümdür. Amber Oud Gold Edition Extreme Pure Parfüm 2022 yılında piyasaya sürüldü. Üst notalarda Bergamot ve Yeşil Notalar; orta notalarda Tatlı Notalar, Kavun, Ananas, Amber ve Sedir; alt notalarda Odunsu Notalar, Mür, Misk ve Vanilya bulunur.</t>
         </is>
@@ -1245,20 +1019,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Acqua di Parma Colonia Pura Acqua di Parmafor women and men</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>86</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'ozonik', 'aromatik', 'taze baharatlı', 'beyaz çiçeksi', 'yeşil', 'odunsu', 'misk', 'sarı çiçeksi', 'pudramsı']</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Acqua di Parma Colonia PurabyAcqua di Parma, kadınlar ve erkekler için narenciye aromalı bir parfümdür. Acqua di Parma Colonia Pura, 2017 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim François Demachy'dir. Üst notalarda ozonik notalar, bergamot, portakal ve turunçgiller; orta notalarda nergis, yasemin ve kişniş; alt notalarda beyaz misk, sedir ve paçuli bulunur.</t>
+          <t>['turunçgil', 'meyvemsi', 'tatlı', 'karamel', 'odunsu', 'pudramsı', 'aromatik', 'misk', 'beyaz çiçeksi', 'kehribar']</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Erba Pura MagicabySospiro Perfumesis, kadınlar ve erkekler için bir parfümdür. Bu yeni bir parfümdür. Erba Pura Magic, 2022 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Christian Provenzano'dur. Üst notalarda Meyveli Notalar, Limon, Bergamot ve Yasemin; orta notalarda Balzamik Notalar ve Süsen; alt notalarda Karamel, Sedir, Misk ve Amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -1275,20 +1041,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Haramain Oud Cambodi Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>86</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>['misk', 'pudramsı', 'odunsu', 'vanilya', 'aromatik', 'balzamik', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Haramain Oud CambodibyAl Haramain Perfumesis, kadınlar ve erkekler için Amber Woody bir kokudur. Üst notalarda Amyris, Zencefil, Deri ve Değerli Ağaçlar; orta notalarda Sandal Ağacı, Agar Ağacı (Ud), Guaiac Ağacı, Paçuli ve Sedir; temel notalarda Beyaz Misk, Vanilya, Benzoin, Amber, Tütsü ve Mür bulunur.</t>
+          <t>['ud', 'gül', 'odunsu', 'kehribar', 'sıcak baharatlı', 'paçuli', 'balzamik', 'çiçeksi', 'pudramsı', 'misk']</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Dioris'in Oud Ispahan adlı parfümü, kadınlar ve erkekler için Amber Floral bir kokudur. Oud Ispahan, 2012 yılında piyasaya sürülmüştür. Parfümün arkasındaki isim François Demachy'dir. Üst notalarda Laden; orta notalarda Gül, Paçuli ve Safran; alt notalarda Agarwood (Ud), Sandal Ağacı ve Sedir bulunur.</t>
         </is>
       </c>
     </row>
@@ -1305,20 +1063,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Entourage Rouge Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>86</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>['odunsu', 'taze baharatlı', 'aromatik', 'topraksı', 'yosunlu', 'dumanlı', 'yeşil', 'turunçgil', 'paçuli', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Entourage RougebyAl Haramain Perfumesis, kadınlar ve erkekler için bir parfümdür. Üst notalarda Sardunya ve Bergamot; orta notalarda Çay, Duman ve Hindistan Cevizi; alt notalarda Yosun, Vetiver, Paçuli ve Sedir bulunur.</t>
+          <t>['aromatik', 'tuzlu', 'deniz', 'turunçgil', 'misk', 'bitkisel', 'hafif baharatlı', 'çiçeksi', 'sucul']</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Wood Sage &amp; Sea SaltJo Malone London tarafından üretilen, kadınlar ve erkekler için aromatik bir kokudur. Wood Sage &amp; Sea Salt 2014 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Christine Nagel'dır.</t>
         </is>
       </c>
     </row>
@@ -1335,20 +1085,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Blackberry Amber Bath &amp; Body Worksfor women</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>86</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'pudramsı', 'tatlı', 'vanilya', 'odunsu', 'kehribar', 'misk', 'karamel', 'sıcak baharatlı', 'paçuli']</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Bath &amp; Body Works'ten Blackberry Amber, kadınlar için çiçeksi ve meyveli bir gurme kokusudur. Blackberry Amber, 2007 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Calice Becker'dır. Üst notalarda Böğürtlen ve Ahududu; orta notalarda Heliotrope, Karamel ve Yasemin; alt notalarda ise Kehribar, Misk, Sandal Ağacı, Vanilya ve Paçuli bulunur.</t>
+          <t>['meyvemsi', 'taze baharatlı', 'aromatik', 'turunçgil', 'odunsu', 'tatlı', 'kafur', 'çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Blackberry &amp; BaybyJo Malone London, kadınlar için çiçeksi ve meyveli bir kokudur.Blackberry &amp; Bay, 2012 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Fabrice Pellegrin'dir.</t>
         </is>
       </c>
     </row>
@@ -1365,20 +1107,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Urban Flowers Paris Avonfor women</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>86</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>['pudramsı', 'çiçeksi', 'turunçgil', 'sıcak baharatlı', 'sarı çiçeksi', 'tatlı', 'ozonik', 'misk kokulu', 'odunsu', 'yeşil']</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Urban Flowers ParisbyAvon, kadınlara yönelik çiçeksi bir kokudur. Urban Flowers Paris, 2007 yılında piyasaya sürülmüştür. Üst notalarda Limon, Kakule ve Kızılcık; orta notalarda Kamelya, Mimoza, Menekşe Yaprağı ve Orkide; alt notalarda Misk ve Sandal Ağacı bulunmaktadır.</t>
+          <t>['beyaz çiçeksi', 'sümbülteber', 'odunsu', 'tatlı', 'vanilya', 'sarı çiçeksi', 'pudramsı', 'turunçgil', 'hayvansal', 'yeşil']</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>MarfabyMemo Paris, kadınlar ve erkekler için çiçeksi odunsu misk kokusudur. Marfaby, 2016 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki koku Alienor Massenet'tir. Üst notalarda Portakal Çiçeği ve Mandalina; orta notalarda Sümbülteber, Ylang-Ylang ve Agave; alt notalarda Vanilya, Sandal Ağacı, Beyaz Misk ve Sedir bulunur.</t>
         </is>
       </c>
     </row>
@@ -1395,20 +1129,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Queen of the Night Al-Rehabfor women</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>86</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>['odunsu', 'beyaz çiçeksi', 'vanilya', 'turunçgil', 'lavanta', 'sıcak baharatlı', 'pudramsı', 'aromatik', 'taze baharatlı', 'çikolata']</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Al-Rehabi'nin Queen of the Night'ı kadınlar için Amber Floral bir koku. Bu yeni bir koku. Queen of the Night, 2024 yılında piyasaya sürüldü. Üst notalarda Bergamot ve Lavanta; orta notalarda Beyaz Çiçekler ve Çikolata; alt notalarda Sandal Ağacı ve Vanilya bulunmaktadır.</t>
+          <t>['turunçgil', 'çiçeksi', 'taze', 'aromatik', 'gül', 'yeşil', 'misk', 'taze baharatlı', 'yosunlu', 'topraksı']</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Kedu SesamebyMemo Paris, kadınlar ve erkekler için bir Chypre Çiçeksi kokusudur. Kedu Sesame, 2017 yılında piyasaya sürülmüştür. Üst notalarda Şakayık, Frezya ve Gül; orta notalarda Greyfurt, Portakal Çiçeği, Mandalina, Mate ve Lotus; alt notalarda Susam, Beyaz Misk, Yosun ve Palmiye Ağacı bulunur.</t>
         </is>
       </c>
     </row>
@@ -1425,20 +1151,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Playing With The Devil By Kilianfor women</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>86</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'sıcak baharatlı', 'odunsu', 'turunçgil', 'taze baharatlı', 'taze']</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Playing With The Devilby Kilian, kadınlar için Amber Floral bir koku. Playing With The Devil, 2013 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Calice Becker. Üst notalarda Siyah Frenk Üzümü, Beyaz Şeftali, Litchi ve Kan Portakalı; orta notalarda Yenibahar, Biber, Gül ve Yasemin; alt notalarda Vanilya, Sandal Ağacı, Paçuli, Sedir, Benzoin ve Tonka Fasulyesi bulunuyor.</t>
+          <t>['gül', 'pudramsı', 'vanilya', 'odunsu', 'turunçgil', 'çiçeksi', 'misk', 'deri', 'hafif baharatlı', 'tatlı']</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Devil TenderbyEx Nihilo, kadınlar için çiçeksi bir kokudur. Devil Tender, 2016 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki burun Nadege Le Garlantezec'tir. Üst notalarda Pembe Biber, Şeftali, Pembe Greyfurt ve Bergamot; orta notalarda Gül Suyu, Bulgar Gülü, Gül Yaprakları ve Çay; alt notalarda Süet, Heliotrope, Sandal Ağacı, Vanilya ve Beyaz Sedir Özü bulunur.</t>
         </is>
       </c>
     </row>
@@ -1455,20 +1173,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Absolute by Exclusive Avonfor men</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>86</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>['ud', 'kehribar', 'odunsu', 'sıcak baharatlı', 'taze baharatlı', 'aromatik', 'dumanlı', 'paçuli', 'balzamik', 'turunçgil']</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>ExclusivebyAvon'dan Absolute, erkekler için odunsu aromatik bir kokudur. Absolute by Exclusive, 2020 yılında piyasaya sürüldü. Absolute by Exclusive, Marion Costero ve Stephen Nilsen tarafından yaratıldı. Üst notalarda Sicilya Limonu, Lavanta ve Afrika Sardunyası; orta notalarda Agar Ağacı (Ud), Teksas Sediri, Tütsü ve Safralein; alt notalarda Kehribar, Endonezya Paçuli Yaprağı ve Ambrein bulunur.</t>
+          <t>['çiçeksi', 'odunsu', 'pudramsı', 'menekşe', 'meyvemsi', 'misk', 'kehribar', 'turunçgil']</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Mojave GhostbyByredo, kadınlar ve erkekler için Amber Floral bir kokudur. Mojave Ghost, 2014 yılında piyasaya sürülmüştür. Üst notalarda Sapodilla ve Ambrette (Misk Hatmisi); orta notalarda Manolya, Menekşe ve Sandal Ağacı; alt notalarda Ambergris ve Sedir bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -1485,20 +1195,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Max'd Al Haramain Perfumesfor men</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>86</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'odunsu', 'sıcak baharatlı', 'çiçeksi', 'misk', 'tatlı', 'metalik', 'deri', 'pudramsı', 'tütün']</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Max'dbyAl Haramain Perfumesis erkekler için odunsu çiçeksi misk kokusu.</t>
+          <t>['turunçgil', 'misk', 'taze', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>BlancbyAl-Rehabi, kadınlara ve erkeklere yönelik bir parfümdür.</t>
         </is>
       </c>
     </row>
@@ -1515,20 +1217,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Naseej Al Oud Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>86</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>['ud', 'deri', 'odunsu', 'kehribar', 'hafif baharatlı', 'hayvansal', 'taze baharatlı', 'gül']</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Naseej Al Oudby Afnani, kadınlar ve erkekler için bir Deri kokusudur. Naseej Al Oud, 2021 yılında piyasaya sürülmüştür. Üst notalarda Agarwood (Ud), Pembe Biber, Bergamot ve Safran; orta notalarda Odunsu Notalar, Gül, Yasemin ve Süsen; temel notalarda Agarwood (Ud), Deri ve Amber bulunmaktadır.</t>
+          <t>['odunsu', 'ud', 'sıcak baharatlı', 'aromatik', 'vanilya', 'balzamik', 'taze baharatlı', 'kehribar', 'pudramsı', 'tatlı']</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Tom Ford'un Oud Wood'u kadınlar ve erkekler için Amber Woody notalı bir parfümdür. Oud Wood 2007 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Richard Herpin'dir.</t>
         </is>
       </c>
     </row>
@@ -1545,18 +1239,10 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Blanche Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>86</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
           <t>['meyvemsi', 'tropikal', 'çiçeksi', 'gül', 'taze', 'odunsu', 'turunçgil', 'taze baharatlı', 'aromatik']</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>BlanchebyAl Haramain Perfumesis, kadınlar ve erkekler için bir parfümdür. Bu yeni bir parfümdür. Blanche 2023 yılında piyasaya sürüldü. Üst notalarda Litchi, Pitahaya, Bergamot ve Hindistan cevizi; orta notalarda Gül, Şakayık ve Vanilya; alt notalarda Sedir, Misk, Vetiver ve Kaşmir bulunur.</t>
         </is>
@@ -1575,20 +1261,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Naturals Pomegranate &amp; Mango Avonfor women</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>86</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'tropikal', 'tatlı', 'odunsu', 'terpenik', 'ekşi', 'taze baharatlı']</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Naturals Pomegranate &amp; MangobyAvon, kadınlar için Aromatik Meyveli bir kokudur. Naturals Pomegranate &amp; Mango, 2019 yılında piyasaya sürülmüştür.</t>
+          <t>['tropikal', 'tatlı', 'meyvemsi', 'odunsu', 'turunçgil', 'ud', 'sarı çiçeksi', 'beyaz çiçeksi', 'terpenik', 'topraksı']</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Mango MangabyMontale, kadınlar ve erkekler için bir parfümdür. Mango Manga, 2010 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Pierre Montale'dir. Üst notalarda Mango ve Portakal; orta notalarda Ylang-Ylang, Yasemin ve Portakal Çiçeği; alt notalarda Agar Ağacı (Ud), meşe yosunu, Vetiver ve Virginia Sediri bulunur.</t>
         </is>
       </c>
     </row>
@@ -1605,20 +1283,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scentini Nights Purple Pulse Avonfor women</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>86</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>['odunsu', 'çiçeksi', 'meyveli', 'taze', 'taze baharatlı', 'ekşi']</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Scentini Nights Purple PulsebyAvon, kadınlar için çiçeksi ve meyveli bir kokudur. Scentini Nights Purple Pulse, 2012 yılında piyasaya sürülmüştür. Üst notasında Nar; orta notasında Kiraz Çiçeği; alt notasında Sedir bulunmaktadır.</t>
+          <t>['meyvemsi', 'gül', 'tatlı', 'odunsu', 'misk', 'taze baharatlı', 'paçuli', 'pudramsı', 'aromatik', 'sıcak baharatlı']</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Montale'den Dark Purple, kadınlar için Amber Floral bir kokudur. Dark Purple, 2011 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Pierre Montale'dir. Üst notalarda erik ve portakal; orta notalarda gül, kırmızı meyveler, paçuli ve sardunya; alt notalarda misk, tik ağacı ve amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -1635,20 +1305,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Musk Al Ghazal Eau de Parfum Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>86</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>['misk', 'sıcak baharatlı', 'taze baharatlı', 'tatlı', 'anason', 'pudramsı', 'çikolata', 'hafif baharatlı', 'aromatik', 'vanilya']</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Musk Al Ghazal Eau de ParfumbyAl Haramain Perfumesis, kadınlar ve erkekler için bir Amber kokusudur. Üst notalarda kimyon ve anason; orta notalarda misk; alt notalarda baharatlar, bitter çikolata, odunsu notalar ve vanilya bulunur.</t>
+          <t>['gül', 'çiçeksi', 'meyveli', 'taze', 'misk', 'yeşil', 'aromatik', 'pudramsı', 'tropikal', 'odunsu']</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DelinabyParfums de Marly, kadınlar için çiçeksi bir kokudur. Delin, 2017 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Quentin Bisch'tir. Üst notalarda Litchi, Ravent, Bergamot ve Hindistan cevizi; orta notalarda Türk gülü, şakayık, misk, Petalia ve vanilya; alt notalarda ise kaşmir, tütsü, sedir ve Haiti vetiveri bulunur.</t>
         </is>
       </c>
     </row>
@@ -1665,20 +1327,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>God Is A Woman Body Mist Ariana Grandefor women</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>86</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>['vanilya', 'meyveli', 'tatlı', 'pudramsı', 'çiçeksi', 'misk', 'odunsu', 'su', 'süsen', 'gül']</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Ariana Grande'nin God Is A Woman Body Mist'i, kadınlar için Amber Floral bir koku. Bu kokunun arkasındaki isim Jérôme Epinette. Üst notalarda Armut ve Misk Hatmi; orta notalarda Türk Gülü ve Süsen; alt notalarda Madagaskar Vanilyası ve Sandal Ağacı bulunuyor.</t>
+          <t>['vanilya', 'tatlı', 'odunsu', 'balzamik', 'pudramsı', 'laktonik', 'sıcak baharatlı', 'hafif baharatlı', 'misk']</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>This is HerbyZadig &amp; Voltaire, kadınlar için Amber Vanilya aromalı bir parfümdür. This is Her, 2016 yılında piyasaya sürülmüştür. This is Her, Sidonie Lancesseur ve Michel Almairac tarafından yaratılmıştır. Üst notalarda Pembe Biber, İpek Ağacı Çiçeği ve Yasemin Sambac; orta notalarda Çırpılmış Krema, Vanilya ve Kestane; alt notalarda Sandal Ağacı ve Kaşmir Ağacı bulunur.</t>
         </is>
       </c>
     </row>
@@ -1695,20 +1349,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Autumn Pear &amp; Cashmere Woods Bath &amp; Body Worksfor women</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>86</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'odunsu', 'tatlı', 'taze', 'kehribar', 'misk', 'pudramsı', 'su', 'balzamik']</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Bath &amp; Body Works'ün Autumn Pear &amp; Cashmere Woods'u kadınlar için çiçeksi ve meyveli bir kokudur. Autumn Pear &amp; Cashmere Woods 2014 yılında piyasaya sürülmüştür. Üst notalarda Granny Smith elması ve nektarin; orta notalarda armut, incir ve yasemin; alt notalarda kaşmir ağacı, sandal ağacı ve amber bulunur.</t>
+          <t>['çiçeksi', 'meyveli', 'tatlı', 'gül', 'su', 'misk', 'taze', 'paçuli', 'yeşil', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>English Pear &amp; Freesia by Jo Malone London, kadınlar için Chypre Fruity bir parfümdür. English Pear &amp; Freesia, 2010 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Christine Nagel'dır. Üst notalarda Armut ve Kavun; orta notalarda Frezya ve Gül; alt notalarda Misk, Paçuli, Ravent ve Amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -1725,18 +1371,10 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Not A Perfume Juliette Has A Gunfor women</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>88</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
           <t>['kehribar', 'misk', 'odunsu']</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Juliette Has A Gun'ın Not A Perfume'u kadınlara yönelik çiçeksi odunsu misk kokusudur. Not A Perfume 2010 yılında piyasaya sürülmüştür.</t>
         </is>
@@ -1755,20 +1393,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>In Bloom by Reese Witherspoon Avonfor women</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>86</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>['beyaz çiçeksi', 'yeşil', 'çiçeksi', 'meyvemsi', 'laktik', 'tozlu', 'tatlı']</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Reese Witherspoon'un In Bloom by Avoni, kadınlar için çiçeksi yeşil bir koku. Reese Witherspoon'un In Bloom'u 2009 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Reese Witherspoon. Üst notalarda Şeftali, Beyaz Çay ve Yeşil Notalar; orta notalarda Gardenya, Yasemin, Manolya ve Mimoza; alt notalarda Kaşmir Ağacı, Kavak (Populus) tomurcukları ve Amber bulunuyor.</t>
+          <t>['taze', 'çiçeksi', 'gül', 'misk', 'meyvemsi', 'tropikal', 'pudramsı', 'hafif baharatlı']</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Ex Nihilo'nun Lust in Paradise'ı, kadınlar için çiçeksi odunsu misk kokusudur. Lust in Paradise, 2019 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Louise Turner'dır. Üst notalarda Pembe Biber; orta notalarda Şakayık, Litchi ve Petalia; alt notalarda Misk, Beyaz Sedir Özü ve Amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -1785,20 +1415,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Haramain Oud Cambodi Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>86</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>['misk', 'pudramsı', 'odunsu', 'vanilya', 'aromatik', 'balzamik', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Haramain Oud CambodibyAl Haramain Perfumesis, kadınlar ve erkekler için Amber Woody bir kokudur. Üst notalarda Amyris, Zencefil, Deri ve Değerli Ağaçlar; orta notalarda Sandal Ağacı, Agar Ağacı (Ud), Guaiac Ağacı, Paçuli ve Sedir; temel notalarda Beyaz Misk, Vanilya, Benzoin, Amber, Tütsü ve Mür bulunur.</t>
+          <t>['odunsu', 'sıcak baharatlı', 'kehribar', 'balzamik', 'dumanlı', 'aromatik', 'deri', 'meyvemsi', 'vanilya', 'ud']</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Ombre Oud Intense BlackbyArmafis, kadınlar ve erkekler için Amber Woody bir koku. Üst notalarda Tagetes, Frenk Üzümü, Şeftali ve Gül; orta notalarda Safran, Tütsü ve Huş Ağacı; alt notalarda Sandal Ağacı, Paçuli, Amber Ağacı, Öd Ağacı, Vanilya ve Benzoin bulunur.</t>
         </is>
       </c>
     </row>
@@ -1815,20 +1437,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Urbanist Femme Intense Al Haramain Perfumesfor women</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>86</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'tatlı', 'paçuli', 'taze', 'tropikal', 'kehribar', 'beyaz çiçeksi', 'odunsu', 'topraksı', 'pudramsı']</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Al Haramain Perfumesi tarafından üretilen Urbanist Femme Intense, kadınlar için Chypre Meyveli bir kokudur. Urbanist Femme Intense, 2020 yılında piyasaya sürülmüştür. Üst notalarda Ananas, Elma, Limon ve Portakal; orta notalarda Yasemin ve Süsen; alt notalarda Paçuli, Amber ve Misk bulunmaktadır.</t>
+          <t>['kehribar', 'odunsu', 'sıcak baharatlı', 'yeşil', 'çiçeksi', 'paçuli', 'pudramsı', 'taze baharatlı', 'balzamik', 'hayvansal']</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CoSTUME NATIONAL'ın Scent Intense'i, kadınlar ve erkekler için Amber Woody bir kokudur. Scent Intense, 2002 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Laurent Bruyere. Üst notalarda Çay, Tarçın, Elma ve Bergamot; orta notalarda Ebegümeci, Yasemin ve Davana; alt notalarda Kristal Amber, Amber, Paçuli, Sandal Ağacı, Deri ve Olibanum bulunur.</t>
         </is>
       </c>
     </row>
@@ -1845,20 +1459,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fearless and Fabulous Carolina Herrerafor women</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>86</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>['beyaz çiçeksi', 'meyveli', 'tatlı', 'odunsu', 'misk', 'su', 'hafif baharatlı', 'laktik', 'taze', 'paçuli']</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Carolina Herrera'nın Fearless and Fabulous'u, kadınlar için çiçeksi ve meyveli bir koku. Bu yeni bir parfüm. Fearless and Fabulous, 2022'de piyasaya sürüldü. Fearless and Fabulous, Fanny Bal ve Julien Rasquinet tarafından yaratıldı. Üst notalarda Armut ve Pembe Biber; orta notalarda Gardenya; alt notalarda Kaşmir Ağacı ve Paçuli yer alıyor.</t>
+          <t>['aromatik', 'deri', 'vanilya', 'badem', 'kehribar', 'odunsu', 'lavanta', 'tatlı', 'pudramsı', 'hayvansal']</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Tom Ford'un Fucking Fabulous parfümü, kadınlar ve erkekler için bir Deri parfümüdür. Fucking Fabulous 2017 yılında piyasaya sürülmüştür. Üst notalarda Lavanta ve Adaçayı; orta notalarda Deri, Acı Badem, Vanilya ve Süsen; alt notalarda Deri, Tonka Fasulyesi, Kaşmir, Beyaz Ağaçlar ve Amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -1875,20 +1481,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Afrodite Tiziana Terenzifor women and men</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>86</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>['çiçeksi', 'taze', 'tatlı', 'meyvemsi', 'misk', 'beyaz çiçeksi', 'hafif baharatlı', 'pudramsı', 'odunsu', 'yeşil']</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Afrodite by Tiziana Terenzi, kadınlar ve erkekler için Amber Floral bir kokudur. Afrodite, 2018 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Paolo Terenzi. Üst notalarda Leylak, Beyaz Frenk Üzümü, Beyaz Şeftali, Pembe Biber ve Vanilya Özü; orta notalarda Vadi Zambağı, Portakal Çiçeği, Sardunya, Sümbülteber ve Süsen; alt notalarda Beyaz Misk, Ambergris, Abanoz, Paçuli ve Sandal Ağacı bulunur.</t>
+          <t>['turunçgil', 'tatlı', 'meyvemsi', 'pudramsı', 'odunsu', 'misk', 'ozonik', 'taze baharatlı']</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>GuminbyTiziana Terenzi, kadınlar ve erkekler için bir parfümdür. Gumin, 2016 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Paolo Terenzi'dir. Üst notalarda Mandalina, Portakal, Ananas ve Bergamot; orta notalarda Ozon, Amber, Menekşe, Yasemin ve Gül; alt notalarda Misk, Sandal Ağacı, Huş Ağacı ve Öd Ağacı bulunur.</t>
         </is>
       </c>
     </row>
@@ -1905,18 +1503,10 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lira Xerjofffor women</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>60</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
           <t>['turunçgil', 'karamel', 'vanilya', 'tatlı', 'tarçın', 'pudramsı', 'taze baharatlı', 'hafif baharatlı', 'sıcak baharatlı', 'balzamik']</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>LirabyXerjoffi, kadınlar için Amber Floral bir kokudur. LirabyXerjoffi, 2011 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Chris Maurice'tir. Üst notalarda Kan Portakalı, Bergamot ve Lavanta; orta notalarda Tarçın, Meyan Kökü ve Yasemin; alt notalarda Karamel, Vanilya ve Misk bulunur.</t>
         </is>
@@ -1935,20 +1525,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>9pm Afnanfor men</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>86</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>['vanilya', 'kehribar', 'sıcak baharatlı', 'tarçın', 'tatlı', 'meyvemsi', 'pudramsı', 'lavanta', 'aromatik', 'taze']</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>9pmbyAfnani erkekler için Amber Vanilya kokusu. 9pm, 2020 yılında piyasaya sürüldü. Üst notalarda Elma, Tarçın, Yabani Lavanta ve Bergamot; orta notalarda Portakal Çiçeği ve Vadi Zambağı; alt notalarda Vanilya, Tonka Fasulyesi, Amber ve Paçuli bulunuyor.</t>
+          <t>['odunsu', 'pudramsı', 'misk', 'sıcak baharatlı', 'süsen', 'paçuli', 'kehribar', 'ozonik', 'topraksı', 'sucul']</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Rumz Al Rasasi 9325 Pour EllebyRasasi kadınlara yönelik bir parfümdür. Rumz Al Rasasi 9325 Pour Elle 2014 yılında piyasaya sürülmüştür. Üst notalarda Menekşe Yaprağı ve Karanfil; orta notalarda Sedir ve Süsen; alt notalarda Misk, Paçuli, Amber, Sandal Ağacı ve Vanilya bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -1965,20 +1547,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Club de Nuit Sillage Armaffor women and men</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>86</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'odunsu', 'misk', 'pudramsı', 'aromatik', 'meyvemsi', 'kehribar', 'taze baharatlı', 'çiçeksi', 'gül']</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Armafis Club de Nuit Sillage, kadınlar ve erkekler için çiçeksi odunsu misk kokusudur. Club de Nuit Sillage, 2020 yılında piyasaya sürülmüştür. Üst notalarda Bergamot, Siyah Frenk Üzümü, Limon, Misket Limonu, Menekşe Yaprağı ve Zencefil; orta notalarda Gül, Süsen ve Yasemin; temel notalarda Ambroxan, Misk, Sandal Ağacı ve Sedir bulunmaktadır.</t>
+          <t>['sıcak baharatlı', 'ud', 'aromatik', 'odunsu', 'topraksı', 'metalik', 'deri', 'tütün']</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DignifiedbyHouse Of Sillage, erkekler için odunsu baharatlı bir kokudur. Dignified 2015 yılında piyasaya sürülmüştür.</t>
         </is>
       </c>
     </row>
@@ -1995,20 +1569,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cherry Flower Al-Rehabfor women and men</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>86</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>['çiçeksi', 'taze', 'misk', 'meyvemsi', 'pudramsı', 'aromatik', 'gül', 'su', 'turunçgil']</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Al-Rehabi Cherry Flower, kadınlar ve erkekler için çiçeksi yeşil bir koku. Üst notalarda Bergamot ve Frenk üzümü tomurcukları; orta notalarda Kiraz Çiçeği, Nilüfer ve Çay Gülü; alt notalarda Beyaz Misk, Süsen Kökü ve Vetiver bulunuyor.</t>
+          <t>['kiraz', 'tatlı', 'badem', 'fındıksı', 'meyvemsi', 'vanilya', 'sıcak baharatlı', 'kehribar', 'odunsu', 'balzamik']</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Tom Fort'un Lost Cherry'si, kadınlar ve erkekler için Amber Floral bir kokudur. Lost Cherry, 2018 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Louise Turner'dır. Üst notalarda Acı Badem, Siyah Kiraz ve Kiraz Likörü; orta notalarda Ekşi Kiraz, Erik, Türk Gülü ve Yasemin Sambac; alt notalarda Vanilya, Tonka Fasulyesi, Tarçın, Peru Balsamı, Benzoin, Sandal Ağacı, Karanfil, Sedir, Paçuli ve Vetiver bulunur.</t>
         </is>
       </c>
     </row>
@@ -2025,20 +1591,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Naseej Al Kiswah Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>86</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>['odunsu', 'kehribar', 'deri', 'ud', 'paçuli', 'hayvansal', 'vanilya', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Naseej Al KiswahbyAfnani, Kadınlar ve Erkekler için Amber Woody Kokusudur. orta notalarda Woodsy Notes ve Sedir; temel notalar Amber, Deri ve Agarwood'dur (Ud).</t>
+          <t>['misk', 'meyvemsi', 'pudramsı', 'turunçgil', 'tatlı']</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Summer TiffanybyReef Perfumesis, kadınlar ve erkekler için çiçeksi ve meyveli bir kokudur. Bu yeni bir kokudur. Summer Tiffany 2023 yılında piyasaya sürüldü. Üst notalarda mandalina, orta notalarda şeftali, alt notalarda misk bulunur.</t>
         </is>
       </c>
     </row>
@@ -2055,20 +1613,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Musk Al Ghazal Eau de Parfum Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>86</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>['misk', 'sıcak baharatlı', 'taze baharatlı', 'tatlı', 'anason', 'pudramsı', 'çikolata', 'hafif baharatlı', 'aromatik', 'vanilya']</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Musk Al Ghazal Eau de ParfumbyAl Haramain Perfumesis, kadınlar ve erkekler için bir Amber kokusudur. Üst notalarda kimyon ve anason; orta notalarda misk; alt notalarda baharatlar, bitter çikolata, odunsu notalar ve vanilya bulunur.</t>
+          <t>['misk', 'pudramsı', 'sıcak baharatlı', 'taze baharatlı', 'odunsu', 'beyaz çiçeksi', 'hayvansal']</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Musk KashmirbyAttar Collection, kadınlar ve erkekler için çiçeksi odunsu bir misk kokusudur. Musk Kashmir, 2016 yılında piyasaya sürülmüştür.</t>
         </is>
       </c>
     </row>
@@ -2085,20 +1635,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Aquavibe Abraça (Aquavibe Laugh More) Avonfor women</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>86</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'beyaz çiçeksi', 'taze', 'meyvemsi', 'tatlı', 'yeşil', 'kehribar', 'misk', 'ozonik', 'hafif baharatlı']</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Avoni markalı Aquavibe Abraça (Aquavibe Laugh More), kadınlara yönelik çiçeksi ve meyveli bir kokudur. Aquavibe Abraça (Aquavibe Laugh More), 2017 yılında piyasaya sürülmüştür. Üst notalarda Mandalina, Limon ve Rezene; orta notalarda Vadi Zambağı, Ahududu ve Menekşe Yaprağı; alt notalarda Misk, Amber ve Tonka Fasulyesi bulunmaktadır.</t>
+          <t>['kehribar', 'ud', 'meyvemsi', 'çiçeksi', 'sıcak baharatlı', 'odunsu', 'tatlı', 'taze baharatlı']</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>More Than WordsbyXerjoffi, kadınlar ve erkekler için Amber Woody aromalı bir parfümdür. More Than Words, 2012 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Chris Maurice'dir.</t>
         </is>
       </c>
     </row>
@@ -2115,20 +1657,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Black Oudh Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>86</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>['odunsu', 'pudramsı', 'misk', 'kehribar', 'paçuli', 'vanilya', 'yeşil', 'sıcak baharatlı', 'balzamik', 'hayvansal']</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Black OudhbyAl Haramain Perfumesis, kadınlar ve erkekler için Amber-Woody bir kokudur. Üst notalarda Misk; orta notalarda Sedir ve Bitkisel Notalar; alt notalarda Amber, Paçuli ve Vanilya bulunur.</t>
+          <t>['odunsu', 'pudramsı', 'misk', 'sıcak baharatlı', 'süsen', 'paçuli', 'kehribar', 'ozonik', 'topraksı', 'sucul']</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Rumz Al Rasasi 9325 Pour EllebyRasasi kadınlara yönelik bir parfümdür. Rumz Al Rasasi 9325 Pour Elle 2014 yılında piyasaya sürülmüştür. Üst notalarda Menekşe Yaprağı ve Karanfil; orta notalarda Sedir ve Süsen; alt notalarda Misk, Paçuli, Amber, Sandal Ağacı ve Vanilya bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -2145,20 +1679,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Paris – Biarritz Chanelfor women and men</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>86</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'yeşil', 'taze baharatlı', 'beyaz çiçeksi']</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Paris – BiarritzbyChanelis, kadınlar ve erkekler için çiçeksi, odunsu bir misk kokusu. Paris – Biarritz, 2018 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Olivier Polge. Üst notalarda mandalina, bergamot, limon, portakal ve greyfurt; orta notalarda portakal çiçeği esansı, yeşil notalar ve müge; alt notalarda beyaz misk ve paçuli bulunuyor.</t>
+          <t>['odunsu', 'meyvemsi', 'turunçgil', 'pudramsı', 'aromatik', 'deri', 'tatlı', 'sıcak baharatlı', 'hayvansal', 'vanilya']</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Cedrat BoisebyMancera, kadınlar ve erkekler için narenciye aromalı bir parfümdür. Cedrat Boise, 2011 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Pierre Montale'dir. Üst notalarda Sicilya Limonu, Siyah Frenk Üzümü, Bergamot ve Baharatlı Notalar; orta notalarda Meyveli Notalar, Paçuli Yaprağı ve Su Yasemini; alt notalarda Sedir, Deri, Sandal Ağacı, Vanilya, Beyaz Misk ve Yosun bulunur.</t>
         </is>
       </c>
     </row>
@@ -2175,20 +1701,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Roja Dove Haute Parfumerie 15th Anniversary Roja Dovefor women and men</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>86</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>['odunsu', 'pudramsı', 'kehribar', 'turunçgil', 'menekşe', 'balzamik', 'vanilya', 'aromatik', 'sıcak baharatlı', 'çiçeksi']</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Roja Dove Haute Parfumerie 15th Anniversary, Roja Dove tarafından kadınlar ve erkekler için Amber Floral bir kokudur. Roja Dove Haute Parfumerie 15th Anniversary, 2019 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki burun Roja Dove'dur. Üst notalarda Aldehitler, Bergamot, Portakal, Greyfurt, Limon ve Mandalina; orta notalarda Menekşe, Şeftali, Laden, Kediotu, Yasemin, Vadi Zambağı, Şampaka ve Sardunya; alt notalarda İris, Kaşmir Ağacı, Laden, Vanilya, Yosun, Paçuli, Sandal Ağacı, Tonka Fasulyesi, Amyris, Misk Kedisi, Ambrarome, Benzoin, Zencefil, Olibanum, Vetiver, Peru Balsamı, Kişniş, Biber ve Misk bulunur.</t>
+          <t>['yeşil', 'turunçgil', 'taze', 'taze baharatlı', 'kehribar', 'meyvemsi', 'misk', 'hayvansal', 'yosunlu', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Dear Pollyby Vilhelm Parfumerie, kadınlar ve erkekler için aromatik bir kokudur. Dear Polly, 2015 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Jérôme Epinette'dir. Üst notalarda Bergamot ve Elma; orta notalarda Siyah Çay; alt notalarda Siyah Kehribar, Misk ve Meşe Yosunu bulunur.</t>
         </is>
       </c>
     </row>
@@ -2205,22 +1723,10 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Golden Mango Lagoon Bath &amp; Body Worksfor women</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>86</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>['tropikal', 'meyveli', 'tatlı', 'terpenik', 'denizsel']</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Bath &amp; Body Works'ün Golden Mango Lagoon'u, kadınlar için çiçeksi ve meyveli bir kokudur. Bu yeni bir kokudur. Golden Mango Lagoon 2023 yılında piyasaya sürüldü.</t>
-        </is>
-      </c>
+          <t>['tropikal', 'meyveli', 'tatlı', 'terpenik']</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2235,20 +1741,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Amber Oud Gold Edition Extreme Pure Perfume Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>86</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>['tatlı', 'meyveli', 'odunsu', 'kehribar', 'ozonik', 'pudramsı', 'taze', 'vanilya', 'misk', 'su']</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Al Haramain Perfumesi'nin Amber Oud Gold Edition Extreme Pure Parfümü, kadınlar ve erkekler için Amber Woody bir kokudur. Bu yeni bir parfümdür. Amber Oud Gold Edition Extreme Pure Parfüm 2022 yılında piyasaya sürüldü. Üst notalarda Bergamot ve Yeşil Notalar; orta notalarda Tatlı Notalar, Kavun, Ananas, Amber ve Sedir; alt notalarda Odunsu Notalar, Mür, Misk ve Vanilya bulunur.</t>
+          <t>['meyvemsi', 'beyaz çiçeksi', 'odunsu', 'tatlı', 'kehribar', 'karamel', 'turunçgil', 'vanilya', 'pudramsı', 'laktonik']</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Juicy Couture'un Viva La juicy Pink Luxe Parfüm 2019'u kadınlar için Çiçeksi Meyveli Gurme bir kokudur. Viva La juicy Pink Luxe Parfüm 2019, 2019 yılında piyasaya sürülmüştür. Üst notalarda Orman Meyveleri ve Mandalina; orta notalarda Gardenya, Yasemin ve Hanımeli; temel notalarda Pralin, Karamel, Vanilya, Amber ve Sandal Ağacı bulunur.</t>
         </is>
       </c>
     </row>
@@ -2265,22 +1763,10 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avon Frozen Candy Dream Eau de Cologne Avonfor women</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>86</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>['vanilya', 'tatlı', 'pudramsı', 'beyaz çiçeksi', 'laktik', 'meyvemsi']</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Avon Frozen Candy Dream Eau de ColognebyAvon, kadınlar için çiçeksi ve meyveli bir gurme parfümdür. Üst notalarda Kayısı ve Şeker; orta notalarda Gardenya; alt notalarda Vanilya bulunur.</t>
-        </is>
-      </c>
+          <t>['odunsu', 'turunçgil', 'aromatik', 'meyvemsi', 'pudramsı', 'taze baharatlı']</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2295,20 +1781,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>The Pride Of Armaf Admiral Armaffor women and men</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>86</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>['kehribar', 'sıcak baharatlı', 'lavanta', 'vanilya', 'hafif baharatlı', 'aromatik', 'tatlı', 'balzamik', 'paçuli', 'dumanlı']</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Armaf Admiral'ın Gururu, kadınlar ve erkekler için Amber Vanilya kokusudur. Bu yeni bir kokudur. Armaf Admiral'ın Gururu, 2024 yılında piyasaya sürüldü. Üst notalarda Pembe Biber ve Kakule; orta notalarda Lavanta ve Tütsü; alt notalarda Tonka Fasulyesi, Paçuli, Vanilya ve Amber bulunur.</t>
+          <t>['aromatik', 'kehribar', 'aldehitli', 'taze', 'sıcak baharatlı', 'votka', 'yeşil', 'misk', 'yosunlu', 'hafif baharatlı']</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Vodka on the Rocksby, kadınlar ve erkekler için aromatik bir kokudur. Vodka on the Rocks, 2014 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Sidonie Lancesseur. Üst notalarda kişniş, aldehitler ve kakule; orta notalarda ravent, müge ve pembe gül; alt notalarda ambroxan, meşe yosunu ve sandal ağacı bulunur.</t>
         </is>
       </c>
     </row>
@@ -2325,22 +1803,10 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>California Avonfor women</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>86</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>['çiçeksi', 'odunsu', 'pudramsı', 'sıcak baharatlı', 'aldehitli', 'gül']</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>CaliforniabyAvon, kadınlara yönelik Floral Aldehyde bir parfümdür. California 1976 yılında piyasaya sürülmüştür.</t>
-        </is>
-      </c>
+          <t>['odunsu', 'sıcak baharatlı', 'pudramsı', 'turunçgil', 'vanilya']</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2355,20 +1821,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Absolute by Exclusive Avonfor men</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>86</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>['ud', 'kehribar', 'odunsu', 'sıcak baharatlı', 'taze baharatlı', 'aromatik', 'dumanlı', 'paçuli', 'balzamik', 'turunçgil']</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>ExclusivebyAvon'dan Absolute, erkekler için odunsu aromatik bir kokudur. Absolute by Exclusive, 2020 yılında piyasaya sürüldü. Absolute by Exclusive, Marion Costero ve Stephen Nilsen tarafından yaratıldı. Üst notalarda Sicilya Limonu, Lavanta ve Afrika Sardunyası; orta notalarda Agar Ağacı (Ud), Teksas Sediri, Tütsü ve Safralein; alt notalarda Kehribar, Endonezya Paçuli Yaprağı ve Ambrein bulunur.</t>
+          <t>['coca-cola', 'sıcak baharatlı', 'odunsu', 'turunç', 'tarçın', 'taze baharatlı', 'kehribar', 'meyvemsi', 'yeşil']</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Bad Boys Are No Good But Good Boys Are No FunbyBy Kilian, kadınlar ve erkekler için odunsu ve baharatlı bir koku. Bad Boys Are No Good But Good Boys Are No Fun, 2018 yılında piyasaya sürüldü. Üst notalarda Coca-Cola ve Limon; orta notalarda Tarçın, Elma ve Hindistan Cevizi; alt notalarda Sedir ve Amber Ağacı bulunuyor.</t>
         </is>
       </c>
     </row>
@@ -2385,18 +1843,10 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>I Don't Need A Prince By My Side To Be A Princess By Kilianfor women and men</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>88</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
           <t>['tatlı', 'vanilya', 'pudramsı', 'sıcak baharatlı', 'taze', 'yeşil', 'kehribar', 'turunçgil']</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>I Don't Need A Prince By My Side To Be A Princessby Kilian, kadınlar ve erkekler için Amber Vanilya aromalı bir parfümdür. I Don't Need A Prince By My Side To Be A Princess, 2018 yılında piyasaya sürülmüştür. Üst notalarda Limon; orta notalarda Yeşil Çay, Zencefil, Şeftali, Hedione, Yasemin ve Elma; alt notalarda Hatmi, Vanilya ve Benzoin bulunur.</t>
         </is>
@@ -2415,20 +1865,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Amber Oud Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>86</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>['kehribar', 'odunsu', 'aromatik', 'turunçgil', 'taze baharatlı', 'pudramsı', 'misk', 'sıcak baharatlı', 'balzamik']</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Amber OudbyAl Haramain Perfumesi, kadınlar ve erkekler için Amber Woody bir kokudur. Amber Oud, 2018 yılında piyasaya sürüldü. Üst notalarda Biberiye, Bergamot, Sedir ve Limon; orta notalarda Baharatlar, Sedir ve Guaiac Ağacı; temel notalarda Reçineler, Amber ve Misk bulunmaktadır.</t>
+          <t>['odunsu', 'sıcak baharatlı', 'kehribar', 'taze baharatlı', 'aromatik', 'paçuli', 'lavanta', 'pudramsı', 'meyvemsi']</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Amber WoodbyAjmalis kadınlar ve erkekler için Amber Woody bir kokudur. Amber Wood 2014 yılında piyasaya sürülmüştür. Üst notalarda Kakule, Elma, Lavanta ve Beyaz Biber; orta notalarda Sedir ve Süsen; temel notalarda Amber, Odunsu Notalar ve Paçuli bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -2445,18 +1887,10 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Escentric 01 Escentric Moleculesfor women and men</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>86</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
           <t>['odunsu', 'misk', 'turunçgil', 'kehribar', 'hafif baharatlı', 'süsen', 'pudramsı', 'aromatik', 'menekşe']</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Escentric 01 byEscentric Molecules kadınlar ve erkekler için odunsu çiçeksi misk kokusu. Escentric 01 2006 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Geza Schoen.</t>
         </is>
@@ -2475,20 +1909,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Amber Oud Gold Edition Extreme Pure Perfume Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>86</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>['tatlı', 'meyveli', 'odunsu', 'kehribar', 'ozonik', 'pudramsı', 'taze', 'vanilya', 'misk', 'su']</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Al Haramain Perfumesi'nin Amber Oud Gold Edition Extreme Pure Parfümü, kadınlar ve erkekler için Amber Woody bir kokudur. Bu yeni bir parfümdür. Amber Oud Gold Edition Extreme Pure Parfüm 2022 yılında piyasaya sürüldü. Üst notalarda Bergamot ve Yeşil Notalar; orta notalarda Tatlı Notalar, Kavun, Ananas, Amber ve Sedir; alt notalarda Odunsu Notalar, Mür, Misk ve Vanilya bulunur.</t>
+          <t>['sıcak baharatlı', 'tatlı', 'vanilya', 'odunsu', 'pudramsı', 'kehribar', 'taze baharatlı', 'beyaz çiçeksi', 'aromatik', 'turunçgil']</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Tom Ford'un Noir Extreme'i erkekler için Amber Woody notalara sahip bir parfümdür. Noir Extreme, 2015 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Sonia Constant'tır. Üst notalarda Kakule, Hindistan Cevizi, Safran, Mandalina ve Portakal Çiçeği; orta notalarda Kulfi, Gül, Mastik veya Mercan, Portakal Çiçeği ve Yasemin; alt notalarda Vanilya, Amber, Odunsu Notalar ve Sandal Ağacı bulunur.</t>
         </is>
       </c>
     </row>
@@ -2505,20 +1931,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Narcos'is Vertusfor women and men</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>86</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'sıcak baharatlı', 'aromatik', 'tatlı', 'tropikal', 'kehribar', 'yeşil', 'kahve', 'odunsu', 'hayvansal']</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Narcos'isbyVertus kadın ve erkeklere yönelik bir parfümdür. Narcos'is 2017 yılında piyasaya sürülmüştür. Üst notalarda Ravent, Kakule, Kahve ve Mandalina; orta notalarda Mango, Zencefil ve Amber; alt notalarda Vetiver, Ambergris ve Şeftali bulunmaktadır.</t>
+          <t>Bilgi Yok</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Bilgi Yok</t>
         </is>
       </c>
     </row>
@@ -2535,20 +1953,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sweet Sugar Plum &amp; Vanille Avonfor women</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>86</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>['meyveli', 'vanilya', 'tatlı']</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Sweet Sugar Plum &amp; Vanille, Avoni'nin kadınlara yönelik Amber Vanilya kokusudur. Sweet Sugar Plum &amp; Vanille, 2020 yılında piyasaya sürülmüştür.</t>
+          <t>['gül', 'vanilya', 'pudramsı', 'misk', 'çiçeksi', 'odunsu', 'tatlı', 'turunçgil']</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Roses VanillebyMancera, kadınlar için Amber Vanilya kokusudur. Roses Vanille, 2011 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki burun Pierre Montale'dir. Üst nota İtalyan Limonu; orta nota Türk Gülü; alt notalar Vanilya, Beyaz Misk ve Sedir'dir.</t>
         </is>
       </c>
     </row>
@@ -2565,18 +1975,10 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Karagoz Nishanefor women and men</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>86</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
           <t>['meyvemsi', 'tatlı', 'odunsu', 'yeşil', 'topraksı', 'aromatik', 'ud', 'beyaz çiçeksi', 'kehribar', 'paçuli']</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>KaragozbyNishane, kadınlar ve erkekler için Aromatik Meyveli bir kokudur. Karagoz, 2017 yılında piyasaya sürüldü. Bu kokunun arkasındaki burun Jorge Lee'dir. Üst notalarda Üzüm, Ananas ve Bitkisel Notalar; orta notalarda Paçuli, Portakal Çiçeği ve Yasemin; alt notalarda Vetiver, Öd Ağacı ve Amber bulunur.</t>
         </is>
@@ -2595,20 +1997,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Le Parfait Azure Pour Femme Armaffor women</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>86</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'beyaz çiçeksi', 'meyvemsi', 'çiçeksi', 'taze baharatlı', 'aromatik', 'sıcak baharatlı', 'sümbülteber', 'pudramsı', 'tatlı']</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Le Parfait Azure Pour FemmebyArmafis, kadınlar için Amber Floral bir koku. Üst notalarda Bergamot, Kakule, Şeftali ve Gül; orta notalarda Yasemin, Osmanthus, Sümbülteber, Erik ve Elma; alt notalarda Sandal Ağacı, Vanilya ve Tütün bulunmaktadır.</t>
+          <t>['sıcak baharatlı', 'odunsu', 'ozonik', 'su', 'aromatik', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Elite Gentleman'dan Absolute Santal by Avoni, erkekler için odunsu bir koku. Bu yeni bir koku. Elite Gentleman'dan Absolute Santal, 2022'de piyasaya sürüldü. Bu kokunun arkasındaki isim Frank Voelkl. Üst nota Kakule; orta nota Menekşe Yaprağı; alt nota Avustralya Sandal Ağacı.</t>
         </is>
       </c>
     </row>
@@ -2625,20 +2019,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dehnal Oudh Cambodi No.1 Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>86</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>['ud', 'taze baharatlı']</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Dehnal Oudh Cambodi No.1byAl Haramain Perfumesis kadınlar ve erkekler için bir Amber kokusu.</t>
+          <t>['gül', 'taze baharatlı', 'çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Dior Passage No.4byDior kadınlar için çiçeksi bir kokudur. Dior Passage No.4, 2007 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim François Demachy'dir.</t>
         </is>
       </c>
     </row>
@@ -2655,20 +2041,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Leather Oudh Al Haramain Perfumesfor women</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>86</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>['odunsu', 'meyveli', 'deri', 'tatlı', 'kehribar', 'hayvansal', 'dumanlı', 'misk', 'aromatik', 'balzamik']</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Leather OudhbyAl Haramain Perfumesis kadınlara yönelik bir parfümdür. Leather Oudh 2016 yılında piyasaya sürülmüştür. Üst notalarda Ahududu ve Kekik; orta notalarda Odunsu Notalar, Tütsü, Kaşmir Ağacı ve Yasemin; alt notalarda Deri, Sedir, Amber ve Misk bulunmaktadır.</t>
+          <t>['deri', 'meyveli', 'hayvansal', 'tatlı', 'kehribar', 'dumanlı', 'sıcak baharatlı']</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Tom Ford'un Tuscan Leather parfümü, kadınlar ve erkekler için bir deri kokusudur. Tuscan Leather 2007 yılında piyasaya sürülmüştür. Üst notalarda Ahududu, Safran ve Kekik; orta notalarda Olibanum ve Yasemin; alt notalarda Deri, Süet, Odunsu Notalar ve Amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -2685,20 +2063,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portfolio Neroli Canvas Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>86</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'beyaz çiçeksi', 'aromatik', 'taze baharatlı', 'yeşil', 'taze']</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Portfolio Neroli CanvasbyAl Haramain Perfumesis, kadınlar ve erkekler için çiçeksi odunsu misk kokusudur. Portfolio Neroli Canvas, 2018 yılında piyasaya sürülmüştür. Üst notalarda Petitgrain, Bergamot ve Limon; orta notalarda Neroli ve Portakal Çiçeği; temel notalarda Misk, Amber ve Sedir bulunmaktadır.</t>
+          <t>['turunçgil', 'beyaz çiçeksi', 'taze baharatlı', 'aromatik']</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Tom Fordy'nin Neroli Portofino'su, kadınlar ve erkekler için narenciye aromalı bir parfümdür. Neroli Portofino, 2011 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Rodrigo Flores-Roux'dur. Üst notalarda Bergamot, Mandalina, Limon, Acı Portakal, Lavanta, Biberiye ve Mersin; orta notalarda Afrika Portakal Çiçeği, Neroli, Yasemin ve Pitosporum; alt notalarda ise Kehribar, Melekotu ve Ambrette (Ebegümeci) bulunur.</t>
         </is>
       </c>
     </row>
@@ -2715,20 +2085,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Naturals Peach Velvet Avonfor women</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>86</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'tatlı', 'pudramsı', 'vanilya', 'çiçeksi', 'laktonik']</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Naturals Peach VelvetbyAvon, kadınlar için Aromatik Meyveli bir kokudur. Naturals Peach Velvet, 2019 yılında piyasaya sürülmüştür. Üst nota Beyaz Şeftali; orta nota Orkide; temel nota Vanilya'dır.</t>
+          <t>['odunsu', 'sıcak baharatlı', 'meyvemsi', 'kehribar', 'vanilya', 'pudramsı', 'tatlı', 'aromatik', 'balzamik', 'turunçgil']</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Tom Ford'un Bitter Peach'i kadınlar ve erkekler için Amber Vanilya aromalı bir kokudur. Bitter Peach, 2020 yılında piyasaya sürülmüştür. Üst notalarda Şeftali, Kan Portakalı, Kakule ve Heliotrope; orta notalarda Rom, Konyak, Davana ve Yasemin; temel notalarda Vanilya, Endonezya Paçuli Yaprağı, Tonka Fasulyesi, Sandal Ağacı, Benzoin, Kaşmir, Styrax, Labdanum ve Vetiver bulunur.</t>
         </is>
       </c>
     </row>
@@ -2745,18 +2107,10 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ani Nishanefor women and men</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>86</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
           <t>['sıcak baharatlı', 'vanilya', 'odunsu', 'turunçgil', 'pudramsı', 'kehribar', 'aromatik', 'hafif baharatlı', 'balzamik', 'meyvemsi']</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2771,20 +2125,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Entourage Rouge Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>86</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>['odunsu', 'taze baharatlı', 'aromatik', 'topraksı', 'yosunlu', 'dumanlı', 'yeşil', 'turunçgil', 'paçuli', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Entourage RougebyAl Haramain Perfumesis, kadınlar ve erkekler için bir parfümdür. Üst notalarda Sardunya ve Bergamot; orta notalarda Çay, Duman ve Hindistan Cevizi; alt notalarda Yosun, Vetiver, Paçuli ve Sedir bulunur.</t>
+          <t>['odunsu', 'badem', 'kehribar', 'sıcak baharatlı', 'hayvansal', 'fındıksı', 'misk', 'meyvemsi', 'beyaz çiçeksi', 'metalik']</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Baccarat Rouge 540 Extrait de ParfumbyMaison Francis Kurkdjian, kadınlar ve erkekler için Amber Floral bir kokudur. Baccarat Rouge 540 Extrait de Parfum, 2017 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Francis Kurkdjian. Üst notalarda Acı Badem ve Safran; orta notalarda Mısır Yasemini ve Sedir; alt notalarda Ambergris, Odunsu Notalar ve Misk bulunur.</t>
         </is>
       </c>
     </row>
@@ -2801,20 +2147,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bergamask Orto Parisifor women and men</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>86</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'misk', 'pudramsı', 'taze baharatlı', 'aromatik']</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>BergamaskbyOrto Parisi, kadınlar ve erkekler için narenciye aromalı bir kokudur. Bergamask, 2014 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Alessandro Gualtieri'dir. Üst notalarda Bergamot ve Limon; orta notalarda Lavanta, Portakal Çiçeği ve Vadi Zambağı; alt notalarda Misk, Sedir ve Tonka bulunmaktadır.</t>
+          <t>['misk', 'deniz', 'taze', 'su', 'kehribar', 'aromatik', 'turunçgil', 'pudramsı', 'ozonik', 'odunsu']</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>MegamarebyOrto Parisi, kadınlar ve erkekler için Aromatik Su Kokusu'dur. Megamare, 2019 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Alessandro Gualtieri. Üst notalarda Bergamot ve Limon; orta notalarda Deniz Yosunu, Calone ve Hedione; alt notalarda Misk, Ambroxan ve Sedir bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -2831,20 +2169,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Blush Intense Marc Jacobsfor women</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>86</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>['beyaz çiçeksi', 'misk', 'odunsu', 'pudramsı']</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Marc Jacobs'ın Blush Intense'i kadınlara yönelik çiçeksi bir kokudur. Blush Intense 2006 yılında piyasaya sürülmüştür. Orta notalarda Yasemin ve Portakal Çiçeği; temel notalarda Kaşmir Ağacı, Misk ve Sandal Ağacı bulunur.</t>
+          <t>['mineral', 'sıcak baharatlı', 'deri', 'ud', 'odunsu', 'ozonik', 'turunçgil', 'su', 'misk', 'meyvemsi']</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>GanymedebyMarc-Antoine Barrois, kadınlar ve erkekler için odunsu baharatlı bir kokudur. Ganymede, 2019 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Quentin Bisch'tir.</t>
         </is>
       </c>
     </row>
@@ -2861,20 +2191,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Black Oudh Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>86</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>['odunsu', 'pudramsı', 'misk', 'kehribar', 'paçuli', 'vanilya', 'yeşil', 'sıcak baharatlı', 'balzamik', 'hayvansal']</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Black OudhbyAl Haramain Perfumesis, kadınlar ve erkekler için Amber-Woody bir kokudur. Üst notalarda Misk; orta notalarda Sedir ve Bitkisel Notalar; alt notalarda Amber, Paçuli ve Vanilya bulunur.</t>
+          <t>['taze baharatlı', 'kehribar', 'sıcak baharatlı', 'turunçgil', 'beyaz çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Black Pepper &amp; Amber, NerolibyZielinski &amp; Rozenis kadınlar ve erkekler için Amber Baharatlı bir koku.</t>
         </is>
       </c>
     </row>
@@ -2891,20 +2213,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Energizing Energy Mandarin &amp; Jasmine Avonfor women</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>86</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'beyaz çiçeksi']</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Avoni tarafından üretilen Enerji Verici Mandarin ve Yasemin, kadınlar için Çiçeksi ve Meyveli bir kokudur. Enerji Verici Mandarin ve Yasemin, 2019 yılında piyasaya sürülmüştür.</t>
+          <t>['turunçgil', 'odunsu', 'misk', 'kehribar']</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Escentric Molecule tarafından üretilen Molecule 01 + Mandarin, kadınlar ve erkekler için bir narenciye kokusudur. Molecule 01 + Mandarin, 2021 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Geza Schoen'dir.</t>
         </is>
       </c>
     </row>
@@ -2921,20 +2235,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portfolio Cupid's Rose Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>86</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>['odunsu', 'sıcak baharatlı', 'paçuli', 'gül', 'meyvemsi', 'tarçın', 'ud', 'tatlı', 'topraksı', 'balzamik']</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Portfolio Cupid's Rose by Al Haramain Perfumesis, kadınlar ve erkekler için Amber Floral bir kokudur. Portfolio Cupid's Rose, 2019 yılında piyasaya sürülmüştür. Üst notalarda Gül ve Bergamot; orta notalarda erik, Tarçın ve Sedir; alt notalarda Paçuli, Agarwood (Ud) ve Sandal Ağacı bulunmaktadır.</t>
+          <t>['odunsu', 'pudramsı', 'çiçeksi', 'vanilya', 'meyvemsi', 'beyaz çiçeksi', 'yeşil', 'misk', 'tatlı', 'hafif baharatlı']</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Devil's Intrigue, Haute Fragrance Company HFC tarafından üretilen, kadınlar için çiçeksi odunsu misk notalı bir parfümdür. Devil's Intrigue, 2018 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Benoît Bergia'dır. Üst notalarda Osmanthus ve Beyaz Çay; orta notalarda Sandal Ağacı ve Portakal Çiçeği; alt notalarda Vanilya, Kaşmir ve Odunsu Notalar bulunur.</t>
         </is>
       </c>
     </row>
@@ -2951,20 +2257,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Naseej Al Oud Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>86</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>['ud', 'deri', 'odunsu', 'kehribar', 'hafif baharatlı', 'hayvansal', 'taze baharatlı', 'gül']</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Naseej Al Oudby Afnani, kadınlar ve erkekler için bir Deri kokusudur. Naseej Al Oud, 2021 yılında piyasaya sürülmüştür. Üst notalarda Agarwood (Ud), Pembe Biber, Bergamot ve Safran; orta notalarda Odunsu Notalar, Gül, Yasemin ve Süsen; temel notalarda Agarwood (Ud), Deri ve Amber bulunmaktadır.</t>
+          <t>['taze baharatlı', 'aromatik', 'lavanta', 'sıcak baharatlı', 'odunsu', 'ud', 'metalik', 'kozalaklı', 'taze', 'turunçgil']</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Oud for Greatness NeobyInitio Parfums Privesis, kadınlar ve erkekler için aromatik baharatlı bir kokudur. Bu yeni bir kokudur. Oud for Greatness Neo, 2024 yılında piyasaya sürüldü.</t>
         </is>
       </c>
     </row>
@@ -2981,20 +2279,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>51 Pour Femme Essence De Parfum Roja Dovefor women</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>86</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>['beyaz çiçeksi', 'odunsu', 'tatlı', 'vanilya', 'pudramsı', 'sarı çiçeksi', 'kehribar', 'meyvemsi', 'sıcak baharatlı', 'balzamik']</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>51 Pour Femme Essence De ParfumRoja Dove kadınlar için Amber bir kokudur. 51 Pour Femme Essence De Parfum2021 yılında piyasaya sürülmüştür. Üst notalarda Bergamot; orta notalarda Ylang-Ylang, Ahududu, Gardenya, Portakal Çiçeği, Sümbülteber, Zambak, Yasemin, Mayıs Gülü ve Vadi Zambağı; alt notalarda Vanilya, Benzoin, Kaşmir Ağacı, Sandal Ağacı, Süsen, Menekşe, Tarçın, Anason, Karanfil ve Paçuli bulunmaktadır.</t>
+          <t>['turunçgil', 'aromatik', 'odunsu', 'taze baharatlı', 'meyvemsi', 'tatlı', 'deri', 'hafif baharatlı', 'beyaz çiçeksi', 'çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>OligarchbyRoja Dove, erkekler için bir Chypre kokusudur. Oligarch, 2016 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki burun Roja Dove'dur. Üst notalarda Limon, Bergamot, Misket Limonu, Lavanta ve Kekik; orta notalarda Elma, Siyah Frenk Üzümü, Portakal Çiçeği, Şampaka, Hindistan Cevizi, Yasemin ve Zambak; alt notalarda Ardıç Meyvesi, Huş Ağacı, Pembe Biber, Sedir, Meşe Yosunu, Tonka Fasulyesi, Kehribar, Mate, Deri, Misk, Anason, Vanilya, Menekşe Kökü ve Paçuli bulunur.</t>
         </is>
       </c>
     </row>
@@ -3011,20 +2301,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Red African Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>86</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>['taze baharatlı', 'karamel', 'tatlı', 'kehribar', 'balzamik', 'vanilya', 'pudramsı', 'hayvansal', 'odunsu']</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Al Haramain Perfumesi'nin Red African'ı kadınlar ve erkekler için Amber Woody bir kokudur. Red African 2017 yılında piyasaya sürülmüştür. Üst notalarda Brezilya Gül Ağacı; orta notalarda Hindistan Cevizi ve Karamel; alt notalarda Ambergris, Vanilya ve Misk bulunmaktadır.</t>
+          <t>['odunsu', 'sıcak baharatlı', 'kehribar', 'tatlı', 'turunçgil', 'meyvemsi', 'beyaz çiçeksi', 'tarçın', 'paçuli', 'fındıksı']</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain RedbyAl-Jazeera Perfumesis, kadınlar ve erkekler için Amber Spicy bir kokudur. Paris Saint-Germain Red, 2019 yılında piyasaya sürüldü.</t>
         </is>
       </c>
     </row>
@@ -3041,20 +2323,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Queen of the Night Al-Rehabfor women</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>86</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>['odunsu', 'beyaz çiçeksi', 'vanilya', 'turunçgil', 'lavanta', 'sıcak baharatlı', 'pudramsı', 'aromatik', 'taze baharatlı', 'çikolata']</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Al-Rehabi'nin Queen of the Night'ı kadınlar için Amber Floral bir koku. Bu yeni bir koku. Queen of the Night, 2024 yılında piyasaya sürüldü. Üst notalarda Bergamot ve Lavanta; orta notalarda Beyaz Çiçekler ve Çikolata; alt notalarda Sandal Ağacı ve Vanilya bulunmaktadır.</t>
+          <t>['çiçeksi', 'meyvemsi', 'gül', 'taze', 'misk', 'tatlı', 'hayvansal', 'su', 'hafif baharatlı']</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Haute Fragrance Company HFC tarafından üretilen Dancing Queen, kadınlar için Amber Floral bir kokudur. Dancing Queen, 2021 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Vincent Ricord'dur. Üst notalarda Siyah Frenk Üzümü, Armut ve Gül; orta notalarda Şakayık, Gül ve Yasemin; alt notalarda Misk, Ambergris ve Öd Ağacı bulunur.</t>
         </is>
       </c>
     </row>
@@ -3071,18 +2345,10 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bvlgari Extreme Bvlgarifor men</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>86</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
           <t>['turunçgil', 'taze baharatlı', 'odunsu', 'aromatik', 'yeşil', 'taze', 'pudramsı', 'sıcak baharatlı']</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>Bvlgari Extremeby Bvlgari, erkekler için odunsu aromatik bir kokudur. Bvlgari Extreme, 1999 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Jacques Cavallier'dir. Üst notalarda Çay, Greyfurt, Bergamot, Portakal Çiçeği, Petitgrain, Kişniş, Lavanta ve Galbanum; orta notalarda Balsam Köknarı, Guaiac Ağacı, Biber, Hindistan Cevizi, Brezilya Gül Ağacı ve Kakule; alt notalarda Misk, Sedir, Süsen, Meşe Yosunu ve Sandal Ağacı bulunur.</t>
         </is>
@@ -3101,20 +2367,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ombre Oud Intense Black Armaffor women and men</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>86</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>['odunsu', 'sıcak baharatlı', 'kehribar', 'balzamik', 'dumanlı', 'aromatik', 'deri', 'meyvemsi', 'vanilya', 'ud']</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Ombre Oud Intense BlackbyArmafis, kadınlar ve erkekler için Amber Woody bir koku. Üst notalarda Tagetes, Frenk Üzümü, Şeftali ve Gül; orta notalarda Safran, Tütsü ve Huş Ağacı; alt notalarda Sandal Ağacı, Paçuli, Amber Ağacı, Öd Ağacı, Vanilya ve Benzoin bulunur.</t>
+          <t>['kehribar', 'ud', 'sıcak baharatlı', 'dumanlı', 'gül', 'meyveli', 'deri', 'odunsu', 'balzamik', 'tatlı']</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Louis Vuitton'un Ombre Nomade'i kadınlar ve erkekler için Amber Woody bir kokudur. Ombre Nomade 2018 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Jacques Cavallier'dir.</t>
         </is>
       </c>
     </row>
@@ -3131,18 +2389,10 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hacivat Oud Nishanefor women and men</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>86</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
           <t>['ud', 'taze baharatlı', 'tatlı', 'meyveli', 'odunsu', 'turunçgil', 'taze', 'kehribar', 'sıcak baharatlı', 'aromatik']</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>Hacivat OudbyNishane, kadınlar ve erkekler için bir parfüm. Bu yeni bir parfüm. Hacivat Oud, 2023 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Dominique Ropion. Üst notalarda Ananas, Turunçgiller, Pembe Biber ve Karabiber; orta notalarda Tütsü, Olibanum ve Yasemin; alt notalarda Ud, Haiti Vetiveri, Paçuli ve Vanilya bulunuyor.</t>
         </is>
@@ -3161,20 +2411,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Leather Oudh Al Haramain Perfumesfor women</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>86</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>['odunsu', 'meyveli', 'deri', 'tatlı', 'kehribar', 'hayvansal', 'dumanlı', 'misk', 'aromatik', 'balzamik']</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Leather OudhbyAl Haramain Perfumesis kadınlara yönelik bir parfümdür. Leather Oudh 2016 yılında piyasaya sürülmüştür. Üst notalarda Ahududu ve Kekik; orta notalarda Odunsu Notalar, Tütsü, Kaşmir Ağacı ve Yasemin; alt notalarda Deri, Sedir, Amber ve Misk bulunmaktadır.</t>
+          <t>['deri', 'ozonik', 'hayvansal', 'sıcak baharatlı', 'topraksı', 'yosunlu', 'su', 'paçuli', 'odunsu', 'beyaz çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Tom Ford'un Ombre Leather 16'sı kadın ve erkekler için bir deri kokusudur. Ombre Leather 16, 2016 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki burun Sonia Constant'tır.</t>
         </is>
       </c>
     </row>
@@ -3191,20 +2433,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portfolio Cupid's Rose Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>86</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>['odunsu', 'sıcak baharatlı', 'paçuli', 'gül', 'meyvemsi', 'tarçın', 'ud', 'tatlı', 'topraksı', 'balzamik']</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Portfolio Cupid's Rose by Al Haramain Perfumesis, kadınlar ve erkekler için Amber Floral bir kokudur. Portfolio Cupid's Rose, 2019 yılında piyasaya sürülmüştür. Üst notalarda Gül ve Bergamot; orta notalarda erik, Tarçın ve Sedir; alt notalarda Paçuli, Agarwood (Ud) ve Sandal Ağacı bulunmaktadır.</t>
+          <t>['sıcak baharatlı', 'vanilya', 'ud', 'odunsu', 'kehribar', 'dumanlı', 'balzamik', 'aromatik', 'kahve', 'beyaz çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Penhaligon'un Bewitching Yasmine'i kadınlar için Amber Floral bir kokudur. Bewitching Yasmine 2017 yılında piyasaya sürülmüştür. Üst notalarda Kakule ve Kahve; orta notalarda Yasemin Sambac ve Köknar; alt notalarda Tahiti Vanilyası, Laos Oud ve Tütsü bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -3221,20 +2455,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portfolio Imperial Oud Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>86</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>['kehribar', 'balzamik', 'sıcak baharatlı', 'hayvansal', 'ud', 'odunsu', 'misk', 'dumanlı']</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Portfolio Imperial OudbyAl Haramain Perfumesis, kadınlar ve erkekler için Amber Woody bir kokudur. Portfolio Imperial Oud, 2018 yılında piyasaya sürülmüştür. Üst notalarda Hayvansal notalar ve Amber; orta notalarda Mür, Tütsü ve Ambrarom; temel notalarda Agarwood (Ud), Paçuli ve Misk bulunmaktadır.</t>
+          <t>['odunsu', 'taze baharatlı', 'aromatik', 'ud', 'kehribar', 'yeşil', 'topraksı', 'sıcak baharatlı']</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Bois Impérial by Essential Parfum, kadınlar ve erkekler için aromatik bir kokudur. Bois Impérial, 2020 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Quentin Bisch'tir.</t>
         </is>
       </c>
     </row>
@@ -3251,20 +2477,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Thohfa Attar Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>86</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>['odunsu', 'kehribar', 'çiçeksi', 'pudramsı', 'sıcak baharatlı', 'ud', 'misk', 'vanilya', 'metalik']</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Thohfa AttarbyAl Haramain Perfumesis kadınlar ve erkekler için bir Amber kokusu.</t>
+          <t>['vanilya', 'tatlı', 'pudramsı', 'çikolata', 'misk', 'sıcak baharatlı', 'meyvemsi', 'taze baharatlı']</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Crystal Love For HerbyAttar Koleksiyonu, kadınlar için Amber Vanilya aromalı bir kokudur. Crystal Love For Her, 2020 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Nuria Du Chene De Vere. Üst notalarda Meyve ve Gül; orta notalarda Sütlü Çikolata, Beyaz Misk ve Hindistan Cevizi; alt notalarda Burbon Vanilya ve Tonka Fasulyesi bulunur.</t>
         </is>
       </c>
     </row>
@@ -3281,20 +2499,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Thohfa Attar Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>86</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>['odunsu', 'kehribar', 'çiçeksi', 'pudramsı', 'sıcak baharatlı', 'ud', 'misk', 'vanilya', 'metalik']</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Thohfa AttarbyAl Haramain Perfumesis kadınlar ve erkekler için bir Amber kokusu.</t>
+          <t>['tatlı', 'meyveli', 'vanilya']</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>HayatibyAttar Koleksiyonu, kadınlar ve erkekler için çiçeksi ve meyveli bir kokudur. Hayati, 2018 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Yann Vasnier. Üst notalarda Ahududu, Orman Meyveleri ve Ananas; orta notalarda Çırpılmış Krema, Bal, Siyah Frenk Üzümü, Erik ve Çiçeksi Notalar; alt notalarda Dondurma, Vanilya ve Beyaz Misk bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -3311,20 +2521,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dehnal Oudh Cambodi No.1 Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>86</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>['ud', 'taze baharatlı']</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Dehnal Oudh Cambodi No.1byAl Haramain Perfumesis kadınlar ve erkekler için bir Amber kokusu.</t>
+          <t>Bilgi Yok</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Bilgi Yok</t>
         </is>
       </c>
     </row>
@@ -3341,20 +2543,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Leather Oudh Al Haramain Perfumesfor women</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>86</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>['odunsu', 'meyveli', 'deri', 'tatlı', 'kehribar', 'hayvansal', 'dumanlı', 'misk', 'aromatik', 'balzamik']</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Leather OudhbyAl Haramain Perfumesis kadınlara yönelik bir parfümdür. Leather Oudh 2016 yılında piyasaya sürülmüştür. Üst notalarda Ahududu ve Kekik; orta notalarda Odunsu Notalar, Tütsü, Kaşmir Ağacı ve Yasemin; alt notalarda Deri, Sedir, Amber ve Misk bulunmaktadır.</t>
+          <t>['gül', 'misk', 'aromatik', 'odunsu', 'turunçgil', 'deri', 'pudramsı', 'hafif baharatlı', 'taze baharatlı', 'çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Memo Paris'in French Leather parfümü, kadınlar ve erkekler için bir deri kokusudur. French Leather 2014 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Alienor Massenet'tir.</t>
         </is>
       </c>
     </row>
@@ -3371,20 +2565,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Haramain Oud Cambodi Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>86</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>['misk', 'pudramsı', 'odunsu', 'vanilya', 'aromatik', 'balzamik', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Haramain Oud CambodibyAl Haramain Perfumesis, kadınlar ve erkekler için Amber Woody bir kokudur. Üst notalarda Amyris, Zencefil, Deri ve Değerli Ağaçlar; orta notalarda Sandal Ağacı, Agar Ağacı (Ud), Guaiac Ağacı, Paçuli ve Sedir; temel notalarda Beyaz Misk, Vanilya, Benzoin, Amber, Tütsü ve Mür bulunur.</t>
+          <t>['gül', 'vanilya', 'ud', 'pudramsı', 'menekşe', 'kehribar', 'çiçeksi', 'sıcak baharatlı', 'balzamik']</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Maison Francis Kurkdjian'ın Oud Satin Mood'u kadınlar ve erkekler için Amber Woody bir kokudur. Oud Satin Mood 2015 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki burun Francis Kurkdjian'dır.</t>
         </is>
       </c>
     </row>
@@ -3401,20 +2587,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Abaan Lattafa Perfumesfor women</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>86</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>['odunsu', 'turunçgil', 'beyaz çiçeksi', 'pudramsı', 'sıcak baharatlı', 'paçuli', 'misk', 'balzamik', 'tatlı', 'taze baharatlı']</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>AbaanbyLattafa Perfumesis, kadınlar için çiçeksi odunsu misk kokusudur. Abaan, 2022 yılında piyasaya sürülmüştür. Üst notalarda Bergamot ve Portakal; orta notalarda Yasemin ve Portakal Çiçeği; alt notalarda Sandal Ağacı, Paçuli ve Misk bulunmaktadır.</t>
+          <t>['tatlı', 'vanilya', 'pudramsı', 'tropikal', 'misk', 'meyvemsi', 'çiçeksi', 'turunçgil']</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>YarabyLattafa Perfumesis, kadınlar için Amber Vanilya kokusudur. Yaraby 2020 yılında piyasaya sürülmüştür. Üst notalarda Orkide, Heliotrope ve Mandalina; orta notalarda Gurme Akor ve Tropikal Meyveler; temel notalarda Vanilya, Misk ve Sandal Ağacı bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -3431,18 +2609,10 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Naturals Berry Cake Avonfor women</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>86</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
           <t>['tatlı', 'meyveli']</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>Naturals Berry CakebyAvon, kadınlar için Aromatik Meyveli bir kokudur. Naturals Berry Cake, 2019 yılında piyasaya sürülmüştür.</t>
         </is>
@@ -3461,20 +2631,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>White Leather Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>86</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>['odunsu', 'taze baharatlı', 'aromatik', 'topraksı', 'dumanlı', 'yosunlu', 'paçuli', 'turunçgil', 'yeşil', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Al Haramain Perfumesis'in White Leather parfümü, kadınlar ve erkekler için bir Deri kokusudur. White Leather, 2000'li yıllarda piyasaya sürülmüştür. Üst notalarda Sardunya ve Bergamot; orta notalarda Duman, Çay ve Hindistan Cevizi; alt notalarda Vetiver, Sedir, Paçuli ve Meşe Yosunu bulunur.</t>
+          <t>['vanilya', 'pudramsı', 'tatlı', 'misk', 'meyvemsi', 'taze']</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>White ChocolabyChristian Richard kadınlara yönelik bir parfümdür. White Chocolat 2016 yılında piyasaya sürülmüştür. Üst notalarda Elma ve Karamel; orta notalarda Vanilya Çiçeği; alt notalarda Vanilya, Beyaz Misk ve Sandal Ağacı bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -3491,18 +2653,10 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Fiji Pineapple Palm Bath &amp; Body Worksfor women</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>86</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
           <t>['tatlı', 'meyveli', 'turunçgil', 'hindistan cevizi', 'tropikal', 'taze', 'beyaz çiçeksi', 'odunsu', 'yeşil', 'su']</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>Fiji Pineapple Palmby Bath &amp; Body Works, kadınlar için Çiçeksi Yeşil bir kokudur. Fiji Pineapple Palm, 2017 yılında piyasaya sürülmüştür. Üst notalarda Parmak Limonu, Armut ve Palmiye Yaprağı; orta notalarda Ananas, Yıldız Yasemini, Tiare Çiçeği ve Mango; alt notalarda Hindistan Cevizi Sütü, Odunsu Notalar, Karamel, Huş Ağacı ve Misk bulunmaktadır.</t>
         </is>
@@ -3521,18 +2675,10 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Almaz Kajalfor women and men</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>86</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
           <t>['meyvemsi', 'tatlı', 'vanilya', 'turunçgil', 'pudramsı', 'odunsu', 'aromatik', 'çiçeksi', 'hafif baharatlı', 'gül']</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>AlmazbyKajalis, kadınlar ve erkekler için bir parfüm. Bu yeni bir parfüm. Almaz, 2022 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Rania Jouaneh. Üst notalarda Siyah Frenk Üzümü, Kalabriyen bergamotu, Amalfi Limonu ve Mandalina; orta notalarda Ahududu, Kediotu, Türk Gülü ve Süsen; alt notalarda Esmer Şeker, Madagaskar Vanilyası, Tonka Fasulyesi, Sandal Ağacı, Misk ve Amber bulunuyor.</t>
         </is>
@@ -3551,20 +2697,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Thank U Next 2.0 Body Mist Ariana Grandefor women</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>86</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>['tatlı', 'meyveli', 'odunsu', 'pudralı', 'misk', 'çiçeksi']</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Ariana Grande'nin Thank U Next 2.0 Body Mist'i kadınlar için çiçeksi ve meyveli bir kokudur. Üst notalarda Nar, Elma suyu ve Yabani Çilek; orta notalarda Beyaz Orkide ve Yasemin; alt notalarda Hatmi, Misk ve Sandal Ağacı bulunur.</t>
+          <t>['meyveli', 'tatlı', 'gül', 'tropikal', 'çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Toy 2 Bubble Gumby Moschino, kadınlar için çiçeksi ve meyveli bir kokudur. Toy 2 Bubble Gum, 2021 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Olivier Pescheux. Üst notalarda Şekerlenmiş Meyveler, Acı Portakal ve Limon; orta notalarda Sakız, Bulgar Gülü, Yaban Mersini, Şeftali, Şeftali Çiçeği, Tarçın ve Zencefil; alt notalarda Misk, Ambroxan ve Sedir bulunur.</t>
         </is>
       </c>
     </row>
@@ -3581,20 +2719,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cherry Flower Al-Rehabfor women and men</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>86</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>['çiçeksi', 'taze', 'misk', 'meyvemsi', 'pudramsı', 'aromatik', 'gül', 'su', 'turunçgil']</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Al-Rehabi Cherry Flower, kadınlar ve erkekler için çiçeksi yeşil bir koku. Üst notalarda Bergamot ve Frenk üzümü tomurcukları; orta notalarda Kiraz Çiçeği, Nilüfer ve Çay Gülü; alt notalarda Beyaz Misk, Süsen Kökü ve Vetiver bulunuyor.</t>
+          <t>['misk', 'kiraz', 'tatlı', 'hafif baharatlı', 'kehribar', 'beyaz çiçeksi', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Tom Ford'un Electric Cherry'si, kadınlar ve erkekler için çiçeksi ve meyveli bir kokudur. Bu yeni bir kokudur. Electric Cherry, 2023 yılında piyasaya sürüldü. Üst notalarda Kiraz ve Zencefil; orta notalarda Yasemin Sambac; alt notalarda Pembe Biber, Ambrettolid ve Misk bulunur.</t>
         </is>
       </c>
     </row>
@@ -3611,20 +2741,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Naseej Al Kiswah Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>86</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>['odunsu', 'kehribar', 'deri', 'ud', 'paçuli', 'hayvansal', 'vanilya', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Naseej Al KiswahbyAfnani, Kadınlar ve Erkekler için Amber Woody Kokusudur. orta notalarda Woodsy Notes ve Sedir; temel notalar Amber, Deri ve Agarwood'dur (Ud).</t>
+          <t>['vanilya', 'ud', 'pudramsı', 'taze baharatlı', 'turunçgil', 'paçuli', 'misk', 'balzamik', 'odunsu', 'tatlı']</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>SahebbyArd Al Zaafarani, kadınlar ve erkekler için bir parfümdür. Üst notalarda Bergamot; orta notalarda Vanilya ve Paçuli; alt notalarda ise Öd Ağacı ve Misk bulunur.</t>
         </is>
       </c>
     </row>
@@ -3641,20 +2763,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Abaan Lattafa Perfumesfor women</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>86</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>['odunsu', 'turunçgil', 'beyaz çiçeksi', 'pudramsı', 'sıcak baharatlı', 'paçuli', 'misk', 'balzamik', 'tatlı', 'taze baharatlı']</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>AbaanbyLattafa Perfumesis, kadınlar için çiçeksi odunsu misk kokusudur. Abaan, 2022 yılında piyasaya sürülmüştür. Üst notalarda Bergamot ve Portakal; orta notalarda Yasemin ve Portakal Çiçeği; alt notalarda Sandal Ağacı, Paçuli ve Misk bulunmaktadır.</t>
+          <t>['meyvemsi', 'tarçın', 'misk', 'sıcak baharatlı', 'vanilya', 'pudramsı', 'odunsu', 'turunçgil', 'taze', 'yeşil']</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>HayaatibyLattafa Perfumesis, kadınlar ve erkekler için odunsu aromatik bir kokudur. Hayaati, 2020 yılında piyasaya sürülmüştür. Üst notalarda Elma ve Bergamot; orta notalarda Tarçın ve Odunsu Notalar; alt notalarda Misk ve Vanilya bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -3671,20 +2785,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ambre Ardent Avonfor women and men</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>86</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>['sıcak baharatlı', 'kehribar', 'paçuli', 'tarçın', 'taze baharatlı']</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Ambre ArdentbyAvon, kadınlar ve erkekler için bir Chypre kokusudur. Ambre Ardent, 2020 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Rodrigo Flores-Roux. Üst notalarda Kakule, Tarçın, Karanfil, Karabiber, Bergamot ve Mirabelle; orta notalarda Süsen, Beyaz Datura ve Yasemin; alt notalarda ise Kehribar, Benzoin ve Paçuli yer alıyor.</t>
+          <t>['tatlı', 'sıcak baharatlı', 'vanilya', 'tarçın', 'bal', 'kehribar', 'rom', 'karamel', 'balzamik', 'odunsu']</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Hermessence Ambre NarguilebyHermèsis, kadınlar ve erkekler için Amber baharatlı bir koku. Hermessence Ambre Narguile, 2004 yılında piyasaya sürüldü. Bu kokunun arkasındaki burun Jean-Claude Ellena'dır.</t>
         </is>
       </c>
     </row>
@@ -3701,22 +2807,10 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>51 Pour Femme Essence De Parfum Roja Dovefor women</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>86</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>['beyaz çiçeksi', 'odunsu', 'tatlı', 'vanilya', 'pudramsı', 'sarı çiçeksi', 'kehribar', 'meyvemsi', 'sıcak baharatlı', 'balzamik']</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>51 Pour Femme Essence De ParfumRoja Dove kadınlar için Amber bir kokudur. 51 Pour Femme Essence De Parfum2021 yılında piyasaya sürülmüştür. Üst notalarda Bergamot; orta notalarda Ylang-Ylang, Ahududu, Gardenya, Portakal Çiçeği, Sümbülteber, Zambak, Yasemin, Mayıs Gülü ve Vadi Zambağı; alt notalarda Vanilya, Benzoin, Kaşmir Ağacı, Sandal Ağacı, Süsen, Menekşe, Tarçın, Anason, Karanfil ve Paçuli bulunmaktadır.</t>
-        </is>
-      </c>
+          <t>['çiçeksi', 'turunçgil', 'odunsu', 'beyaz çiçeksi', 'misk', 'pudramsı', 'meyvemsi', 'tatlı', 'taze', 'taze baharatlı']</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3731,20 +2825,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Afrodite Tiziana Terenzifor women and men</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>86</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>['çiçeksi', 'taze', 'tatlı', 'meyvemsi', 'misk', 'beyaz çiçeksi', 'hafif baharatlı', 'pudramsı', 'odunsu', 'yeşil']</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Afrodite by Tiziana Terenzi, kadınlar ve erkekler için Amber Floral bir kokudur. Afrodite, 2018 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Paolo Terenzi. Üst notalarda Leylak, Beyaz Frenk Üzümü, Beyaz Şeftali, Pembe Biber ve Vanilya Özü; orta notalarda Vadi Zambağı, Portakal Çiçeği, Sardunya, Sümbülteber ve Süsen; alt notalarda Beyaz Misk, Ambergris, Abanoz, Paçuli ve Sandal Ağacı bulunur.</t>
+          <t>['tatlı', 'meyveli', 'aromatik', 'tropikal', 'taze', 'misk', 'vanilya', 'pudramsı', 'odunsu', 'sıcak baharatlı']</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Cassiopeaby Tiziana Terenzi, kadınlar ve erkekler için bir Chypre Floral parfümüdür. Cassiopea, 2015 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Paolo Terenzi'dir. Üst notalarda Çarkıfelek Meyvesi, Frenk Üzümü, Limon ve Eğreltiotu; orta notalarda Çay Gülü, Karanfil ve Vadi Zambağı; alt notalarda Tonka Fasulyesi, Misk ve Sandal Ağacı bulunur.</t>
         </is>
       </c>
     </row>
@@ -3761,22 +2847,10 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dehnal Oudh Cambodi No.1 Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>86</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>['ud', 'taze baharatlı']</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Dehnal Oudh Cambodi No.1byAl Haramain Perfumesis kadınlar ve erkekler için bir Amber kokusu.</t>
-        </is>
-      </c>
+          <t>['turunçgil', 'odunsu', 'ud', 'sıcak baharatlı', 'pudramsı', 'taze baharatlı', 'deri', 'aromatik', 'kehribar', 'misk']</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3791,18 +2865,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>XJ 1861 Decas Xerjofffor women and men</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>86</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>['kehribar', 'turunçgiller', 'vanilya', 'balzamik', 'tatlı', 'pudramsı', 'sümbülteber', 'tütün', 'beyaz çiçeksi', 'süsen']</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
+          <t>['tatlı', 'vanilya', 'bal', 'tütün', 'lavanta', 'turunçgil', 'aromatik', 'çiçeksi', 'sıcak baharatlı', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>XJ 1861 NaxosbyXerjoffis kadınlar ve erkekler için bir Citrus Gourmand kokusudur. XJ 1861 Naxos 2015 yılında piyasaya sürülmüştür. Üst notalarda Lavanta, Bergamot ve Limon; orta notalarda Bal, Tarçın, Kaşmir ve Yasemin Sambac; alt notalarda Tütün Yaprağı, Vanilya ve Tonka Fasulyesi bulunmaktadır.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3817,20 +2887,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Musk Al Haramain Perfumesfor women</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>86</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>['misk', 'çiçeksi', 'pudramsı', 'meyvemsi', 'yeşil', 'tatlı', 'aromatik', 'taze baharatlı']</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>MuskbyAl Haramain Perfumesis, kadınlara özel Amber Floral bir kokudur.</t>
+          <t>['turunçgil', 'misk', 'çiçeksi', 'pudramsı', 'meyvemsi', 'odunsu', 'yeşil', 'taze baharatlı', 'aromatik']</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Initio Parfums Privesis'in Musk Therapy'si kadınlar ve erkekler için odunsu çiçeksi bir misk kokusudur. Musk Therapy 2021 yılında piyasaya sürülmüştür.</t>
         </is>
       </c>
     </row>
@@ -3847,20 +2909,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cherry Flower Al-Rehabfor women and men</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>86</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>['çiçeksi', 'taze', 'misk', 'meyvemsi', 'pudramsı', 'aromatik', 'gül', 'su', 'turunçgil']</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Al-Rehabi Cherry Flower, kadınlar ve erkekler için çiçeksi yeşil bir koku. Üst notalarda Bergamot ve Frenk üzümü tomurcukları; orta notalarda Kiraz Çiçeği, Nilüfer ve Çay Gülü; alt notalarda Beyaz Misk, Süsen Kökü ve Vetiver bulunuyor.</t>
+          <t>['kiraz', 'odunsu', 'dumanlı', 'deri', 'tatlı', 'meyveli', 'fındıksı', 'badem', 'hayvansal', 'çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Cherry Smoke by Tom Ford, kadınlar ve erkekler için Amber Spicy bir kokudur. Bu yeni bir kokudur. Cherry Smoke, 2022 yılında piyasaya sürüldü. Üst notalarda Ekşi Kiraz ve Safran; orta notalarda Deri, Zeytin, Çin Osmanthus ve Kayısı; alt notalarda Duman, Odunsu Notalar ve Kıbrıs Yağı veya Nagarmotha bulunur.</t>
         </is>
       </c>
     </row>
@@ -3877,20 +2931,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Musk Black Vanilla Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>86</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>['kehribar', 'balzamik', 'dumanlı', 'sıcak baharatlı', 'meyvemsi', 'paçuli', 'vanilya', 'hafif baharatlı']</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Al Haramain Perfumesis'in Musk Black Vanilla parfümü, kadınlar ve erkekler için Amber Vanilya aromalı bir kokudur. Bu yeni bir parfümdür. Musk Black Vanilla 2023 yılında piyasaya sürüldü. Üst notalarda Siyah Frenk Üzümü, Bitkisel Notalar ve Sedir; orta notalarda Vanilya, Amber ve Baharatlar; alt notalarda Tütsü, Paçuli ve Misk bulunur.</t>
+          <t>['vanilya', 'badem', 'tatlı', 'fındıksı', 'pudramsı', 'meyveli', 'odunsu', 'çiçeksi', 'kehribar']</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Tom Ford'un Vanilla Sex'i, kadınlar ve erkekler için Amber Vanilya aromalı bir parfümdür. Bu yeni bir parfümdür. Vanilla Sex, 2023 yılında piyasaya sürülmüştür. Üst nota Acı Badem; orta notalar Vanilya ve Çiçeksi Notalar; alt notalar Vanilla Absolute, Ultravanil™, Tonka Fasulyesi ve Sandal Ağacı'dır.</t>
         </is>
       </c>
     </row>
@@ -3907,20 +2953,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portfolio Cupid's Rose Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>86</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>['odunsu', 'sıcak baharatlı', 'paçuli', 'gül', 'meyvemsi', 'tarçın', 'ud', 'tatlı', 'topraksı', 'balzamik']</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Portfolio Cupid's Rose by Al Haramain Perfumesis, kadınlar ve erkekler için Amber Floral bir kokudur. Portfolio Cupid's Rose, 2019 yılında piyasaya sürülmüştür. Üst notalarda Gül ve Bergamot; orta notalarda erik, Tarçın ve Sedir; alt notalarda Paçuli, Agarwood (Ud) ve Sandal Ağacı bulunmaktadır.</t>
+          <t>['odunsu', 'tatlı', 'sıcak baharatlı', 'vanilya', 'tarçın', 'pudramsı', 'kehribar']</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>By Kilian'ın Angels' Share Anniversary Edition'ı, kadınlar ve erkekler için Amber Vanilya aromalı bir koku. Bu yeni bir koku. Angels' Share Anniversary Edition, 2022'de piyasaya sürüldü. Bu kokunun arkasındaki isim Benoist Lapouza. Üst notalarda Konyak; orta notalarda Tarçın, Meşe ve Tonka Fasulyesi; alt notalarda Pralin, Vanilya ve Sandal Ağacı bulunuyor.</t>
         </is>
       </c>
     </row>
@@ -3937,20 +2975,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>J. Crew Homesteader’s Cologne DS&amp;Durgafor men</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>86</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>['odunsu', 'aromatik', 'kafur', 'bitkisel']</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>J. Crew Homesteader’ın DS&amp;Durga Cologne’u erkekler için Aromatik Fougere kokusudur. J. Crew Homesteader’ın Cologne’u 2013 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim David Seth Moltz’dur.</t>
+          <t>['taze baharatlı', 'sıcak baharatlı', 'gül', 'aromatik', 'misk', 'turunçgil', 'meyvemsi', 'pudramsı', 'çiçeksi', 'metalik']</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>FearlessbyOrmonde Jayne, kadınlar ve erkekler için Amber Floral bir kokudur. Bu yeni bir kokudur. Fearless, 2023 yılında piyasaya sürülmüştür. Üst notalarda Safran, Karabiber, Bergamot ve Siyah Frenk Üzümü; orta notalarda Gül, Sardunya ve Yasemin; alt notalarda Misk, Yosun, Paçuli ve Vanilya Çekirdeği bulunur.</t>
         </is>
       </c>
     </row>
@@ -3967,20 +2997,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Blue Sugar Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>86</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>['tatlı', 'vanilya', 'turunçgil', 'hindistan cevizi', 'laktonik']</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Blue Sugar by Al Haramain Perfumesis, kadınlar ve erkekler için çiçeksi meyveli gurme bir kokudur. Blue Sugar, 2016 yılında piyasaya sürülmüştür.</t>
+          <t>['turunçgil', 'meyvemsi', 'tatlı', 'misk', 'sıcak baharatlı', 'beyaz çiçeksi', 'odunsu', 'ud', 'pudramsı', 'taze']</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Ex Nihilo'nun Blue Talisman'ı, kadınlar ve erkekler için bir parfümdür. Bu yeni bir parfümdür. Blue Talisman, 2023 yılında piyasaya sürüldü. Üst notalarda Armut, Bergamot, Mandalina ve Zencefil; orta notalarda Portakal Çiçeği ve Georgywood; alt notalarda Ambrofix™, Misk ve Akigalawood bulunur.</t>
         </is>
       </c>
     </row>
@@ -3997,20 +3019,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Mod Noir Marc Jacobsfor women</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>86</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>['beyaz çiçeksi', 'yeşil', 'turunçgil', 'çiçeksi', 'tatlı', 'sümbülteber', 'hayvansal', 'laktik', 'taze', 'sucul']</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Marc Jacobs'un Mod Noir'i kadınlar için çiçeksi bir koku. Mod Noir, 2015 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Jean Claude Delville. Üst notalarda Yeşil Notalar, Yuzu ve Klementin; orta notalarda Gardenya, Nilüfer, Sümbülteber ve Manolya; alt notalarda Nektarin, Portakal Çiçeği ve Misk bulunuyor.</t>
+          <t>['sarı çiçeksi', 'tatlı', 'beyaz çiçeksi', 'pudramsı', 'çiçeksi', 'bal', 'vanilya', 'yeşil']</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Tiliaby Marc-Antoine Barrois, kadınlar ve erkekler için çiçeksi odunsu misk kokusudur. Bu yeni bir kokudur. Tilia 2024 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Quentin Bisch'tir.</t>
         </is>
       </c>
     </row>
@@ -4027,20 +3041,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Pas Ce Soir Extrait BDK Parfumsfor women and men</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>86</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'tatlı', 'sıcak baharatlı', 'kehribar', 'odunsu', 'beyaz çiçeksi', 'taze', 'turunçgil', 'misk', 'paçuli']</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>BDK Parfum'dan Pas Ce Soir Extrait, kadınlar ve erkekler için Amber Floral bir kokudur. Bu yeni bir kokudur. Pas Ce Soir Extrait, 2023 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Violaine Collas. Üst notalarda Armut, Zencefil, Mandalina, Kakao Kabuğu ve Karabiber; orta notalarda Ayva, Şeftali, Fas Yasemini ve Portakal Çiçeği; alt notalarda Endonezya Paçuli Yaprağı, Kaşmir, Ambroxan, Vanilya ve Benzoin bulunur.</t>
+          <t>['kehribar', 'vanilya']</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Maison Francis Kurkdjian Grand Soir, kadınlar ve erkekler için bir Amber kokusudur. Grand Soir, 2016 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki burun Francis Kurkdjian'dır.</t>
         </is>
       </c>
     </row>
@@ -4057,18 +3063,10 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Musk Al Ghazal Eau de Parfum Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>86</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
           <t>['misk', 'sıcak baharatlı', 'taze baharatlı', 'tatlı', 'anason', 'pudramsı', 'çikolata', 'hafif baharatlı', 'aromatik', 'vanilya']</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>Musk Al Ghazal Eau de ParfumbyAl Haramain Perfumesis, kadınlar ve erkekler için bir Amber kokusudur. Üst notalarda kimyon ve anason; orta notalarda misk; alt notalarda baharatlar, bitter çikolata, odunsu notalar ve vanilya bulunur.</t>
         </is>
@@ -4087,20 +3085,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bronze Tonka Carolina Herrerafor women and men</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>86</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>['sıcak baharatlı', 'odunsu', 'ud', 'kahve', 'topraksı', 'metalik', 'deri', 'pudramsı']</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Bronze TonkabyCarolina Herrera, kadınlar ve erkekler için Amber Baharatlı bir kokudur. Bronze Tonka, 2018 yılında piyasaya sürülmüştür. Üst notalarda Agarwood (Ud), Kahve ve Kıbrıs Yağı veya Nagarmotha; orta nota Tonka Fasulyesi; temel notalarda Safran ve Sandal Ağacı bulunur.</t>
+          <t>['tatlı', 'vanilya', 'kehribar', 'sıcak baharatlı', 'ud', 'gül', 'misk', 'metalik', 'aromatik', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Arabians TonkabyMontale, kadınlar ve erkekler için Amber Woody bir kokudur. Arabians Tonka, 2019 yılında piyasaya sürülmüştür. Üst notalarda Safran ve Bergamot; orta notalarda Agar Ağacı (Ud) ve Bulgar Gülü; alt notalarda Tonka Fasulyesi, Şeker Kamışı, Amber, Beyaz Misk ve Meşe Yosunu bulunur.</t>
         </is>
       </c>
     </row>
@@ -4117,20 +3107,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Eau de Voyage Louis Vuittonfor women and men</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>86</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Louis Vuitton'un Eau de Voyage parfümü, kadın ve erkeklere yönelik bir parfümdür. Eau de Voyage 1946 yılında piyasaya sürülmüştür.</t>
+          <t>['turunçgil', 'kehribar', 'taze', 'taze baharatlı', 'yeşil', 'sıcak baharatlı']</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Louis Vuitton'dan Imagination, erkekler için narenciye aromalı bir parfümdür. Imagination, 2021 yılında piyasaya sürüldü. Bu parfümün arkasındaki isim Jacques Cavallier. Üst notalarda limon, Calabria bergamotu ve Sicilya portakalı; orta notalarda Tunus portakalı, Nijerya zencefili ve Seylan tarçını; alt notalarda Çin siyah çayı, ambroxan, guaiac ağacı ve olibanum bulunur.</t>
         </is>
       </c>
     </row>
@@ -4147,18 +3129,10 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Guidance 46 Amouagefor women and men</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>86</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
           <t>['odunsu', 'kehribar', 'sıcak baharatlı', 'meyvemsi', 'çiçeksi', 'ud', 'tatlı', 'misk', 'gül', 'badem']</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>Guidance 46byAmouage, kadınlar ve erkekler için Amber Floral bir kokudur. Bu yeni bir kokudur. Guidance 46, 2024 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Quentin Bisch'tir. Üst notalarda Gül Suyu, Acı Badem, Armut, Tütsü, Pembe Biber ve Fındık; orta notalarda Gül, Osmanthus, Safran ve Yasemin Sambac; alt notalarda Akigala Ağacı, Sandal Ağacı, Ambrette, Georgywood, Vanilya, Laden, Ambergris ve Kıbrıs bulunur.</t>
         </is>
@@ -4177,20 +3151,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ego Panthera Armaffor women and men</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>61</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>['kehribar', 'hafif baharatlı', 'aromatik', 'deri', 'hayvansal']</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Ego PantherabyArmaf, kadınlar ve erkekler için Amber Woody bir kokudur. Bu yeni bir kokudur. Ego Panthera 2024 yılında piyasaya sürülmüştür. Üst notalarda Pembe Biber, Olibanum, Kakule ve Limon; orta notalarda Clary Sage ve Lavanta; alt notalarda Amber, Vetiver, Deri, Sandal Ağacı, Sedir Ağacı ve Ambroxan bulunur.</t>
+          <t>Bilgi Yok</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Bilgi Yok</t>
         </is>
       </c>
     </row>
@@ -4207,20 +3173,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Musk Black Vanilla Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>86</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>['kehribar', 'balzamik', 'dumanlı', 'sıcak baharatlı', 'meyvemsi', 'paçuli', 'vanilya', 'hafif baharatlı']</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Al Haramain Perfumesis'in Musk Black Vanilla parfümü, kadınlar ve erkekler için Amber Vanilya aromalı bir kokudur. Bu yeni bir parfümdür. Musk Black Vanilla 2023 yılında piyasaya sürüldü. Üst notalarda Siyah Frenk Üzümü, Bitkisel Notalar ve Sedir; orta notalarda Vanilya, Amber ve Baharatlar; alt notalarda Tütsü, Paçuli ve Misk bulunur.</t>
+          <t>['beyaz çiçeksi', 'vanilya', 'hindistan cevizi', 'tatlı', 'pudramsı', 'sümbülteber', 'laktonik', 'misk', 'çiçeksi', 'odunsu']</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Utopia Vanilla Coco 21, Kayali Fragrance tarafından kadınlar ve erkekler için Amber Vanilya aromalı bir kokudur. Utopia Vanilla Coco 21, 2021 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Gabriela Chelariu. Üst notalarda Hindistan Cevizi Sütü, Hanımeli, Armut Çiçeği ve İtalyan Limonu; orta notalarda Tuberose, Yasemin Sambac, Gardenya ve Ambrette (Misk Hatmi); alt notalarda Burbon Vanilya, Sandal Ağacı, Misk ve Paçuli yer alıyor.</t>
         </is>
       </c>
     </row>
@@ -4237,18 +3195,10 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Musk Al Ghazal Eau de Parfum Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>86</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
           <t>['misk', 'sıcak baharatlı', 'taze baharatlı', 'tatlı', 'anason', 'pudramsı', 'çikolata', 'hafif baharatlı', 'aromatik', 'vanilya']</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>Musk Al Ghazal Eau de ParfumbyAl Haramain Perfumesis, kadınlar ve erkekler için bir Amber kokusudur. Üst notalarda kimyon ve anason; orta notalarda misk; alt notalarda baharatlar, bitter çikolata, odunsu notalar ve vanilya bulunur.</t>
         </is>
@@ -4267,18 +3217,10 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Gingerbread Latte Bath &amp; Body Worksfor women</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>86</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
           <t>['tatlı', 'vanilya', 'laktonik', 'pudramsı', 'tarçın', 'odunsu', 'sıcak baharatlı', 'turunçgil']</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>Bath &amp; Body Works'ten Gingerbread Latte, kadınlar için çiçeksi meyveli bir gurme kokusudur. Gingerbread Latte, 2016 yılında piyasaya sürülmüştür. Üst notalarda Zencefilli Kurabiye, Portakal Kabuğu ve Armut Dondurması; orta notalarda Esmer Şeker, Vanilya ve Süt; alt notalarda Sandal Ağacı, Çırpılmış Krema ve Misk bulunmaktadır.</t>
         </is>
@@ -4297,18 +3239,10 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Naseej Al Oud Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>86</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
           <t>['ud', 'deri', 'odunsu', 'kehribar', 'hafif baharatlı', 'hayvansal', 'taze baharatlı', 'gül']</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>Naseej Al Oudby Afnani, kadınlar ve erkekler için bir Deri kokusudur. Naseej Al Oud, 2021 yılında piyasaya sürülmüştür. Üst notalarda Agarwood (Ud), Pembe Biber, Bergamot ve Safran; orta notalarda Odunsu Notalar, Gül, Yasemin ve Süsen; temel notalarda Agarwood (Ud), Deri ve Amber bulunmaktadır.</t>
         </is>
@@ -4327,20 +3261,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>California Bath Co. Pacific Heights Avonfor women</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>86</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>California Bath Co. Pacific HeightsbyAvon kadınlara yönelik bir parfümdür.</t>
+          <t>['turunçgil', 'meyvemsi', 'aromatik', 'yeşil', 'taze baharatlı', 'tatlı', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Pacific ChillbyLouis Vuitton, kadınlar ve erkekler için aromatik meyveli bir kokudur. Pacific Chill, 2023 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Jacques Cavallier. Üst notalarda turunç, portakal, nane, limon, siyah frenk üzümü ve kişniş; orta notalarda kayısı, fesleğen, havuç çekirdeği ve mayıs gülü; alt notalarda ise incir, hurma ve ambrette bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -4357,20 +3283,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Opus V – Woods Symphony Amouagefor women and men</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>86</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>['iris', 'odunsu', 'pudramsı', 'gül', 'ud', 'beyaz çiçeksi', 'rom', 'çiçeksi', 'topraksı', 'misk']</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Amouage'ın Opus V – Woods Symphony'si kadın ve erkeklere yönelik bir parfümdür. Opus V – Woods Symphony, 2011 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Jacques Cavallier'dir. Üst notalarda Süsen Kökü ve Rom; orta notalarda Süsen Kökü, Gül ve Yasemin; alt notalarda Öd Ağacı (Oud), Kuru Ağaç ve Misk Kedisi bulunur.</t>
+          <t>['turunçgil', 'taze baharatlı', 'sıcak baharatlı', 'aromatik']</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>SymphonybyLouis Vuitton, kadınlar ve erkekler için bir narenciye kokusudur. Symphony, 2021 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Jacques Cavallier'dir.</t>
         </is>
       </c>
     </row>
@@ -4387,20 +3305,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Midnight Swim Bath &amp; Body Worksfor women and men</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>86</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>['su', 'taze', 'bitkisel']</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Midnight Swimby Bath &amp; Body Works, kadınlar ve erkekler için bir parfümdür. Bu yeni bir parfümdür. Midnight Swim, 2023 yılında piyasaya sürüldü.</t>
+          <t>['turunçgil']</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Afternoon SwimbyLouis Vuitton, kadınlar ve erkekler için bir turunçgil kokusudur. Afternoon Swim, 2019 yılında piyasaya sürüldü. Bu kokunun arkasındaki burun Jacques Cavallier'dir.</t>
         </is>
       </c>
     </row>
@@ -4417,20 +3327,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>L'Aventure Al Haramain Perfumesfor men</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>86</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'aromatik', 'odunsu', 'misk', 'taze baharatlı', 'pudramsı', 'beyaz çiçeksi']</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>L'Aventure by Al Haramain Perfumesis erkekler için Chypre Fruity bir kokudur. L'Aventure 2016 yılında piyasaya sürülmüştür. Üst notalarda Limon, Bergamot ve elemi; orta notalarda Odunsu Notalar, Yasemin ve Vadi Zambağı; alt notalarda Misk, Paçuli ve Amber bulunmaktadır.</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Louis Vuitton'un Eau de Voyage parfümü, kadın ve erkeklere yönelik bir parfümdür. Eau de Voyage 1946 yılında piyasaya sürülmüştür.</t>
         </is>
       </c>
     </row>
@@ -4447,20 +3349,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Abaan Lattafa Perfumesfor women</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>86</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>['odunsu', 'turunçgil', 'beyaz çiçeksi', 'pudramsı', 'sıcak baharatlı', 'paçuli', 'misk', 'balzamik', 'tatlı', 'taze baharatlı']</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>AbaanbyLattafa Perfumesis, kadınlar için çiçeksi odunsu misk kokusudur. Abaan, 2022 yılında piyasaya sürülmüştür. Üst notalarda Bergamot ve Portakal; orta notalarda Yasemin ve Portakal Çiçeği; alt notalarda Sandal Ağacı, Paçuli ve Misk bulunmaktadır.</t>
+          <t>['tatlı', 'sıcak baharatlı', 'vanilya', 'kehribar', 'tarçın', 'odunsu', 'taze baharatlı', 'meyveli']</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>KhamrahbyLattafa Perfumesis, kadınlar ve erkekler için aromatik baharatlı bir kokudur. Bu yeni bir parfümdür. Khamrah, 2022 yılında piyasaya sürüldü. Üst notalarda Tarçın, Hindistan Cevizi ve Bergamot; orta notalarda Hurma, Pralin, Sümbülteber ve Mahonial; alt notalarda Vanilya, Tonka Fasulyesi, Amber Ağacı, Mür, Benzoin ve Akigala Ağacı bulunur.</t>
         </is>
       </c>
     </row>
@@ -4477,20 +3371,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Blush Intense Marc Jacobsfor women</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>86</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>['beyaz çiçeksi', 'misk', 'odunsu', 'pudramsı']</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Marc Jacobs'ın Blush Intense'i kadınlara yönelik çiçeksi bir kokudur. Blush Intense 2006 yılında piyasaya sürülmüştür. Orta notalarda Yasemin ve Portakal Çiçeği; temel notalarda Kaşmir Ağacı, Misk ve Sandal Ağacı bulunur.</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>MarcbyAl-Rehabi erkeklere yönelik bir parfüm.</t>
         </is>
       </c>
     </row>
@@ -4507,20 +3393,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Musk Black Vanilla Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>86</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>['kehribar', 'balzamik', 'dumanlı', 'sıcak baharatlı', 'meyvemsi', 'paçuli', 'vanilya', 'hafif baharatlı']</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Al Haramain Perfumesis'in Musk Black Vanilla parfümü, kadınlar ve erkekler için Amber Vanilya aromalı bir kokudur. Bu yeni bir parfümdür. Musk Black Vanilla 2023 yılında piyasaya sürüldü. Üst notalarda Siyah Frenk Üzümü, Bitkisel Notalar ve Sedir; orta notalarda Vanilya, Amber ve Baharatlar; alt notalarda Tütsü, Paçuli ve Misk bulunur.</t>
+          <t>['vanilya', 'pudramsı', 'tatlı']</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Vanilla BlendbyZielinski &amp; Rozenis kadınlar ve erkekler için Amber Vanilya kokusu.</t>
         </is>
       </c>
     </row>
@@ -4537,22 +3415,10 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Paris Amour Bath &amp; Body Worksfor women</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>86</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>['çiçeksi', 'meyveli', 'tatlı', 'vanilya', 'pudramsı', 'turunçgil', 'Şampanya', 'hafif baharatlı', 'tropikal']</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Paris Amourby Bath &amp; Body Works, kadınlar için çiçeksi ve meyveli bir kokudur. Üst notalarda büyük çilek, şampanya, elma çiçeği, frezya, frenk üzümü ve mandalina; orta notalarda pembe lale, frangipani, şeftali, yasemin ve nilüfer; alt notalarda vanilya, misk, hindistan cevizi, amber ve sandal ağacı bulunur.</t>
-        </is>
-      </c>
+          <t>['kehribar', 'çiçeksi', 'meyvemsi', 'misk', 'turunçgil', 'ud', 'odunsu', 'lavanta', 'laktonik', 'hafif baharatlı']</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4567,20 +3433,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>United Colors of Benetton Unisex Benettonfor women and men</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>86</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'odunsu', 'pudramsı', 'taze baharatlı', 'çiçeksi', 'aromatik', 'beyaz çiçeksi', 'misk']</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>United Colors of Benetton UnisexbyBenetto, kadınlar ve erkekler için çiçeksi odunsu misk kokusudur. United Colors of Benetton Unisex, 2006 yılında piyasaya sürülmüştür. Üst notalarda Bergamot ve Portakal Çiçeği; orta notalarda Bambu ve Pamuk Çiçeği; alt notalarda Guaiac Ağacı ve Beyaz Misk bulunmaktadır.</t>
+          <t>['kehribar', 'deri', 'hayvansal', 'misk']</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Jump up and Kiss Me Hedonistic by Clive Christian, erkekler için bir Amber kokusudur.Jump up and Kiss Me Hedonistic, 2017 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Julie Pluchet'dir.</t>
         </is>
       </c>
     </row>
@@ -4597,20 +3455,12 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>United Colors of Benetton Unisex Benettonfor women and men</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>86</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'odunsu', 'pudramsı', 'taze baharatlı', 'çiçeksi', 'aromatik', 'beyaz çiçeksi', 'misk']</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>United Colors of Benetton UnisexbyBenetto, kadınlar ve erkekler için çiçeksi odunsu misk kokusudur. United Colors of Benetton Unisex, 2006 yılında piyasaya sürülmüştür. Üst notalarda Bergamot ve Portakal Çiçeği; orta notalarda Bambu ve Pamuk Çiçeği; alt notalarda Guaiac Ağacı ve Beyaz Misk bulunmaktadır.</t>
+          <t>['misk', 'çiçeksi', 'meyvemsi', 'turunçgil', 'beyaz çiçeksi', 'odunsu', 'pudramsı', 'kehribar', 'sıcak baharatlı', 'aromatik']</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>UnisexbyLia Ruy, kadınlar ve erkekler için odunsu ve çiçeksi bir misk kokusudur. Unisex, 2019 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Julia Kupriyanova'dır. Üst notalarda Osmanthus ve Amalfi Limonu; orta notalarda Beyaz Çiçekler, Sedir, Olibanum ve Gül; alt notalarda Beyaz Misk ve Safran bulunur.</t>
         </is>
       </c>
     </row>
@@ -4627,20 +3477,12 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sweet Diamond Pink Pepper 25 Kayali Fragrancesfor women and men</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>86</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>['gül', 'sıcak baharatlı', 'hafif baharatlı', 'çiçeksi', 'misk', 'odunsu', 'pudramsı', 'kehribar', 'tatlı', 'metalik']</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Sweet Diamond Pink Pepper 25 by Kayali Fragrance, kadınlar ve erkekler için Amber Floral bir kokudur. Sweet Diamond Pink Pepper 25, 2021 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Gabriela Chelariu. Üst notalarda Pembe Biber, Safran, Bergamot ve Kraliyet Zambağı; orta notalarda Bulgar Gülü, Mayıs Gülü, Vanilya Orkidesi ve Manolya; alt notalarda ise Amber, Sandal Ağacı, Paçuli ve Misk bulunuyor.</t>
+          <t>['tatlı', 'pudramsı', 'vanilya', 'beyaz çiçeksi', 'meyvemsi']</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Bath &amp; Body Works'ün Hope Winter Peach Marshmallow'u kadınlara yönelik çiçeksi ve meyveli bir kokudur. Hope Winter Peach Marshmallow 2021 yılında piyasaya sürülmüştür.</t>
         </is>
       </c>
     </row>
@@ -4657,22 +3499,10 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Déjà Vu White Flower 57 Kayali Fragrancesfor women and men</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>86</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>['beyaz çiçeksi', 'tatlı', 'sümbülteber', 'odunsu', 'vanilya', 'meyveli', 'pudramsı', 'hayvansal']</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Déjà Vu White Flower 57, Kayali Fragrance tarafından kadınlar ve erkekler için Amber Floral bir kokudur. Déjà Vu White Flower 57, 2020 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Gabriela Chelariu. Üst notalarda Nektarin, Gardenya ve Armut; orta notalarda Sümbülteber, Hint Yasemini ve Portakal Çiçeği; alt notalarda Tahiti Vanilyası, Paçuli, Kaşmir Ağacı ve Sandal Ağacı bulunmaktadır.</t>
-        </is>
-      </c>
+          <t>['tatlı', 'odunsu', 'vanilya', 'fındıksı', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4687,22 +3517,10 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Déjà Vu White Flower 57 Kayali Fragrancesfor women and men</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>86</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>['beyaz çiçeksi', 'tatlı', 'sümbülteber', 'odunsu', 'vanilya', 'meyveli', 'pudramsı', 'hayvansal']</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Déjà Vu White Flower 57, Kayali Fragrance tarafından kadınlar ve erkekler için Amber Floral bir kokudur. Déjà Vu White Flower 57, 2020 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Gabriela Chelariu. Üst notalarda Nektarin, Gardenya ve Armut; orta notalarda Sümbülteber, Hint Yasemini ve Portakal Çiçeği; alt notalarda Tahiti Vanilyası, Paçuli, Kaşmir Ağacı ve Sandal Ağacı bulunmaktadır.</t>
-        </is>
-      </c>
+          <t>['tatlı', 'odunsu', 'vanilya', 'fındıksı', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4717,18 +3535,10 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>125th &amp; Bloom Vilhelm Parfumeriefor women and men</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>86</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
           <t>['deri', 'sıcak baharatlı', 'odunsu', 'gül', 'hayvansal', 'metalik', 'pudramsı', 'çiçeksi', 'menekşe', 'dumanlı']</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>125th &amp; BloombyVilhelm Parfumerie, kadın ve erkeklere yönelik bir parfümdür. 125th &amp; Bloom, 2020'li yıllarda piyasaya sürülmüştür. Üst notalarda Safran ve Melekotu; orta notalarda Gül ve Menekşe; alt notalarda Deri ve Abanoz bulunmaktadır.</t>
         </is>
@@ -4747,20 +3557,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Amber Oud Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>86</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>['kehribar', 'odunsu', 'aromatik', 'turunçgil', 'taze baharatlı', 'pudramsı', 'misk', 'sıcak baharatlı', 'balzamik']</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Amber OudbyAl Haramain Perfumesi, kadınlar ve erkekler için Amber Woody bir kokudur. Amber Oud, 2018 yılında piyasaya sürüldü. Üst notalarda Biberiye, Bergamot, Sedir ve Limon; orta notalarda Baharatlar, Sedir ve Guaiac Ağacı; temel notalarda Reçineler, Amber ve Misk bulunmaktadır.</t>
+          <t>['sıcak baharatlı', 'kehribar', 'odunsu', 'beyaz çiçeksi', 'tatlı', 'vanilya', 'meyveli', 'aromatik', 'turunçgil', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Clive Christian'ın Blonde Amber'ı, kadınlar ve erkekler için bir Amber kokusu. Bu yeni bir koku. Blonde Amber, 2022'de piyasaya sürüldü. Bu kokunun arkasındaki isim Vincent Ricord. Üst notalarda Rom, Olibanum, Acı Portakal, Kakule, Pembe Biber, Zencefil, Bergamot ve Greyfurt; orta notalarda Kuru Meyveler, Beyaz Tütün, Sandal Ağacı, Sümbülteber, Safran, Osmanthus, Süsen ve Yasemin; alt notalarda Tonka Fasulyesi, Mür, Vanilya, Laden, Paçuli, Misk, Sedir ve Vetiver bulunuyor.</t>
         </is>
       </c>
     </row>
@@ -4777,18 +3579,10 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Musk Black Vanilla Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>86</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
           <t>['kehribar', 'balzamik', 'dumanlı', 'sıcak baharatlı', 'meyvemsi', 'paçuli', 'vanilya', 'hafif baharatlı']</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>Al Haramain Perfumesis'in Musk Black Vanilla parfümü, kadınlar ve erkekler için Amber Vanilya aromalı bir kokudur. Bu yeni bir parfümdür. Musk Black Vanilla 2023 yılında piyasaya sürüldü. Üst notalarda Siyah Frenk Üzümü, Bitkisel Notalar ve Sedir; orta notalarda Vanilya, Amber ve Baharatlar; alt notalarda Tütsü, Paçuli ve Misk bulunur.</t>
         </is>
@@ -4807,20 +3601,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>P.S. I Love You Bath &amp; Body Worksfor women</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>86</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>['gül', 'çiçeksi', 'kehribar', 'taze', 'dumanlı', 'sıcak baharatlı', 'odunsu', 'balzamik', 'beyaz çiçeksi', 'pudramsı']</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Bath &amp; Body Works'ün P.S. I Love You'su, kadınlar için Amber Floral bir kokudur. P.S. I Love You, 2009 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim David Apel'dir. Üst notalarda Şakayık, Litchi ve Turunçgiller; orta notalarda Gül, Tütsü, Yasemin, Zambak ve Orkide; alt notalarda Misk, Paçuli, Sandal Ağacı ve Amber bulunur.</t>
+          <t>['misk', 'turunçgil', 'taze', 'beyaz çiçeksi', 'aldehitli', 'pudramsı', 'kehribar', 'odunsu', 'meyvemsi', 'çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ValayabyParfums de Marly, kadınlar için çiçeksi ve meyveli bir koku. Bu yeni bir parfüm. Valaya 2023 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Quentin Bisch. Üst notalarda Aldehitler, Beyaz Şeftali, Bergamot ve Mandalina; orta notalarda Portakal Çiçeği, Petalia, Vadi Zambağı, Vetiver, Nympheal™ ve Mahonia; alt notalarda Misk, Ambroxan, Akigala Ağacı ve Vanilya bulunuyor.</t>
         </is>
       </c>
     </row>
@@ -4837,20 +3623,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Expressions by Reese Witherspoon: Laugh Often Avonfor women</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>86</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'taze', 'yeşil', 'çiçeksi', 'gül']</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Reese Witherspoon'un İfadeleri: Laugh Often, Avoni tarafından üretilen, kadınlar için bir narenciye kokusudur. Reese Witherspoon'un İfadeleri: Laugh Often, 2011 yılında piyasaya sürülmüştür. Üst notalarda narenciye, çay ve mandalina; orta notalarda frezya ve gül; alt notalarda misk bulunmaktadır.</t>
+          <t>['aromatik', 'kehribar', 'aldehitli', 'taze', 'sıcak baharatlı', 'votka', 'yeşil', 'misk', 'yosunlu', 'hafif baharatlı']</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Vodka on the Rocksby, kadınlar ve erkekler için aromatik bir kokudur. Vodka on the Rocks, 2014 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Sidonie Lancesseur. Üst notalarda kişniş, aldehitler ve kakule; orta notalarda ravent, müge ve pembe gül; alt notalarda ambroxan, meşe yosunu ve sandal ağacı bulunur.</t>
         </is>
       </c>
     </row>
@@ -4867,18 +3645,10 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Guidance 46 Amouagefor women and men</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>86</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
           <t>['odunsu', 'kehribar', 'sıcak baharatlı', 'meyvemsi', 'çiçeksi', 'ud', 'tatlı', 'misk', 'gül', 'badem']</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>Guidance 46byAmouage, kadınlar ve erkekler için Amber Floral bir kokudur. Bu yeni bir kokudur. Guidance 46, 2024 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Quentin Bisch'tir. Üst notalarda Gül Suyu, Acı Badem, Armut, Tütsü, Pembe Biber ve Fındık; orta notalarda Gül, Osmanthus, Safran ve Yasemin Sambac; alt notalarda Akigala Ağacı, Sandal Ağacı, Ambrette, Georgywood, Vanilya, Laden, Ambergris ve Kıbrıs bulunur.</t>
         </is>
@@ -4897,20 +3667,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Tom of Finland Etat Libre d'Orangefor men</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>86</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>['deri', 'odunsu', 'pudramsı', 'aromatik', 'misk', 'vanilya', 'kehribar', 'aldehitli', 'iris', 'dumanlı']</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Etat Libre d'Orange'ın Tom of Finland'ı, erkekler için odunsu aromatik bir kokudur. Tom of Finland, 2007 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Antoine Lie'dir. Üst notalarda Aldehitler ve Amalfi Limonu; orta notalarda Huş Ağacı, Çam Ağacı, Selvi, Biber, Sardunya ve Galbanum; alt notalarda Süet, Vanilya, Süsen, Tonka Fasulyesi, Misk, Vetiver, Styrax ve Ambergris bulunur.</t>
+          <t>['turunçgil', 'sıcak baharatlı', 'odunsu', 'taze baharatlı', 'aromatik', 'tütün', 'topraksı', 'kehribar', 'taze', 'tatlı']</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Tom Ford for Men, erkekler için odunsu ve çiçeksi bir misk kokusudur. Tom Ford for Men, 2007 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Yves Cassar'dır. Üst notalarda Limon Yaprağı Yağı, Zencefil, Mandalina, Bergamot, Fesleğen ve Menekşe Yaprağı; orta notalarda Tütün Yaprağı, Biber, Tunus Portakal Çiçeği ve Greyfurt Çiçeği; alt notalarda Kehribar, Sedir, Vetiver, Virginia Paçulisi, Meşe Yosunu, Deri ve Kıbrıs Yağı veya Nagarmotha bulunur.</t>
         </is>
       </c>
     </row>
@@ -4927,18 +3689,10 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Clinique Happy Cliniquefor women</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>90</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
           <t>['turunçgil', 'çiçeksi', 'beyaz çiçeksi', 'tatlı', 'taze baharatlı', 'yeşil']</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>Clinique HappybyClinique, kadınlar için çiçeksi ve meyveli bir kokudur. Clinique Happy, 1998 yılında piyasaya sürülmüştür. Clinique Happy, Jean Claude Delville ve Rodrigo Flores-Roux tarafından yaratılmıştır. Üst notalarda Portakal, Kan Greyfurtu, Hint Mandalinası, Bergamot, Elma ve Erik; orta notalarda Vadi Zambağı, Frezya, Orkide ve Gül; alt notalarda Mimoza, Zambak, Manolya, Misk ve Amber bulunur.</t>
         </is>
@@ -4957,20 +3711,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Blue Sugar Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>86</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>['tatlı', 'vanilya', 'turunçgil', 'hindistan cevizi', 'laktonik']</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Blue Sugar by Al Haramain Perfumesis, kadınlar ve erkekler için çiçeksi meyveli gurme bir kokudur. Blue Sugar, 2016 yılında piyasaya sürülmüştür.</t>
+          <t>['pudramsı', 'vanilya', 'turunçgil', 'beyaz çiçeksi', 'odunsu', 'sümbülteber', 'misk', 'çiçeksi', 'badem', 'kehribar']</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Katarina Light BluebyArmafis, kadınlar için çiçeksi odunsu misk kokusudur. Üst notalarda mandalina, portakal ve bergamot; orta notalarda güneş çiçeği, sümbülteber ve yasemin; alt notalarda kaşmir ve vanilya bulunur.</t>
         </is>
       </c>
     </row>
@@ -4987,20 +3733,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>A One Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>86</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>['çiçekli', 'yeşil']</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>OnebyAl Haramain Perfumesis, kadınlara ve erkeklere yönelik bir parfümdür.</t>
+          <t>['meyvemsi', 'beyaz çiçeksi', 'tatlı', 'vanilya', 'kehribar', 'taze', 'ekşi', 'aromatik', 'çiçeksi', 'sıcak baharatlı']</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Sweet Honesty The OnebyAvon, kadınlar için çiçeksi bir kokudur. Bu yeni bir kokudur. Sweet Honesty The One, 2022 yılında piyasaya sürüldü. Üst notasında kırmızı meyveler; orta notasında yasemin sambac; alt notasında tonka fasulyesi bulunur.</t>
         </is>
       </c>
     </row>
@@ -5017,20 +3755,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Dehnal Oudh Cambodi No.1 Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>86</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>['ud', 'taze baharatlı']</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Dehnal Oudh Cambodi No.1byAl Haramain Perfumesis kadınlar ve erkekler için bir Amber kokusu.</t>
+          <t>['aromatik', 'turunçgil', 'odunsu', 'taze baharatlı', 'sıcak baharatlı', 'taze', 'lavanta']</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>K by Dolce &amp; GabbanabyDolce&amp;Gabbana, erkekler için odunsu aromatik bir kokudur. K by Dolce &amp; Gabbana, 2019 yılında piyasaya sürülmüştür. K by Dolce &amp; Gabbana, Daphné Bugey ve Nathalie Lorson tarafından yaratılmıştır. Üst notalarda ardıç meyvesi, turunçgiller, kan portakalı ve Sicilya limonu; orta notalarda yenibahar, lavanta, misk adaçayı ve sardunya; alt notalarda ise vetiver, sedir ve paçuli bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -5047,20 +3777,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>The One Dolce&amp;Gabbanafor women</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>90</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'beyaz çiçeksi', 'vanilya', 'pudramsı', 'tatlı', 'kehribar', 'turunçgil', 'taze', 'misk', 'hafif baharatlı']</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>OnebyDolce&amp;Gabbana, kadınlar için Amber Floral bir kokudur. One, 2006 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Christine Nagel'dır. Üst notalarda Şeftali, Litchi, Mandalina ve Bergamot; orta notalarda Zambak, Erik, Yasemin ve Vadi Zambağı; alt notalarda Vanilya, Amber, Misk ve Vetiver bulunur.</t>
+          <t>['meyvemsi', 'beyaz çiçeksi', 'tatlı', 'vanilya', 'kehribar', 'taze', 'ekşi', 'aromatik', 'çiçeksi', 'sıcak baharatlı']</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Sweet Honesty The OnebyAvon, kadınlar için çiçeksi bir kokudur. Bu yeni bir kokudur. Sweet Honesty The One, 2022 yılında piyasaya sürüldü. Üst notasında kırmızı meyveler; orta notasında yasemin sambac; alt notasında tonka fasulyesi bulunur.</t>
         </is>
       </c>
     </row>
@@ -5077,20 +3799,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Light Blue Dolce&amp;Gabbanafor women</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>90</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'odunsu', 'taze', 'meyvemsi', 'aromatik', 'misk', 'pudramsı', 'yeşil']</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Dolce&amp;Gabbana'nın Light Blue'su kadınlar için çiçeksi ve meyveli bir kokudur. Light Blue, 2001 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Olivier Cresp'tir. Üst notalarda Sicilya Limonu, Elma, Sedir ve Çan Çiçeği; orta notalarda Bambu, Yasemin ve Beyaz Gül; alt notalarda Sedir, Misk ve Amber bulunur.</t>
+          <t>['pudramsı', 'vanilya', 'turunçgil', 'beyaz çiçeksi', 'odunsu', 'sümbülteber', 'misk', 'çiçeksi', 'badem', 'kehribar']</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Katarina Light BluebyArmafis, kadınlar için çiçeksi odunsu misk kokusudur. Üst notalarda mandalina, portakal ve bergamot; orta notalarda güneş çiçeği, sümbülteber ve yasemin; alt notalarda kaşmir ve vanilya bulunur.</t>
         </is>
       </c>
     </row>
@@ -5107,20 +3821,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>9am Afnanfor women</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>86</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'misk', 'odunsu', 'aromatik', 'sıcak baharatlı', 'lavanta', 'yosunlu', 'meyveli', 'topraksı', 'beyaz çiçeksi']</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>9ambyAfnani kadınlara özel bir parfüm. Üst notalarda Limon, Mandalina, Kakule ve Pembe Biber; orta notalarda Lavanta, Yeşil Elma, Portakal Çiçeği ve Gül; alt notalarda Misk, Yosun, Sedir ve Paçuli bulunuyor.</t>
+          <t>['beyaz çiçeksi', 'vanilya', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Valentino Donna Born in Roma Green Stravaganza, kadınlara yönelik bir parfümdür. Bu yeni bir parfümdür. Valentino Donna Born in Roma Green Stravaganza, 2024 yılında piyasaya sürüldü. Üst notasında Lapsang Souchong Çayı; orta notasında Yasemin; alt notasında Vanilya bulunur.</t>
         </is>
       </c>
     </row>
@@ -5137,20 +3843,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Acqua Fiorentina The Encore Creedfor women</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>86</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'meyvemsi', 'aromatik', 'taze baharatlı', 'odunsu', 'yeşil', 'taze', 'çiçeksi', 'tatlı']</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Acqua Fiorentina The Encoreby Creed, kadınlar için çiçeksi ve meyveli bir kokudur. Acqua Fiorentina The Encore, 2012 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Olivier Creed'dir. Üst notalarda elma, erik, erik ve prunela; orta notalarda bergamot, limon, gül, karanfil ve armut; alt notalarda greyfurt, sandal ağacı ve sedir bulunur.</t>
+          <t>['turunçgil', 'aromatik', 'deniz', 'taze baharatlı', 'çiçeksi', 'odunsu', 'taze']</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Acqua di Gioby Giorgio Armanis, erkekler için aromatik bir su kokusudur. Üst notalarda limon, bergamot, yasemin, portakal, mandalina ve portakal çiçeği esansı; orta notalarda deniz notaları, yasemin, kalon, biberiye, şeftali, frezya, sümbül, siklamen, menekşe, kişniş, gül, hindistan cevizi ve mignonette; alt notalarda beyaz misk, sedir, meşe yosunu, paçuli ve amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -5167,20 +3865,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Black Oudh Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>86</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>['odunsu', 'pudramsı', 'misk', 'kehribar', 'paçuli', 'vanilya', 'yeşil', 'sıcak baharatlı', 'balzamik', 'hayvansal']</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Black OudhbyAl Haramain Perfumesis, kadınlar ve erkekler için Amber-Woody bir kokudur. Üst notalarda Misk; orta notalarda Sedir ve Bitkisel Notalar; alt notalarda Amber, Paçuli ve Vanilya bulunur.</t>
+          <t>['turunçgil', 'deri', 'anason', 'hafif baharatlı', 'çiçeksi', 'tütün', 'tatlı', 'aromatik', 'vanilya', 'hayvansal']</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Armani CodebyGiorgio Armani, erkekler için Amber Spicy bir kokudur. Armani Code, 2004 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Antoine Lie'dir. Üst notalarda Limon ve Bergamot; orta notalarda Yıldız Anason, Zeytin Çiçeği ve Guaiac Ağacı; alt notalarda Deri, Tonka Fasulyesi ve Tütün bulunur. Bu parfüm, 2006 Yılın Parfümü Erkek Lüks Ödülü'nü kazanmıştır.</t>
         </is>
       </c>
     </row>
@@ -5197,20 +3887,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Musk Al Ghazal Eau de Parfum Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>86</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>['misk', 'sıcak baharatlı', 'taze baharatlı', 'tatlı', 'anason', 'pudramsı', 'çikolata', 'hafif baharatlı', 'aromatik', 'vanilya']</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Musk Al Ghazal Eau de ParfumbyAl Haramain Perfumesis, kadınlar ve erkekler için bir Amber kokusudur. Üst notalarda kimyon ve anason; orta notalarda misk; alt notalarda baharatlar, bitter çikolata, odunsu notalar ve vanilya bulunur.</t>
+          <t>['vanilya', 'turunçgil', 'aromatik', 'misk', 'pudramsı', 'lavanta', 'tatlı', 'deri', 'kehribar', 'taze baharatlı']</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Armani Code Eau de Parfum by Giorgio Armani, erkekler için bir Amber Fougere kokusudur. Armani Code Eau de Parfum, 2021 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Antoine Maisondieu'dur. Üst notalarda Lavanta, Limon ve Bergamot; orta notalarda Tonka Fasulyesi; alt notalarda Vanilya, Süet, Misk ve Sedir bulunur.</t>
         </is>
       </c>
     </row>
@@ -5227,20 +3909,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Acqua di Gio Giorgio Armanifor women</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>86</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>['çiçeksi', 'taze', 'beyaz çiçeksi', 'yeşil', 'gül', 'meyveli', 'tatlı', 'pudramsı', 'odunsu', 'votka']</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Acqua di GiobyGiorgio Armani, kadınlar için çiçeksi ve meyveli bir kokudur. Acqua di Gioby, 1995 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Edouard Fléchier'dir. Üst notalarda Şakayık, Misk Votkası, Ananas, Limon, Şeftali, Muz Yaprağı ve Menekşe; orta notalarda Vadi Zambağı, Zambak, Hiacynth, Yasemin, Frezya, Calone, Ylang-Ylang ve Gül; alt notalarda Misk, Sedir, Sandal Ağacı, Amber ve Styrax bulunur.</t>
+          <t>['yeşil', 'aromatik', 'odunsu', 'balzamik', 'kehribar', 'yosunlu', 'çiçeksi', 'tatlı', 'beyaz çiçeksi', 'topraksı']</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ArmanibyGiorgio Armani, kadınlar için bir Chypre Floral parfümüdür. Armani, 1981 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Ron Winnegrad'dır. Üst notalarda Galbanum, Kadife Çiçeği, Aldehitler, Ananas, Bergamot ve Nane; orta notalarda Nergis, Süsen Kökü, Sümbülteber, Gül, Yasemin, Siklamen, Vadi Zambağı ve Orkide; alt notalarda Meşe Yosunu, Benzoin, Sedir, Kehribar, Sandal Ağacı, Tonka Fasulyesi ve Misk bulunur.</t>
         </is>
       </c>
     </row>
@@ -5257,20 +3931,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Naseej Al Kiswah Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>86</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>['odunsu', 'kehribar', 'deri', 'ud', 'paçuli', 'hayvansal', 'vanilya', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Naseej Al KiswahbyAfnani, Kadınlar ve Erkekler için Amber Woody Kokusudur. orta notalarda Woodsy Notes ve Sedir; temel notalar Amber, Deri ve Agarwood'dur (Ud).</t>
+          <t>['turunçgil', 'deri', 'anason', 'hafif baharatlı', 'çiçeksi', 'tütün', 'tatlı', 'aromatik', 'vanilya', 'hayvansal']</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Armani CodebyGiorgio Armani, erkekler için Amber Spicy bir kokudur. Armani Code, 2004 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Antoine Lie'dir. Üst notalarda Limon ve Bergamot; orta notalarda Yıldız Anason, Zeytin Çiçeği ve Guaiac Ağacı; alt notalarda Deri, Tonka Fasulyesi ve Tütün bulunur. Bu parfüm, 2006 Yılın Parfümü Erkek Lüks Ödülü'nü kazanmıştır.</t>
         </is>
       </c>
     </row>
@@ -5287,20 +3953,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Brown Sugar &amp; Fig Bath &amp; Body Worksfor women</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>86</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>['tatlı', 'meyveli', 'odunsu', 'vanilya', 'karamel', 'hindistan cevizi', 'pudramsı', 'yeşil', 'taze', 'laktik']</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Brown Sugar &amp; Figby Bath &amp; Body Works, kadınlar için çiçeksi ve meyveli bir gurme kokusudur. Üst notalarda Kaliforniya İnciri, Çarkıfelek Meyvesi, Beyaz Çiçekler, Beyaz Şeftali ve Bergamot; orta notalarda Hindistan Cevizi Sütü, Vanilya Orkidesi, Yasemin, Sarı Frezya ve Vadi Zambağı; alt notalarda Karamel, Vanilya Baklası, Akçaağaç, İncir Yaprağı, Amber ve Misk bulunur.</t>
+          <t>['taze baharatlı', 'turunçgil', 'aromatik', 'odunsu', 'sıcak baharatlı', 'lavanta', 'bitkisel']</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Givenchy pour Homme Blue Label, erkekler için odunsu ve baharatlı bir kokudur. Givenchy pour Homme Blue Label, 2004 yılında piyasaya sürülmüştür. Givenchy pour Homme Blue Label, Alberto Morillas ve Ilias Ermenidis tarafından yaratılmıştır. Üst notalarda greyfurt ve bergamot; orta notalarda biber, lavanta, kakule ve artemisia; alt notalarda sedir, vetiver ve olibanum bulunur.</t>
         </is>
       </c>
     </row>
@@ -5317,20 +3975,12 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Blue Sugar Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>86</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>['tatlı', 'vanilya', 'turunçgil', 'hindistan cevizi', 'laktonik']</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Blue Sugar by Al Haramain Perfumesis, kadınlar ve erkekler için çiçeksi meyveli gurme bir kokudur. Blue Sugar, 2016 yılında piyasaya sürülmüştür.</t>
+          <t>['taze baharatlı', 'turunçgil', 'aromatik', 'odunsu', 'sıcak baharatlı', 'lavanta', 'bitkisel']</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Givenchy pour Homme Blue Label, erkekler için odunsu ve baharatlı bir kokudur. Givenchy pour Homme Blue Label, 2004 yılında piyasaya sürülmüştür. Givenchy pour Homme Blue Label, Alberto Morillas ve Ilias Ermenidis tarafından yaratılmıştır. Üst notalarda greyfurt ve bergamot; orta notalarda biber, lavanta, kakule ve artemisia; alt notalarda sedir, vetiver ve olibanum bulunur.</t>
         </is>
       </c>
     </row>
@@ -5347,20 +3997,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Secret Wonderland Bath &amp; Body Worksfor women</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>86</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'tatlı', 'pudramsı', 'vanilya', 'beyaz çiçeksi', 'kehribar', 'misk']</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Bath &amp; Body Works'ün Secret Wonderland'i kadınlar için çiçeksi ve meyveli bir kokudur. Secret Wonderland 2010 yılında piyasaya sürülmüştür. Üst notalarda büyük çilek, ahududu ve kırmızı meyveler; orta notalarda yasemin, gardenya ve şeftali; alt notalarda vanilya, amber, misk ve sandal ağacı bulunur.</t>
+          <t>['taze', 'çiçeksi', 'turunçgil', 'meyvemsi', 'yeşil', 'beyaz çiçeksi', 'odunsu', 'taze baharatlı', 'gül', 'paçuli']</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Ange Ou Demon Le SecretbyGivench, kadınlar için çiçeksi bir kokudur. Ange Ou Demon Le Secret, 2009 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki burun Bernard Ellena'dır. Üst notalarda Çay, Kızılcık ve Amalfi Limonu; orta notalarda Şakayık, Yasemin ve Nilüfer; alt notalarda Odunsu Notalar ve Paçuli bulunur.</t>
         </is>
       </c>
     </row>
@@ -5377,20 +4019,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Musk Al Ghazal Eau de Parfum Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>86</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>['misk', 'sıcak baharatlı', 'taze baharatlı', 'tatlı', 'anason', 'pudramsı', 'çikolata', 'hafif baharatlı', 'aromatik', 'vanilya']</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Musk Al Ghazal Eau de ParfumbyAl Haramain Perfumesis, kadınlar ve erkekler için bir Amber kokusudur. Üst notalarda kimyon ve anason; orta notalarda misk; alt notalarda baharatlar, bitter çikolata, odunsu notalar ve vanilya bulunur.</t>
+          <t>['çiçeksi', 'turunçgil', 'taze', 'gül', 'meyvemsi', 'odunsu', 'hafif baharatlı', 'paçuli', 'sıcak baharatlı']</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Gucci Flora Eau de Parfum Gucci tarafından üretilen kadınlar için çiçeksi bir kokudur. Gucci Flora Eau de Parfum 2010 yılında piyasaya sürülmüştür. Üst notalarda Şakayık, Turunçgiller ve Mandalina; orta notalarda Osmanthus ve Gül; alt notalarda Sandal Ağacı, Pembe Biber ve Paçuli bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -5407,20 +4041,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Naturals Delicate Lily &amp; Gardenia Avonfor women</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>86</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>['beyaz çiçekli']</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Naturals Delicate Lily &amp; Gardenia by Avoni, kadınlara yönelik çiçeksi bir kokudur. Naturals Delicate Lily &amp; Gardenia, 2019 yılında piyasaya sürülmüştür.</t>
+          <t>['meyvemsi', 'beyaz çiçeksi', 'tatlı', 'laktik', 'taze', 'çiçeksi', 'tropikal', 'su', 'paçuli']</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Gucci'nin Flora Gorgeous Gardenia'sı, kadınlar için çiçeksi ve meyveli bir kokudur. Gucci'nin Flora Gorgeous Gardenia'sı 2012 yılında piyasaya sürülmüştür. Üst notalarda Armut ve Kırmızı Meyveler; orta notalarda Gardenya ve Frangipani; temel notalarda Paçuli bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -5437,20 +4063,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Azzaro Pour Homme Édition Noire Azzarofor men</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>86</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>['aromatik', 'taze baharatlı', 'odunsu', 'turunçgil', 'bitkisel', 'misk', 'kehribar']</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Azzarois'in Azzaro Pour Homme Édition Noire'ı erkekler için Aromatik Fougere kokusudur. Azzaro Pour Homme Édition Noire 2017'de piyasaya sürüldü. Üst notalarda Acı Portakal, Adaçayı ve Limon; orta notalarda Sardunya, Artemisia ve Kimyon; temel notalar Iso E Super, Vetiver, Kimyon ve Kumarindir.</t>
+          <t>['tatlı', 'meyveli', 'bademli', 'fındıklı', 'kiraz', 'pudralı', 'vanilya', 'gül', 'hafif baharatlı', 'menekşe']</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Guerlaini'nin La Petite Robe Noire Extrait'i kadınlar için Çiçeksi Meyveli Gurme bir kokudur. La Petite Robe Noire Extrait 2016 yılında piyasaya sürülmüştür. Üst notalarda Meyveli Notalar, Meyan Kökü ve Limon; orta notalarda Kiraz, Badem, Gül ve Menekşe; temel notalarda Vanilya, Çay, Paçuli ve Misk bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -5467,20 +4085,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Max'd Al Haramain Perfumesfor men</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>86</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'odunsu', 'sıcak baharatlı', 'çiçeksi', 'misk', 'tatlı', 'metalik', 'deri', 'pudramsı', 'tütün']</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>Max'dbyAl Haramain Perfumesis erkekler için odunsu çiçeksi misk kokusu.</t>
+          <t>['turunçgil', 'odunsu', 'taze baharatlı', 'aromatik', 'mineral']</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Terre d'Hermes Eau GivreebyHermèsis, erkekler için narenciye aromalı bir parfüm. Bu yeni bir parfüm. Terre d'Hermes Eau Givree, 2022'de piyasaya sürüldü. Bu kokunun arkasındaki isim Christine Nagel. Üst notalarda turunçgiller; orta notalarda ardıç meyveleri ve timpani; alt notalarda odunsu notalar ve mineral notalar yer alıyor.</t>
         </is>
       </c>
     </row>
@@ -5497,20 +4107,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Boss Intense Shimmer Edition Hugo Bossfor women</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>86</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>['kehribar', 'odunsu', 'vanilya', 'beyaz çiçeksi', 'pudramsı', 'balzamik', 'gül', 'sıcak baharatlı', 'paçuli', 'çiçeksi']</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Hugo Boss'un Boss Intense Shimmer Edition'ı kadınlara yönelik Amber Spicy bir kokudur. Boss Intense Shimmer Edition 2004 yılında piyasaya sürülmüştür. Orta notalarda Vanilya, Yasemin ve Türk Gülü; temel notalarda Styrax, Amber, Sandal Ağacı ve Paçuli bulunur.</t>
+          <t>['sıcak baharatlı', 'odunsu', 'vanilya', 'pudramsı', 'beyaz çiçeksi', 'kehribar', 'gül', 'balzamik', 'paçuli', 'turunçgil']</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Hugo Boss'un Boss Intense'i, kadınlar için Amber Woody bir kokudur. Boss Intense, 2003 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Ursula Wandel'dir. Üst notalarda baharatlar ve portakal çiçeği; orta notalarda vanilya ve gül; alt notalarda sandal ağacı, amber ve paçuli bulunur.</t>
         </is>
       </c>
     </row>
@@ -5527,20 +4129,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>50 Years Oudh Ma’al Attar Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>86</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>['odunsu', 'turunçgil', 'pudramsı', 'çiçeksi', 'yeşil', 'taze', 'topraksı', 'aldehitli', 'gül', 'süsen']</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>50 Years Oudh Ma’al Attar by Al Haramain Perfumesis, kadınlar ve erkekler için Amber Floral bir kokudur. 50 Years Oudh Ma’al Attar, 2020 yılında piyasaya sürüldü. Üst notalarda Bergamot, Portakal, Galbanum, Ylang-Ylang ve Aldehitler; orta notalarda Gül, Leylak, Süsen ve Vadi Zambağı; temel notalarda Sedir, Amber, Sandal Ağacı, Meşe Yosunu ve Misk bulunmaktadır.</t>
+          <t>['çiçeksi', 'gül', 'taze', 'yeşil', 'misk']</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Boss Ma Vie L'EaubyHugo Boss, kadınlara yönelik çiçeksi bir kokudur. Boss Ma Vie L'Eau, 2018 yılında piyasaya sürülmüştür. Üst notalarda Kaktüs Çiçeği; orta notalarda Şakayık, Manolya ve Pembe Gül; alt notalarda Beyaz Misk ve Sedir bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -5557,20 +4151,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Musk Al Ghazal Eau de Parfum Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>86</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>['misk', 'sıcak baharatlı', 'taze baharatlı', 'tatlı', 'anason', 'pudramsı', 'çikolata', 'hafif baharatlı', 'aromatik', 'vanilya']</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>Musk Al Ghazal Eau de ParfumbyAl Haramain Perfumesis, kadınlar ve erkekler için bir Amber kokusudur. Üst notalarda kimyon ve anason; orta notalarda misk; alt notalarda baharatlar, bitter çikolata, odunsu notalar ve vanilya bulunur.</t>
+          <t>['çiçeksi', 'taze', 'yeşil', 'su', 'taze baharatlı', 'odunsu', 'bitkisel', 'aromatik', 'pudramsı', 'misk']</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>L'Eau par KenzobyKenzo, kadınlar için çiçeksi, su temalı bir kokudur. L'Eau par Kenzo, 1996 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki burun Olivier Cresp'tir. Üst notalarda Kamış, Nane, Yeşil Leylak, Mandalina ve Pembe Biber; orta notalarda Nilüfer, Biber, Menekşe, Beyaz Şeftali, Amaryllis ve Gül; alt notalarda Sedir, Beyaz Misk ve Vanilya bulunur.</t>
         </is>
       </c>
     </row>
@@ -5587,20 +4173,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>White Leather Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>86</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>['odunsu', 'taze baharatlı', 'aromatik', 'topraksı', 'dumanlı', 'yosunlu', 'paçuli', 'turunçgil', 'yeşil', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>Al Haramain Perfumesis'in White Leather parfümü, kadınlar ve erkekler için bir Deri kokusudur. White Leather, 2000'li yıllarda piyasaya sürülmüştür. Üst notalarda Sardunya ve Bergamot; orta notalarda Duman, Çay ve Hindistan Cevizi; alt notalarda Vetiver, Sedir, Paçuli ve Meşe Yosunu bulunur.</t>
+          <t>['odunsu', 'aromatik', 'turunçgil', 'taze baharatlı', 'deri', 'sarı çiçeksi', 'sümbülteber', 'beyaz çiçeksi', 'hayvansal', 'sıcak baharatlı']</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Lacoste Fragrance tarafından üretilen Eau de Lacoste L.12.12 Blanc Limited Edition, erkekler için odunsu aromatik bir kokudur. Eau de Lacoste L.12.12 Blanc Limited Edition, 2014 yılında piyasaya sürülmüştür. Üst notalarda Greyfurt, Biberiye, Sedir İğneleri ve Kakule; orta notalarda Ylang-Ylang ve Sümbülteber; alt notalarda Virginia Sediri, Vetiver, Deri ve Süet bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -5617,22 +4195,10 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Lacoste Essential Collector Edition Lacoste Fragrancesfor men</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>90</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'odunsu', 'taze baharatlı', 'aromatik', 'gül', 'sıcak baharatlı', 'meyvemsi', 'yeşil', 'paçuli', 'hafif baharatlı']</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Lacoste Fragrance tarafından üretilen Lacoste Essential Collector Edition, erkekler için odunsu aromatik bir kokudur. Lacoste Essential Collector Edition, 2008 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Laurent Bruyere'dir. Üst notalarda Bergamot, Mandalina ve Çin Tarçını; orta notalarda Gül ve Biber; alt notalarda Paçuli ve Sandal Ağacı bulunur.</t>
-        </is>
-      </c>
+          <t>['aromatik', 'turunçgil', 'taze baharatlı', 'yeşil', 'odunsu', 'meyvemsi', 'hafif baharatlı', 'sıcak baharatlı', 'gül', 'paçuli']</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5647,20 +4213,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>9am pour Femme Afnanfor women</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>86</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'misk', 'kehribar', 'turunçgil', 'pudramsı', 'tatlı', 'hayvansal', 'hafif baharatlı']</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>9am pour FemmebyAfna, kadınlar için bir Amber kokusudur. Bu yeni bir kokudur. 9am pour Femme, 2022 yılında piyasaya sürüldü. Üst notalarda Mandalina, Greyfurt ve Bergamot; orta notalarda Ahududu ve Siyah Frenk Üzümü; alt notalarda Misk, Amber ve Portakal bulunur.</t>
+          <t>['çiçeksi', 'pudramsı', 'misk', 'odunsu', 'beyaz çiçeksi', 'sıcak baharatlı', 'gül', 'kehribar', 'vanilya']</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Femme de Lacoste by Lacoste Fragrance, kadınlar için çiçeksi odunsu misk kokusudur. Femme de Lacoste, 2008 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Olivier Cresp'tir. Üst notalarda Frezya ve Kırmızı Biber; orta notalarda Yasemin, Bulgar Gülü, Ebegümeci ve Kediotu; alt notalarda Sandal Ağacı, Misk ve Amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -5677,20 +4235,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Club de Nuit Blue Iconic Armaffor men</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>86</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'odunsu', 'sıcak baharatlı', 'kehribar', 'aromatik', 'taze baharatlı', 'taze', 'yeşil', 'balzamik', 'dumanlı']</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Club de Nuit Blue Iconic by Armafis erkekler için bir parfüm. Bu yeni bir parfüm. Club de Nuit Blue Iconic 2022 yılında piyasaya sürüldü. Üst notalarda Greyfurt, Limon, Nane, Pembe Biber ve Kişniş; orta notalarda Zencefil, Kavun, Hindistan Cevizi ve Yasemin; alt notalarda Odunsu Notalar, Tütsü, Kehribar, Sandal Ağacı, Sedir, Paçuli ve Laden bulunmaktadır.</t>
+          <t>['sıcak baharatlı', 'turunçgil', 'taze baharatlı', 'vanilya', 'tarçın', 'aromatik', 'yeşil', 'paçuli', 'hafif baharatlı', 'odunsu']</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Bois NuitbyArmafis erkekler için aromatik baharatlı bir koku. Üst notalarda Greyfurt, Nane, Pembe Biber ve Bergamot; orta notalarda Tarçın, Zencefil, Lavanta ve Hindistan Cevizi; alt notalarda Vanilya, Paçuli, Amber, Sedir ve Vetiver bulunur.</t>
         </is>
       </c>
     </row>
@@ -5707,20 +4257,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Belle Rouge Al Haramain Perfumesfor women</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>86</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>['lavanta', 'aromatik', 'turunçgil', 'vanilya', 'meyvemsi', 'odunsu', 'tatlı', 'beyaz çiçeksi', 'pudramsı', 'taze baharatlı']</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Belle RougebyAl Haramain Perfumesis, kadınlar için Amber Floral bir kokudur. Belle Rouge, 2020 yılında piyasaya sürülmüştür. Üst notalarda Portakal, Greyfurt, Armut, Mandalina ve Limon; orta notalarda Lavanta, Yasemin, Gül, Şeftali ve Siyah Frenk Üzümü; temel notalarda Vanilya, Tonka Fasulyesi, Misk, Vetiver, Sandal Ağacı ve Sedir bulunmaktadır.</t>
+          <t>['tatlı', 'vanilya', 'meyveli', 'paçuli', 'odunsu', 'beyaz çiçeksi', 'pudramsı', 'topraksı', 'süsen', 'sıcak baharatlı']</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>La Vie Est BellebyLancôme, kadınlar için çiçeksi meyveli gurme bir koku. La Vie Est Belle, 2012 yılında piyasaya sürüldü. La Vie Est Belle, Olivier Polge, Dominique Ropion ve Anne Flipo tarafından yaratıldı. Üst notalarda Siyah Frenk Üzümü ve Armut; orta notalarda Süsen, Yasemin ve Portakal Çiçeği; alt notalarda Pralin, Vanilya, Paçuli ve Tonka Fasulyesi yer alıyor.</t>
         </is>
       </c>
     </row>
@@ -5737,20 +4279,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Trust Me Al-Rehabfor men</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>86</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>['kehribar', 'misk', 'pudramsı', 'odunsu', 'süsen']</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>Trust MebyAl-Rehabi erkekler için bir Amber Fougere kokusudur. Bu yeni bir kokudur. Trust Me, 2024 yılında piyasaya sürülmüştür. Üst notalarda Menekşe Yaprağı, Yeşil Yapraklar, Greyfurt ve Limon; orta notalarda Süsen, Elma ve Sulu Notalar; alt notalarda Misk, Sedir Ağacı, Ambroxan ve Kristal Amber bulunur.</t>
+          <t>['çiçeksi', 'sıcak baharatlı', 'badem', 'tarçın', 'odunsu', 'meyveli', 'fındıksı', 'taze', 'pudramsı', 'tatlı']</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Marry (Me) On ThursdaybyAll Your Personal Aroma, kadın ve erkeklere yönelik bir parfümdür. Marry (Me) On Thursday, 2019 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Raluca Vasile'dir.</t>
         </is>
       </c>
     </row>
@@ -5767,20 +4301,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Max'd Al Haramain Perfumesfor men</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>86</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'odunsu', 'sıcak baharatlı', 'çiçeksi', 'misk', 'tatlı', 'metalik', 'deri', 'pudramsı', 'tütün']</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Max'dbyAl Haramain Perfumesis erkekler için odunsu çiçeksi misk kokusu.</t>
+          <t>['odunsu', 'meyveli', 'çiçeksi', 'beyaz çiçeksi', 'turunçgil', 'aromatik', 'topraksı', 'kehribar', 'paçuli', 'gül']</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Giorgio Armani'nin Eclat de Jasmin'i kadınlar ve erkekler için bir Chypre Floral parfümüdür. Eclat de Jasmin 2007 yılında piyasaya sürülmüştür. Üst notalarda Bergamot ve Limon; orta notalarda Yasemin, Osmanthus, Erik ve Gül; alt notalarda Tahiti Vetiver'i, Labdanum ve Paçuli bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -5797,18 +4323,10 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Allure of Love Al-Rehabfor women</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>86</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
           <t>['turunçgil', 'beyaz çiçeksi', 'odunsu', 'tatlı', 'meyveli', 'pudramsı', 'tropikal', 'taze', 'gül', 'kehribar']</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
+      <c r="D180" t="inlineStr">
         <is>
           <t>Allure of LovebyAl-Rehabi, kadınlar için bir Citrus Gourmand kokusudur. Bu yeni bir kokudur. Allure of Love, 2024 yılında piyasaya sürülmüştür. Üst notalarda Portakal Yağı, Bergamot, Hindistan Cevizi, Şeftali ve İtalyan Mandalinası; orta notalarda Vadi Zambağı, Tropikal Meyveler, Portakal Çiçeği, Yasemin ve Gül; alt notalarda Sandal Ağacı, Paçuli, Sedir Ağacı, Amber ve Misk bulunur.</t>
         </is>
@@ -5827,22 +4345,10 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Red African Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>86</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>['taze baharatlı', 'karamel', 'tatlı', 'kehribar', 'balzamik', 'vanilya', 'pudramsı', 'hayvansal', 'odunsu']</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>Al Haramain Perfumesi'nin Red African'ı kadınlar ve erkekler için Amber Woody bir kokudur. Red African 2017 yılında piyasaya sürülmüştür. Üst notalarda Brezilya Gül Ağacı; orta notalarda Hindistan Cevizi ve Karamel; alt notalarda Ambergris, Vanilya ve Misk bulunmaktadır.</t>
-        </is>
-      </c>
+          <t>['yeşil', 'aromatik', 'taze baharatlı', 'meyveli', 'tatlı', 'taze']</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5857,20 +4363,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Eau de Calandre Paco Rabannefor women</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>86</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>['odunsu', 'aromatik', 'topraksı', 'beyaz çiçeksi', 'turunçgil', 'pudramsı', 'gül', 'taze baharatlı', 'yosunlu', 'misk']</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>Eau de CalandrebyPaco Rabanne, kadınlar için bir Chypre Çiçeksi parfümüdür. Eau de Calandrews 1969 yılında piyasaya sürülmüştür. Üst notalarda Sardunya, Bergamot ve Limon; orta notalarda Vadi Zambağı, Gül, Süsen, Yasemin ve Ylang-Ylang; alt notalarda Meşe Yosunu, Vetiver, Misk, Sedir, Sandal Ağacı ve Amber bulunur.</t>
+          <t>['taze baharatlı', 'aromatik', 'turunçgil', 'odunsu', 'lavanta', 'kehribar', 'yeşil', 'topraksı', 'bitkisel', 'dumanlı']</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Eau Paco Rabanne, erkekler için aromatik bir Fougere kokusudur. Eau Paco Rabanne, 2002 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Olivier Cresp'tir. Üst notalarda Bergamot, Lavanta, Limon ve Portakal Çiçeği; orta notalarda Fesleğen, Vetiver, Biber ve Değerli Ağaçlar; alt notalarda Tütsü, Meşe Yosunu, Misk, Sandal Ağacı, Amber ve Deri bulunur.</t>
         </is>
       </c>
     </row>
@@ -5887,20 +4385,12 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Million Al Haramain Perfumesfor women</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>86</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>['vanilya', 'tatlı', 'meyveli', 'odunsu', 'pudralı', 'tropikal', 'beyaz çiçeksi', 'sarı çiçeksi', 'kehribar', 'misk']</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>MillionbyAl Haramain Perfumesis, kadınlar için çiçeksi meyveli gurme bir kokudur. Üst notalarda Mango, Erik ve Bergamot; orta notalarda Yasemin, Ylang-Ylang ve Gül; alt notalarda Vanilya, Sandal Ağacı, Amber, Misk ve Sedir bulunur.</t>
+          <t>['beyaz çiçeksi', 'sümbülteber', 'misk', 'hayvansal']</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Bath &amp; Body Works'ün One In A Million'u kadınlara yönelik bir parfümdür. One In A Million 2019 yılında piyasaya sürülmüştür.</t>
         </is>
       </c>
     </row>
@@ -5917,20 +4407,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Calandre Paco Rabannefor women</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>86</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>['yeşil', 'aldehitli', 'taze', 'topraksı', 'gül', 'odunsu', 'beyaz çiçeksi', 'çiçeksi', 'taze baharatlı', 'aromatik']</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>CalandrebyPaco Rabanne, kadınlar için çiçeksi bir aldehit kokusudur. Calandrews 1969 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Michel Hy'dir. Üst notalarda Aldehitler, Yeşil Notalar ve Bergamot; orta notalarda Gül, Vadi Zambağı, Süsen Kökü, Sardunya, Sümbül ve Yasemin; alt notalarda Meşe Yosunu, Vetiver, Misk, Sandal Ağacı ve Amber bulunur.</t>
+          <t>['taze baharatlı', 'aromatik', 'turunçgil', 'odunsu', 'lavanta', 'kehribar', 'yeşil', 'topraksı', 'bitkisel', 'dumanlı']</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Eau Paco Rabanne, erkekler için aromatik bir Fougere kokusudur. Eau Paco Rabanne, 2002 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Olivier Cresp'tir. Üst notalarda Bergamot, Lavanta, Limon ve Portakal Çiçeği; orta notalarda Fesleğen, Vetiver, Biber ve Değerli Ağaçlar; alt notalarda Tütsü, Meşe Yosunu, Misk, Sandal Ağacı, Amber ve Deri bulunur.</t>
         </is>
       </c>
     </row>
@@ -5947,20 +4429,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>One In A Million Bath &amp; Body Worksfor women</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>86</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>['beyaz çiçeksi', 'sümbülteber', 'misk', 'hayvansal']</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>Bath &amp; Body Works'ün One In A Million'u kadınlara yönelik bir parfümdür. One In A Million 2019 yılında piyasaya sürülmüştür.</t>
+          <t>['beyaz çiçeksi', 'tatlı', 'bal', 'turunçgil', 'meyveli', 'çiçeksi', 'paçuli', 'hayvansal', 'kehribar']</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Lady Million by Paco Rabanne, kadınlar için çiçeksi ve meyveli bir kokudur. Lady Million, 2010 yılında piyasaya sürülmüştür. Lady Million, Anne Flipo, Beatrice Piquet, Dominique Ropion ve Bruno Jovanovic tarafından yaratılmıştır. Üst notalarda Ahududu, Portakal Çiçeği ve Amalfi Limonu; orta notalarda Yasemin, Afrika Portakal Çiçeği ve Gardenya; alt notalarda Beyaz Bal, Paçuli ve Amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -5977,20 +4451,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Mugler Cologne Muglerfor women and men</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>86</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'beyaz çiçeksi', 'taze baharatlı', 'aromatik', 'misk', 'yeşil', 'pudramsı']</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>Mugler Cologne, kadınlar ve erkekler için narenciye aromalı bir kokudur. Mugler Cologne, 2001 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Alberto Morillas'tır. Üst notalarda Neroli, Bergamot ve Petitgrain; orta notalarda Afrika Portakal Çiçeği; alt notalarda Misk bulunur.</t>
+          <t>['kehribar', 'beyaz çiçeksi', 'odunsu', 'hayvansal']</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Thierry Mugler Show Collection: Alien Couture Stoneby Mugler kadınlara yönelik bir parfümdür. Thierry Mugler Show Collection: Alien Couture Stone, 2010 yılında piyasaya sürülmüştür. Thierry Mugler Show Collection: Alien Couture Stone, Dominique Ropion ve Laurent Bruyere tarafından yaratılmıştır.</t>
         </is>
       </c>
     </row>
@@ -6007,20 +4473,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Trussardi Donna (2011) Trussardifor women</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>90</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'beyaz çiçeksi', 'meyveli', 'tatlı', 'çiçeksi', 'vanilya', 'odunsu', 'pudramsı']</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>Trussardi Donna (2011), kadınlar için Amber Floral bir kokudur. Trussardi Donna (2011), 2011 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Nathalie Lorson'dır. Üst notalarda Meyveli Notalar, Yuzu ve Amalfi Limonu; orta notalarda Yasemin, Afrika Portakal Çiçeği ve Lotus; alt notalarda Vanilya, Sandal Ağacı, Paçuli ve Virginia Sediri bulunur.</t>
+          <t>['kehribar', 'aromatik', 'çiçeksi', 'sıcak baharatlı', 'beyaz çiçeksi', 'odunsu', 'turunçgil', 'taze baharatlı', 'yeşil', 'taze']</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Donna TrussardibyTrussardi, kadınlar için bir Chypre Floral parfümüdür. Donna Trussardi, 1994 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Jean Guichard'dır. Üst notalarda Aldehitler, Kişniş, Adaçayı, Hiacynth, Bergamot, Mandalina, Fesleğen ve Zencefil; orta notalarda Gül, Karanfil, Ylang-Ylang, Sümbülteber, Yasemin, Süsen Kökü ve Vadi Zambağı; alt notalarda Laden, Benzoin, Styrax, Amber, Paçuli, Misk, Vanilya ve Sedir bulunur.</t>
         </is>
       </c>
     </row>
@@ -6037,20 +4495,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Musk Al Ghazal Eau de Parfum Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>86</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>['misk', 'sıcak baharatlı', 'taze baharatlı', 'tatlı', 'anason', 'pudramsı', 'çikolata', 'hafif baharatlı', 'aromatik', 'vanilya']</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>Musk Al Ghazal Eau de ParfumbyAl Haramain Perfumesis, kadınlar ve erkekler için bir Amber kokusudur. Üst notalarda kimyon ve anason; orta notalarda misk; alt notalarda baharatlar, bitter çikolata, odunsu notalar ve vanilya bulunur.</t>
+          <t>['turunçgil', 'aromatik', 'odunsu', 'meyvemsi', 'taze baharatlı', 'tropikal', 'sıcak baharatlı', 'taze']</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Versace Man Eau FraichebyVersace, erkekler için odunsu ve sucul bir kokudur. Versace Man Eau Fraiche, 2006 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Olivier Cresp'tir. Üst notalarda Limon, Bergamot, Karambola (Yıldız Meyvesi), Kakule ve Brezilya Gül Ağacı; orta notalarda Sedir, Tarhun, Adaçayı ve Biber; alt notalarda Misk, Odunsu Notalar, Safran, Amber ve Çınar bulunur.</t>
         </is>
       </c>
     </row>
@@ -6067,18 +4517,10 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Eros O Boticáriofor men</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>86</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
           <t>['odunsu', 'turunçgil', 'çiçeksi', 'taze']</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6093,20 +4535,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Crystal Oud Al-Rehabfor women and men</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>86</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>['ud', 'taze baharatlı']</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>Crystal OudbyAl-Rehabis kadınlar ve erkekler için bir Amber kokusu.</t>
+          <t>['çiçeksi', 'turunçgil', 'taze', 'odunsu', 'taze baharatlı', 'gül']</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Versace'nin Bright Crystal'ı, kadınlar için çiçeksi ve meyveli bir kokudur. Bright Crystal, 2006 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Alberto Morillas. Üst notalarda Yuzu, Nar ve Buz; orta notalarda Şakayık, Lotus ve Manolya; alt notalarda Misk, Maun ve Amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -6123,20 +4557,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Absolute by Exclusive Avonfor men</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>86</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>['ud', 'kehribar', 'odunsu', 'sıcak baharatlı', 'taze baharatlı', 'aromatik', 'dumanlı', 'paçuli', 'balzamik', 'turunçgil']</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>ExclusivebyAvon'dan Absolute, erkekler için odunsu aromatik bir kokudur. Absolute by Exclusive, 2020 yılında piyasaya sürüldü. Absolute by Exclusive, Marion Costero ve Stephen Nilsen tarafından yaratıldı. Üst notalarda Sicilya Limonu, Lavanta ve Afrika Sardunyası; orta notalarda Agar Ağacı (Ud), Teksas Sediri, Tütsü ve Safralein; alt notalarda Kehribar, Endonezya Paçuli Yaprağı ve Ambrein bulunur.</t>
+          <t>['kehribar', 'sıcak baharatlı', 'beyaz çiçeksi', 'odunsu', 'balzamik', 'topraksı', 'yosunlu', 'çiçeksi', 'dumanlı', 'hayvansal']</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Gianni VersacebyVersace, kadınlar için bir Chypre Çiçeksi parfümüdür. Gianni Versace 1981 yılında piyasaya sürülmüştür. Üst notalarda Baharatlar, Aldehitler, Meyveli Notalar ve Bergamot; orta notalarda Karanfil, Sümbülteber, Nergis, Gardenya, Süsen Kökü, Yasemin ve Vadi Zambağı; alt notalarda Meşe Yosunu, Benzoin, Mür, Tütsü, Amber, Sandal Ağacı, Deri ve Paçuli bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -6153,20 +4579,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Noir Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>86</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>['sıcak baharatlı', 'taze baharatlı', 'aromatik', 'odunsu', 'turunçgil', 'topraksı', 'bal', 'ud', 'paçuli', 'kehribar']</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>NoirbyAl Haramain Perfumesis, kadınlar ve erkekler için bir parfümdür. Bu yeni bir parfümdür. Noir, 2023 yılında piyasaya sürüldü. Üst notalarda Karabiber, Portakal Çiçeği ve Greyfurt; orta notalarda Safran, Bal ve Kakule; alt notalarda Agar Ağacı, Olibanum, Paçuli ve Vetiver bulunur.</t>
+          <t>['çiçeksi', 'turunçgil', 'taze', 'odunsu', 'taze baharatlı', 'gül']</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Versace'nin Bright Crystal'ı, kadınlar için çiçeksi ve meyveli bir kokudur. Bright Crystal, 2006 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Alberto Morillas. Üst notalarda Yuzu, Nar ve Buz; orta notalarda Şakayık, Lotus ve Manolya; alt notalarda Misk, Maun ve Amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -6183,20 +4601,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Black Oudh Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>86</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>['odunsu', 'pudramsı', 'misk', 'kehribar', 'paçuli', 'vanilya', 'yeşil', 'sıcak baharatlı', 'balzamik', 'hayvansal']</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>Black OudhbyAl Haramain Perfumesis, kadınlar ve erkekler için Amber-Woody bir kokudur. Üst notalarda Misk; orta notalarda Sedir ve Bitkisel Notalar; alt notalarda Amber, Paçuli ve Vanilya bulunur.</t>
+          <t>['vanilya', 'kahve', 'tatlı', 'sıcak baharatlı', 'beyaz çiçeksi', 'hafif baharatlı', 'odunsu', 'meyvemsi', 'pudramsı', 'balzamik']</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Black Opium, Yves Saint Laurentis'in kadınlara özel Amber Vanilya aromalı kokusudur. Black Opium, 2014 yılında piyasaya sürülmüştür. Black Opium, Nathalie Lorson, Marie Salamagne, Olivier Cresp ve Honorine Blanc tarafından yaratılmıştır. Üst notalarda Armut, Pembe Biber ve Portakal Çiçeği; orta notalarda Kahve, Yasemin, Acı Badem ve Meyan Kökü; alt notalarda Vanilya, Paçuli, Kaşmir Ağacı ve Sedir bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -6213,20 +4623,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>VIP Private Show Britney Spearsfor women</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>86</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'tatlı', 'turunçgil', 'tropikal', 'pudramsı', 'menekşe']</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>Britney Spear'ın VIP Private Show'u kadınlara yönelik çiçeksi ve meyveli bir kokudur. VIP Private Show, 2017 yılında piyasaya sürülmüştür. Üst notalarda Mango, Kırmızı Elma ve Kan Portakalı; orta notalarda Menekşe, Portakal Çiçeği ve Manolya; alt notalarda Ahududu, Amber, Misk ve Odunsu Notalar yer almaktadır.</t>
+          <t>['sıcak baharatlı', 'aromatik', 'odunsu', 'votka', 'taze baharatlı', 'hayvansal', 'turunçgil', 'yeşil', 'deri', 'tropikal']</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Carolina Herrera'nın 212 VIP MEN Pills'i, erkekler için Amber Woody bir kokudur. 212 VIP MEN Pills, 2016 yılında piyasaya sürüldü. 212 VIP MEN Pills, Emilie Bevierre-Coppermann ve Lucas Sieuzac tarafından yaratıldı. Üst notalarda Çarkıfelek Meyvesi, Zencefil, Limon, Biber ve Havyar; orta notalarda Votka, Baharatlar, Cin ve Nane; alt notalarda Deri, Amber ve Odunsu Notalar bulunur.</t>
         </is>
       </c>
     </row>
@@ -6243,20 +4645,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Blue Sugar Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>86</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>['tatlı', 'vanilya', 'turunçgil', 'hindistan cevizi', 'laktonik']</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>Blue Sugar by Al Haramain Perfumesis, kadınlar ve erkekler için çiçeksi meyveli gurme bir kokudur. Blue Sugar, 2016 yılında piyasaya sürülmüştür.</t>
+          <t>['turunçgil', 'ozonik', 'su', 'odunsu', 'meyvemsi', 'çiçeksi', 'aromatik', 'yeşil', 'kehribar', 'taze baharatlı']</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Antonio Banderas'ın Cocktail Seduction Blue for Men adlı parfümü, erkekler için aromatik bir koku. 2014 yılında piyasaya sürülen Cocktail Seduction Blue for Men, bu kokunun arkasındaki isim Olivier Cresp. Üst notalarda Mojito, Karpuz, Bergamot ve Siyah Frenk Üzümü; orta notalarda Kakule, Çiçeksi Notalar ve Palisander Gül Ağacı; alt notalarda Ambergris, Sedir ve Misk bulunuyor.</t>
         </is>
       </c>
     </row>
@@ -6273,20 +4667,12 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>My Burberry Burberryfor women</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>95</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>['çiçeksi', 'tatlı', 'turunçgil', 'gül', 'meyveli', 'taze baharatlı', 'aromatik', 'yeşil']</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>My BurberrybyBurberry, kadınlar için çiçeksi bir kokudur. My Burberry, 2014 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Francis Kurkdjian. Üst notalarda bezelye, bergamot, mandalina, greyfurt ve limon; orta notalarda ayva, frezya, sardunya, şeftali, yeşil notalar, gardenya ve çarkıfelek meyvesi; alt notalarda ise şam gülü, gül, paçuli, misk, deri ve menekşe bulunuyor.</t>
+          <t>['aromatik', 'odunsu', 'taze baharatlı', 'yeşil', 'pudramsı', 'lavanta', 'turunçgil', 'bitkisel']</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Burberry MenbyBurberry, erkekler için odunsu aromatik bir kokudur. Burberry Men, 1995 yılında piyasaya sürülmüştür. Burberry Men, Creations Aromatiques ve Michel Almairac tarafından yaratılmıştır. Üst notalarda Nane, Lavanta, Bergamot ve Kekik; orta notalarda Sedir, Sandal Ağacı, Sardunya, Yasemin ve Meşe Yosunu; alt notalarda Misk, Vanilya ve Amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -6303,18 +4689,10 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bvlgari Extreme Bvlgarifor men</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>86</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
           <t>['turunçgil', 'taze baharatlı', 'odunsu', 'aromatik', 'yeşil', 'taze', 'pudramsı', 'sıcak baharatlı']</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
+      <c r="D197" t="inlineStr">
         <is>
           <t>Bvlgari Extremeby Bvlgari, erkekler için odunsu aromatik bir kokudur. Bvlgari Extreme, 1999 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Jacques Cavallier'dir. Üst notalarda Çay, Greyfurt, Bergamot, Portakal Çiçeği, Petitgrain, Kişniş, Lavanta ve Galbanum; orta notalarda Balsam Köknarı, Guaiac Ağacı, Biber, Hindistan Cevizi, Brezilya Gül Ağacı ve Kakule; alt notalarda Misk, Sedir, Süsen, Meşe Yosunu ve Sandal Ağacı bulunur.</t>
         </is>
@@ -6333,20 +4711,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Crystalline for Women Al-Rehabfor women</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>86</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>Al-Rehabi Crystalline for Women kadınlara özel bir parfüm.</t>
+          <t>['odunsu', 'çiçeksi', 'misk', 'yeşil', 'su', 'ozonik', 'meyvemsi', 'taze', 'pudramsı', 'topraksı']</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Bvlgari'nin Omnia Crystalline'ı, kadınlar için çiçeksi ve su temalı bir koku. Omnia Crystalline, 2005 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Alberto Morillas. Üst notalarda Bambu ve Armut; orta notalarda Lotus, Çay ve Çin Tarçını; alt notalarda Misk, Guaiac Ağacı ve Meşe Yosunu bulunuyor.</t>
         </is>
       </c>
     </row>
@@ -6363,18 +4733,10 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Calvin Klein Calvin Kleinfor women</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>86</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
           <t>['çiçeksi', 'odunsu', 'beyaz çiçeksi', 'gül', 'pudramsı', 'topraksı', 'yosunlu', 'yeşil', 'aldehitli', 'taze']</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
+      <c r="D199" t="inlineStr">
         <is>
           <t>Calvin KleinbyCalvin Klein, kadınlar için bir Chypre Floral parfümüdür. Calvin Klein, 1978 yılında piyasaya sürülmüştür. Üst notalarda Sümbül, Aldehitler, Gardenya, Şeftali ve Ahududu; orta notalarda Gül, Karanfil, Vadi Zambağı, Yasemin ve Süsen Kökü; alt notalarda Meşe Yosunu, Amber, Sandal Ağacı, Sedir ve Misk bulunmaktadır.</t>
         </is>
@@ -6393,20 +4755,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avon Life by Kenzo Takada for Her Avonfor women</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>86</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>['çiçeksi', 'taze', 'menekşe', 'turunçgil', 'pudramsı', 'su']</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>Avon Life by Kenzo Takada for HerbyAvon, kadınlar için çiçeksi odunsu misk kokusudur. Avon Life by Kenzo Takada for Her, 2016 yılında piyasaya sürülmüştür. Üst notalarda Nilüfer, Turunçgiller, Beyaz Çay ve Kırmızı Elma; orta notalarda Şakayık, Menekşe ve Japon Kiraz Çiçeği; alt notalarda İris, Ambrette (Misk Ebegümeci) ve Paçuli bulunmaktadır.</t>
+          <t>['tatlı', 'pudramsı', 'misk', 'hafif baharatlı', 'karamel', 'vanilya', 'çiçeksi', 'turunçgil', 'beyaz çiçeksi', 'odunsu']</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>212 SexybyCarolina Herrera, kadınlar için Amber Floral bir kokudur. 212 Sexy, 2004 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Rosendo Mateu'dur. Üst notalarda Pembe Biber, Mandalina ve Bergamot; orta notalarda Pamuk Şeker, Gardenya, Çiçekler, Sardunya ve Gül; alt notalarda Vanilya, Misk, Sandal Ağacı, Karamel, Menekşe ve Paçuli bulunur.</t>
         </is>
       </c>
     </row>
@@ -6423,20 +4777,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Red African Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>86</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>['taze baharatlı', 'karamel', 'tatlı', 'kehribar', 'balzamik', 'vanilya', 'pudramsı', 'hayvansal', 'odunsu']</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>Al Haramain Perfumesi'nin Red African'ı kadınlar ve erkekler için Amber Woody bir kokudur. Red African 2017 yılında piyasaya sürülmüştür. Üst notalarda Brezilya Gül Ağacı; orta notalarda Hindistan Cevizi ve Karamel; alt notalarda Ambergris, Vanilya ve Misk bulunmaktadır.</t>
+          <t>['sıcak baharatlı', 'odunsu', 'vanilya', 'taze baharatlı', 'kehribar', 'aromatik', 'tarçın', 'pudramsı', 'çiçeksi', 'lavanta']</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Armand Basi HommebyArmand Basi, erkekler için Aromatik Fougere kokusudur. Armand Basi Homme, 2000 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki burun Olivier Cresp'tir. Üst notalarda Tarçın, Lavanta ve Kakule; orta notalarda Hindistan Cevizi, Tonka Fasulyesi, Tütsü, Leylak ve Vadi Zambağı; alt notalarda Vanilya, Sedir, Sandal Ağacı, Guaiac Ağacı ve Misk bulunur.</t>
         </is>
       </c>
     </row>
@@ -6453,20 +4799,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Carolina Herrera by Carolina Herrera Carolina Herrerafor women</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>86</v>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>['beyaz çiçeksi', 'sümbülteber', 'yeşil', 'hayvansı', 'odunsu', 'sarı çiçeksi', 'misk', 'pudramsı', 'çiçeksi']</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>Carolina Herrera by Carolina Herrera, kadınlar için çiçeksi bir kokudur. Carolina Herrera by Carolina Herrera, 1988 yılında piyasaya sürülmüştür. Carolina Herrera by Carolina Herrera, Carlos Benaim, Clement Gavarry ve Rosendo Mateu tarafından yaratılmıştır. Üst notalarda Kayısı, Portakal Çiçeği, Yeşil Notalar, Brezilya Gül Ağacı ve Bergamot; orta notalarda Hint Sümbülteberi, Yasemin, İspanyol Yasemini, Ylang-Ylang, Hanımeli, Nergis, Hiacynth ve Vadi Zambağı; alt notalarda Misk Kedisi, Misk, Meşe Yosunu, Kehribar, Sandal Ağacı, Vetiver ve Sedir bulunur.</t>
+          <t>['tatlı', 'pudramsı', 'misk', 'hafif baharatlı', 'karamel', 'vanilya', 'çiçeksi', 'turunçgil', 'beyaz çiçeksi', 'odunsu']</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>212 SexybyCarolina Herrera, kadınlar için Amber Floral bir kokudur. 212 Sexy, 2004 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Rosendo Mateu'dur. Üst notalarda Pembe Biber, Mandalina ve Bergamot; orta notalarda Pamuk Şeker, Gardenya, Çiçekler, Sardunya ve Gül; alt notalarda Vanilya, Misk, Sandal Ağacı, Karamel, Menekşe ve Paçuli bulunur.</t>
         </is>
       </c>
     </row>
@@ -6483,20 +4821,12 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Allure of Love Al-Rehabfor women</t>
-        </is>
-      </c>
-      <c r="D203" t="n">
-        <v>86</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'beyaz çiçeksi', 'odunsu', 'tatlı', 'meyveli', 'pudramsı', 'tropikal', 'taze', 'gül', 'kehribar']</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>Allure of LovebyAl-Rehabi, kadınlar için bir Citrus Gourmand kokusudur. Bu yeni bir kokudur. Allure of Love, 2024 yılında piyasaya sürülmüştür. Üst notalarda Portakal Yağı, Bergamot, Hindistan Cevizi, Şeftali ve İtalyan Mandalinası; orta notalarda Vadi Zambağı, Tropikal Meyveler, Portakal Çiçeği, Yasemin ve Gül; alt notalarda Sandal Ağacı, Paçuli, Sedir Ağacı, Amber ve Misk bulunur.</t>
+          <t>['turunçgil', 'aromatik', 'vanilya', 'aldehitli', 'deniz', 'tatlı', 'taze baharatlı', 'taze', 'kehribar', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Chanel'in Allure Homme Sport'u erkekler için odunsu ve baharatlı bir koku. Allure Homme Sport, 2004 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Jacques Polge. Üst notalarda Portakal, Deniz Notaları, Aldehitler ve Kan Mandalinası; orta notalarda Biber, Portakal Çiçeği ve Sedir; alt notalarda Vanilya, Tonka Fasulyesi, Beyaz Misk, Amber, Vetiver ve Elemi reçinesi bulunuyor.</t>
         </is>
       </c>
     </row>
@@ -6513,20 +4843,12 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Bleu de Chanel Chanelfor men</t>
-        </is>
-      </c>
-      <c r="D204" t="n">
-        <v>95</v>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'odunsu', 'sıcak baharatlı', 'aromatik', 'kehribar', 'taze baharatlı', 'dumanlı', 'balzamik', 'yeşil', 'misk']</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>Bleu de ChanelbyChanel, erkekler için odunsu aromatik bir koku. Bleu de Chanel, 2010 yılında piyasaya sürüldü. Bu kokunun arkasındaki burun Jacques Polge'ye ait. Üst notalarda Greyfurt, Limon, Nane ve Pembe Biber; orta notalarda Zencefil, Hindistan Cevizi, Yasemin ve Iso E Super; alt notalarda Tütsü, Vetiver, Sedir, Sandal Ağacı, Paçuli, Laden ve Beyaz Misk bulunuyor.</t>
+          <t>['odunsu', 'taze', 'beyaz çiçeksi', 'aromatik', 'pudramsı', 'yeşil', 'çiçeksi', 'menekşe', 'aldehitli', 'hafif baharatlı']</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Le 1940 Bleu de Chanelby Chanel, kadınlar için çiçeksi bir aldehit kokusudur. Le 1940 Bleu de Chanel, 1931 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki burun Ernest Beaux'dur. Üst notalarda Aldehitler ve Zambak; orta notalarda Menekşe, Frenk Üzümü, Vadi Zambağı ve Siklamen; alt notalarda Vetiver, Sedir ve Sandal Ağacı bulunur.</t>
         </is>
       </c>
     </row>
@@ -6543,20 +4865,12 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Eau de Dior Coloressence Energizing Diorfor women</t>
-        </is>
-      </c>
-      <c r="D205" t="n">
-        <v>86</v>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'aromatik', 'çiçeksi', 'taze baharatlı', 'yeşil', 'pudramsı']</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>Dioris'in Eau de Dior Coloressence Energizing parfümü, kadınlar için aromatik bir kokudur. Eau de Dior Coloressence Energizing, 2000 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Max Gavarry'dir. Üst notalarda Limon Verbena, Limon, Nane ve Portakal; orta notalarda Manolya, Menekşe ve Gül; alt notalarda Misk ve Köknar bulunur.</t>
+          <t>['tatlı', 'meyveli', 'karamel', 'kiraz', 'paçuli', 'odunsu']</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Miss Dior CheriebyDioris, kadınlar için Chypre Fruity kokusudur. Miss Dior Cherie, 2005 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Christine Nagel'dır. Üst notalarda Kiraz, Çilek, Ananas ve Mandalina; orta notalarda Patlamış Mısır, Karamel, Gül, Yasemin ve Menekşe; alt notalarda Paçuli, Misk ve Amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -6573,18 +4887,10 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Christian Lacroix Absynthe Avonfor women</t>
-        </is>
-      </c>
-      <c r="D206" t="n">
-        <v>86</v>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
           <t>['odunsu', 'aromatik', 'kehribar', 'sıcak baharatlı', 'çiçeksi', 'taze baharatlı', 'acı', 'tatlı', 'anason', 'hafif baharatlı']</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr">
+      <c r="D206" t="inlineStr">
         <is>
           <t>Christian Lacroix AbsynthebyAvon, kadınlar için aromatik bir kokudur. Christian Lacroix Absynthe, 2009 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Laurent Le Guernec'tir. Üst notalarda pelin otu, anason ve frezya; orta notalarda safran, nergis, artemisia ve orkide; alt notalarda odunsu notalar, mür, abanoz ağacı ve kehribar bulunur.</t>
         </is>
@@ -6603,20 +4909,12 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Christian Lacroix Absynthe Avonfor women</t>
-        </is>
-      </c>
-      <c r="D207" t="n">
-        <v>86</v>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>['odunsu', 'aromatik', 'kehribar', 'sıcak baharatlı', 'çiçeksi', 'taze baharatlı', 'acı', 'tatlı', 'anason', 'hafif baharatlı']</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>Christian Lacroix AbsynthebyAvon, kadınlar için aromatik bir kokudur. Christian Lacroix Absynthe, 2009 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Laurent Le Guernec'tir. Üst notalarda pelin otu, anason ve frezya; orta notalarda safran, nergis, artemisia ve orkide; alt notalarda odunsu notalar, mür, abanoz ağacı ve kehribar bulunur.</t>
+          <t>['vanilya', 'beyaz çiçeksi', 'tatlı', 'meyveli', 'kehribar', 'aromatik', 'turunçgil', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Dior AddictbyDior, kadınlar için Amber Floral bir kokudur. Dior Addict, 2002 yılında piyasaya sürülmüştür. Thierry Wasser ve Christian Dussoulier tarafından yaratılmıştır. Üst notalarda Böğürtlen, Mandalina Yaprağı ve İpek Ağacı çiçeği; orta notalarda Yasemin, Portakal Çiçeği, Gece Açan Cereus ve Gül; alt notalarda Vanilya, Tonka Fasulyesi ve Mysore Sandal Ağacı bulunur.</t>
         </is>
       </c>
     </row>
@@ -6633,20 +4931,12 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Azzaro by Parfums Loris Azzaro 1975 Azzarofor women</t>
-        </is>
-      </c>
-      <c r="D208" t="n">
-        <v>86</v>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>['kehribar', 'odunsu', 'beyaz çiçeksi', 'topraksı', 'yosunlu', 'süsen', 'meyveli', 'tatlı', 'gül', 'sarı çiçeksi']</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>Parfums Loris Azzaro 1975 by Azzaro, kadınlar için odunsu bir şipre kokusudur. Parfums Loris Azzaro 1975, 1975 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Jean Martel'dir. Üst notalarda meyveli notalar, gardenya ve aldehitler; orta notalarda süsen kökü, yasemin, gül ve ylang-ylang; alt notalarda meşe yosunu, vetiver, styrax, benzoin, amber ve paçuli bulunur.</t>
+          <t>['aromatik', 'taze baharatlı', 'yeşil', 'deniz', 'odunsu', 'turunçgil', 'su']</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Azzaro Chrome AquabyAzzaro, erkekler için Aromatik Su Kokusu'dur. Azzaro Chrome Aqua, 2019 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Jean-Christophe Hérault. Üst notalarda Greyfurt, Yeşil Elma ve Menekşe Yaprağı; orta notalarda Deniz Notaları, Fesleğen ve Nane; alt notalarda Selvi ve Vetiver bulunur.</t>
         </is>
       </c>
     </row>
@@ -6663,20 +4953,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Urbanist Homme Al Haramain Perfumesfor men</t>
-        </is>
-      </c>
-      <c r="D209" t="n">
-        <v>86</v>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>['aromatik', 'turunçgil', 'odunsu', 'taze baharatlı', 'kehribar', 'pudramsı', 'misk', 'beyaz çiçeksi', 'lavanta', 'tatlı']</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>Urbanist Hommeby Al Haramain Perfumesis, erkekler için Amber ve Baharatlı bir koku. Bu kokunun arkasındaki isim Christian Carbonnel. Üst notalarda Petitgrain, Portakal ve Limon; orta notalarda Lavanta, Biberiye ve Yasemin; alt notalarda Amber, Misk, Sandal Ağacı ve Tonka Fasulyesi bulunuyor.</t>
+          <t>['turunçgil', 'aromatik', 'sıcak baharatlı', 'odunsu', 'taze baharatlı', 'taze']</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Dior Homme SportbyDior, erkekler için odunsu aromatik bir kokudur. Dior Homme Sport, 2008 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim François Demachy'dir. Üst notalarda Amalfi Limonu, Greyfurt, Bergamot ve Elemi reçinesi; orta notalarda Zencefil, Vetiver ve Virginia Sediri; alt notalarda Lavanta, Biberiye ve Sandal Ağacı bulunur.</t>
         </is>
       </c>
     </row>
@@ -6693,18 +4975,10 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Christian Lacroix Absynthe Avonfor women</t>
-        </is>
-      </c>
-      <c r="D210" t="n">
-        <v>86</v>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
           <t>['odunsu', 'aromatik', 'kehribar', 'sıcak baharatlı', 'çiçeksi', 'taze baharatlı', 'acı', 'tatlı', 'anason', 'hafif baharatlı']</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
+      <c r="D210" t="inlineStr">
         <is>
           <t>Christian Lacroix AbsynthebyAvon, kadınlar için aromatik bir kokudur. Christian Lacroix Absynthe, 2009 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Laurent Le Guernec'tir. Üst notalarda pelin otu, anason ve frezya; orta notalarda safran, nergis, artemisia ve orkide; alt notalarda odunsu notalar, mür, abanoz ağacı ve kehribar bulunur.</t>
         </is>
@@ -6723,20 +4997,12 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>L'Aventure Intense Al Haramain Perfumesfor men</t>
-        </is>
-      </c>
-      <c r="D211" t="n">
-        <v>86</v>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'odunsu', 'aromatik', 'taze baharatlı', 'misk']</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>Al Haramain Perfumesi tarafından üretilen L'Aventure Intense, erkekler için Chypre Floral bir kokudur. L'Aventure Intense, 2019 yılında piyasaya sürülmüştür. Üst notalarda Bergamot, Limon ve Elemi; orta notalarda Odunsu Notalar, Yasemin ve Vadi Zambağı; alt notalarda Misk, Amber ve Paçuli bulunmaktadır.</t>
+          <t>['pudramsı', 'iris', 'vanilya', 'odunsu', 'kehribar', 'topraksı', 'menekşe']</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Dior Homme Intense 2007 by Dioris erkekler için çiçeksi odunsu misk kokusu. Dior Homme Intense 2007 2007 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim François Demachy.</t>
         </is>
       </c>
     </row>
@@ -6753,18 +5019,10 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Christian Lacroix Absynthe Avonfor women</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>86</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
           <t>['odunsu', 'aromatik', 'kehribar', 'sıcak baharatlı', 'çiçeksi', 'taze baharatlı', 'acı', 'tatlı', 'anason', 'hafif baharatlı']</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr">
+      <c r="D212" t="inlineStr">
         <is>
           <t>Christian Lacroix AbsynthebyAvon, kadınlar için aromatik bir kokudur. Christian Lacroix Absynthe, 2009 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Laurent Le Guernec'tir. Üst notalarda pelin otu, anason ve frezya; orta notalarda safran, nergis, artemisia ve orkide; alt notalarda odunsu notalar, mür, abanoz ağacı ve kehribar bulunur.</t>
         </is>
@@ -6783,20 +5041,12 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Mademoiselle Azzaro L'Intense Eau de Parfum Azzarofor women</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>86</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>['beyaz çiçeksi', 'meyveli', 'tatlı', 'su', 'taze']</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>Azzaro'nun Mademoiselle Azzaro L'Intense Eau de Parfum, kadınlar için Çiçeksi Meyveli Gourmand kokusudur. Mademoiselle Azzaro L'Intense Eau de Parfum 2021 yılında piyasaya sürüldü. Üst nota Armut; orta notada Beyaz Çiçekler; temel nota Calissons d'Aix'tir.</t>
+          <t>['beyaz çiçeksi', 'çiçeksi', 'taze', 'meyveli', 'turunçgil', 'gül', 'tatlı', 'pudramsı', 'süsen', 'odunsu']</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>MademoisellebyAzzaro, kadınlar için çiçeksi ve meyveli bir kokudur. Mademoiselle, 2015 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Karine Dubreuil-Sereni'dir. Üst notalarda Şeftali ve Mandalina Çiçeği; orta notalarda Şakayık, Yasemin ve Portakal Çiçeği; alt notalarda Süsen ve Odunsu Notalar bulunur.</t>
         </is>
       </c>
     </row>
@@ -6813,20 +5063,12 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Musk Al Ghazal Eau de Parfum Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>86</v>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>['misk', 'sıcak baharatlı', 'taze baharatlı', 'tatlı', 'anason', 'pudramsı', 'çikolata', 'hafif baharatlı', 'aromatik', 'vanilya']</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>Musk Al Ghazal Eau de ParfumbyAl Haramain Perfumesis, kadınlar ve erkekler için bir Amber kokusudur. Üst notalarda kimyon ve anason; orta notalarda misk; alt notalarda baharatlar, bitter çikolata, odunsu notalar ve vanilya bulunur.</t>
+          <t>['turunçgil', 'kehribar', 'odunsu', 'sıcak baharatlı', 'aromatik', 'taze baharatlı', 'dumanlı', 'balzamik', 'taze', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Bleu de Chanel Eau de Parfum, erkekler için odunsu aromatik bir kokudur. Bleu de Chanel Eau de Parfum, 2014 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki burun Jacques Polge'dir. Üst notalarda Greyfurt, Limon, Nane, Pembe Biber, Bergamot, Aldehitler ve Kişniş; orta notalarda Zencefil, Hindistan Cevizi, Yasemin ve Kavun; alt notalarda Tütsü, Kehribar, Sedir, Sandal Ağacı, Paçuli, Kehribar Ağacı ve Laden bulunur.</t>
         </is>
       </c>
     </row>
@@ -6843,20 +5085,12 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Musk Al Ghazal Eau de Parfum Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>86</v>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>['misk', 'sıcak baharatlı', 'taze baharatlı', 'tatlı', 'anason', 'pudramsı', 'çikolata', 'hafif baharatlı', 'aromatik', 'vanilya']</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>Musk Al Ghazal Eau de ParfumbyAl Haramain Perfumesis, kadınlar ve erkekler için bir Amber kokusudur. Üst notalarda kimyon ve anason; orta notalarda misk; alt notalarda baharatlar, bitter çikolata, odunsu notalar ve vanilya bulunur.</t>
+          <t>['turunçgil', 'kehribar', 'odunsu', 'sıcak baharatlı', 'aromatik', 'taze baharatlı', 'dumanlı', 'balzamik', 'taze', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Bleu de Chanel Eau de Parfum, erkekler için odunsu aromatik bir kokudur. Bleu de Chanel Eau de Parfum, 2014 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki burun Jacques Polge'dir. Üst notalarda Greyfurt, Limon, Nane, Pembe Biber, Bergamot, Aldehitler ve Kişniş; orta notalarda Zencefil, Hindistan Cevizi, Yasemin ve Kavun; alt notalarda Tütsü, Kehribar, Sedir, Sandal Ağacı, Paçuli, Kehribar Ağacı ve Laden bulunur.</t>
         </is>
       </c>
     </row>
@@ -6873,20 +5107,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Chanel No 5 Eau de Cologne Chanelfor women</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>90</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>['pudramsı', 'odunsu', 'misk', 'beyaz çiçeksi', 'topraksı', 'süsen', 'hayvansal', 'aldehitli', 'taze', 'kehribar']</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>Chanel No. 5 Eau de Cologneby, kadınlar için çiçeksi bir aldehit kokusudur. Bu kokunun arkasındaki isim Ernest Beaux'dur. Üst notalarda Aldehitler, Ylang-Ylang, Afrika Portakal Çiçeği, Bergamot ve Amalfi Limonu; orta notalarda Süsen, Yasemin, Gül, Süsen Kökü ve Vadi Zambağı; alt notalarda Civetta, Misk, Amber, Sandal Ağacı, Vetiver, Meşe Yosunu, Paçuli ve Vanilya bulunur.</t>
+          <t>['beyaz çiçeksi', 'odunsu', 'pudramsı', 'turunçgil', 'taze baharatlı', 'çiçeksi', 'süsen', 'gül', 'sarı çiçeksi', 'misk']</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Chanel No 46 by Chanel, kadınlar için çiçeksi odunsu misk kokusudur. Chanel No 46, 1946 yılında piyasaya sürülmüştür. Üst notalarda Bergamot, Portakal Çiçeği ve Portakal; orta notalarda Ylang-Ylang, Gül, Yasemin ve Vadi Zambağı; alt notalarda Süsen Kökü, Misk, Sandal Ağacı, Vanilya, Kimyon ve Vetiver bulunur.</t>
         </is>
       </c>
     </row>
@@ -6903,20 +5129,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Musk Al Ghazal Eau de Parfum Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>86</v>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>['misk', 'sıcak baharatlı', 'taze baharatlı', 'tatlı', 'anason', 'pudramsı', 'çikolata', 'hafif baharatlı', 'aromatik', 'vanilya']</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>Musk Al Ghazal Eau de ParfumbyAl Haramain Perfumesis, kadınlar ve erkekler için bir Amber kokusudur. Üst notalarda kimyon ve anason; orta notalarda misk; alt notalarda baharatlar, bitter çikolata, odunsu notalar ve vanilya bulunur.</t>
+          <t>['turunçgil', 'çiçeksi', 'taze', 'misk', 'aromatik', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Little Black Dress Eau FraichebyAvon, kadınlar için çiçeksi ve meyveli bir kokudur. Little Black Dress Eau Fraiche, 2015 yılında piyasaya sürülmüştür. Üst notalarda Limon ve Greyfurt; orta notalarda Çiçekler ve Şakayık; temel notalarda Misk bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -6933,20 +5151,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Musk Al Ghazal Eau de Parfum Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>86</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>['misk', 'sıcak baharatlı', 'taze baharatlı', 'tatlı', 'anason', 'pudramsı', 'çikolata', 'hafif baharatlı', 'aromatik', 'vanilya']</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>Musk Al Ghazal Eau de ParfumbyAl Haramain Perfumesis, kadınlar ve erkekler için bir Amber kokusudur. Üst notalarda kimyon ve anason; orta notalarda misk; alt notalarda baharatlar, bitter çikolata, odunsu notalar ve vanilya bulunur.</t>
+          <t>['çiçeksi', 'gül', 'taze', 'meyveli', 'beyaz çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Chloe Eau de ParfumbyChloé, kadınlar için çiçeksi bir kokudur. Chloe Eau de Parfum, 2008 yılında piyasaya sürülmüştür. Chloe Eau de Parfum, Amandine Clerc-Marie ve Michel Almairac tarafından yaratılmıştır. Üst notalarda Şakayık, Litchi ve Frezya; orta notalarda Gül, Vadi Zambağı ve Manolya; alt notalarda Virginia Sediri ve Amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -6963,20 +5173,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Egoiste Platinum Chanelfor men</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>87</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>['aromatik', 'taze baharatlı', 'odunsu', 'lavanta', 'yeşil', 'bitkisel']</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>Chanel'in Egoiste Platinum'u erkekler için odunsu ve çiçeksi bir misk kokusudur. Egoiste Platinum, 1993 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Jacques Polge'dir. Üst notalarda Lavanta, Biberiye, Portakal Çiçeği ve Turunçgil; orta notalarda Sardunya, Adaçayı, Galbanum ve Yasemin; alt notalarda Meşe Yosunu, Vetiver, Sedir, Sandal Ağacı ve Amber bulunur.</t>
+          <t>['beyaz çiçeksi', 'odunsu', 'pudramsı', 'turunçgil', 'taze baharatlı', 'çiçeksi', 'süsen', 'gül', 'sarı çiçeksi', 'misk']</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Chanel No 46 by Chanel, kadınlar için çiçeksi odunsu misk kokusudur. Chanel No 46, 1946 yılında piyasaya sürülmüştür. Üst notalarda Bergamot, Portakal Çiçeği ve Portakal; orta notalarda Ylang-Ylang, Gül, Yasemin ve Vadi Zambağı; alt notalarda Süsen Kökü, Misk, Sandal Ağacı, Vanilya, Kimyon ve Vetiver bulunur.</t>
         </is>
       </c>
     </row>
@@ -6993,20 +5195,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>9am Dive Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>86</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'odunsu', 'yeşil', 'sıcak baharatlı', 'aromatik', 'turunçgil', 'taze', 'taze baharatlı', 'hafif baharatlı', 'kehribar']</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>9am DivebyAfna, kadınlar ve erkekler için Aromatik Su Kokusu'dur. Bu yeni bir kokudur. 9am Dive, 2022 yılında piyasaya sürüldü. Üst notalarda Limon, Nane, Siyah Frenk Üzümü ve Pembe Biber; orta notalarda Elma, Tütsü ve Sedir; alt notalarda Zencefil, Sandal Ağacı, Paçuli ve Yasemin bulunur.</t>
+          <t>['balzamik']</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Lotus Çiçeği ve Kral Ejderhaby Kilian kadınlar ve erkekler için narenciye aromalı bir kokudur. Lotus Çiçeği ve Kral Ejderha 2015 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Calice Becker'dır.</t>
         </is>
       </c>
     </row>
@@ -7023,18 +5217,10 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Emporio Armani Stronger With You Giorgio Armanifor men</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>90</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
           <t>['vanilya', 'balzamik', 'fındıksı', 'tatlı', 'aromatik', 'pudramsı', 'hafif baharatlı', 'bitkisel', 'sıcak baharatlı', 'lavanta']</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>Giorgio Armani'nin Emporio Armani Stronger With You adlı parfümü, erkekler için aromatik bir Fougere kokusudur. Emporio Armani Stronger With You, 2017 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Cecile Matton'dır. Üst notalarda Kestane ve Şeker; orta notalarda Adaçayı ve Lavanta; alt notalarda Vanilya ve Duman bulunur.</t>
         </is>
@@ -7053,18 +5239,10 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>New World Avonfor men</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>86</v>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
           <t>['odunsu', 'kehribar', 'yosunlu', 'topraksı', 'misk']</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr">
+      <c r="D222" t="inlineStr">
         <is>
           <t>New WorldbyAvon, erkekler için Amber Woody notalı bir parfümdür. New World, 1980'lerde piyasaya sürülmüştür.</t>
         </is>
@@ -7083,20 +5261,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>9pm Afnanfor men</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>86</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>['vanilya', 'kehribar', 'sıcak baharatlı', 'tarçın', 'tatlı', 'meyvemsi', 'pudramsı', 'lavanta', 'aromatik', 'taze']</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>9pmbyAfnani erkekler için Amber Vanilya kokusu. 9pm, 2020 yılında piyasaya sürüldü. Üst notalarda Elma, Tarçın, Yabani Lavanta ve Bergamot; orta notalarda Portakal Çiçeği ve Vadi Zambağı; alt notalarda Vanilya, Tonka Fasulyesi, Amber ve Paçuli bulunuyor.</t>
+          <t>['kehribar', 'beyaz çiçeksi', 'odunsu', 'hayvansal']</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Thierry Mugler Show Collection: Alien Couture Stoneby Mugler kadınlara yönelik bir parfümdür. Thierry Mugler Show Collection: Alien Couture Stone, 2010 yılında piyasaya sürülmüştür. Thierry Mugler Show Collection: Alien Couture Stone, Dominique Ropion ve Laurent Bruyere tarafından yaratılmıştır.</t>
         </is>
       </c>
     </row>
@@ -7113,20 +5283,12 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Naseej Al Kiswah Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>86</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>['odunsu', 'kehribar', 'deri', 'ud', 'paçuli', 'hayvansal', 'vanilya', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>Naseej Al KiswahbyAfnani, Kadınlar ve Erkekler için Amber Woody Kokusudur. orta notalarda Woodsy Notes ve Sedir; temel notalar Amber, Deri ve Agarwood'dur (Ud).</t>
+          <t>['misk', 'lavanta', 'aromatik', 'kehribar', 'bitkisel', 'yosunlu', 'gül', 'pudramsı', 'topraksı', 'hafif baharatlı']</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>WeekendbyAvon erkeklere yönelik bir parfümdür. Weekend 1978 yılında piyasaya sürülmüştür.</t>
         </is>
       </c>
     </row>
@@ -7143,20 +5305,12 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Naseej Al Kiswah Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>86</v>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>['odunsu', 'kehribar', 'deri', 'ud', 'paçuli', 'hayvansal', 'vanilya', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>Naseej Al KiswahbyAfnani, Kadınlar ve Erkekler için Amber Woody Kokusudur. orta notalarda Woodsy Notes ve Sedir; temel notalar Amber, Deri ve Agarwood'dur (Ud).</t>
+          <t>['vanilya', 'beyaz çiçeksi', 'odunsu', 'meyvemsi', 'pudramsı', 'tatlı', 'turunçgil', 'sümbülteber', 'kehribar', 'paçuli']</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Al Haramain Perfumesis tarafından üretilen Prism Classic, kadınlara özel Amber Floral bir kokudur. Üst notalarda Bergamot, Şeftali ve Mirabelle; orta notalarda Menekşe Yaprakları, Yasemin ve Sümbülteber; alt notalarda Vanilya, Paçuli, Sandal Ağacı ve Ambroxan bulunur.</t>
         </is>
       </c>
     </row>
@@ -7173,20 +5327,12 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Naseej Al Kiswah Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>86</v>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>['odunsu', 'kehribar', 'deri', 'ud', 'paçuli', 'hayvansal', 'vanilya', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>Naseej Al KiswahbyAfnani, Kadınlar ve Erkekler için Amber Woody Kokusudur. orta notalarda Woodsy Notes ve Sedir; temel notalar Amber, Deri ve Agarwood'dur (Ud).</t>
+          <t>['vanilya', 'beyaz çiçeksi', 'odunsu', 'meyvemsi', 'pudramsı', 'tatlı', 'turunçgil', 'sümbülteber', 'kehribar', 'paçuli']</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Al Haramain Perfumesis tarafından üretilen Prism Classic, kadınlara özel Amber Floral bir kokudur. Üst notalarda Bergamot, Şeftali ve Mirabelle; orta notalarda Menekşe Yaprakları, Yasemin ve Sümbülteber; alt notalarda Vanilya, Paçuli, Sandal Ağacı ve Ambroxan bulunur.</t>
         </is>
       </c>
     </row>
@@ -7203,20 +5349,12 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Naseej Al Kiswah Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D227" t="n">
-        <v>86</v>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>['odunsu', 'kehribar', 'deri', 'ud', 'paçuli', 'hayvansal', 'vanilya', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>Naseej Al KiswahbyAfnani, Kadınlar ve Erkekler için Amber Woody Kokusudur. orta notalarda Woodsy Notes ve Sedir; temel notalar Amber, Deri ve Agarwood'dur (Ud).</t>
+          <t>['turunçgil', 'beyaz çiçeksi', 'odunsu', 'tatlı', 'meyveli', 'pudramsı', 'tropikal', 'taze', 'gül', 'kehribar']</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Allure of LovebyAl-Rehabi, kadınlar için bir Citrus Gourmand kokusudur. Bu yeni bir kokudur. Allure of Love, 2024 yılında piyasaya sürülmüştür. Üst notalarda Portakal Yağı, Bergamot, Hindistan Cevizi, Şeftali ve İtalyan Mandalinası; orta notalarda Vadi Zambağı, Tropikal Meyveler, Portakal Çiçeği, Yasemin ve Gül; alt notalarda Sandal Ağacı, Paçuli, Sedir Ağacı, Amber ve Misk bulunur.</t>
         </is>
       </c>
     </row>
@@ -7233,18 +5371,10 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Love Story Chloéfor women</t>
-        </is>
-      </c>
-      <c r="D228" t="n">
-        <v>87</v>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
           <t>['beyaz çiçeksi', 'turunçgil', 'misk', 'meyveli', 'tatlı', 'taze baharatlı', 'odunsu', 'gül', 'taze', 'pudramsı']</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr">
+      <c r="D228" t="inlineStr">
         <is>
           <t>Love StorybyChloé, kadınlar için çiçeksi bir kokudur. Love Story, 2014 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Anne Flipo'dur. Üst notalarda Neroli, Armut, Bergamot, Greyfurt ve Limon; orta notalarda Portakal Çiçeği, Stephanotis, Gül, Şeftali ve Siyah Frenk Üzümü; alt notalarda Misk, Sedir, Kaşmir Ağacı ve Paçuli bulunur.</t>
         </is>
@@ -7263,20 +5393,12 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Black XS Paco Rabannefor men</t>
-        </is>
-      </c>
-      <c r="D229" t="n">
-        <v>90</v>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>['tatlı', 'sıcak baharatlı', 'turunçgil', 'kehribar', 'aromatik', 'odunsu', 'balzamik', 'tarçın', 'paçuli', 'laktonik']</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>Black XSbyPaco Rabanne erkekler için Amber Woody bir kokudur. Black XS, 2005 yılında piyasaya sürülmüştür. Black XS, Olivier Cresp, Rosendo Mateu ve Christian Dussoulier tarafından yaratılmıştır. Üst notalarda Limon ve Adaçayı; orta notalarda Pralin, Tarçın, Tolu Balsamı ve Siyah Kakule; alt notalarda Brezilya Gül Ağacı, Paçuli ve Siyah Amber bulunur.</t>
+          <t>['taze baharatlı', 'aromatik', 'turunçgil', 'odunsu', 'lavanta', 'kehribar', 'yeşil', 'topraksı', 'bitkisel', 'dumanlı']</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Eau Paco Rabanne, erkekler için aromatik bir Fougere kokusudur. Eau Paco Rabanne, 2002 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Olivier Cresp'tir. Üst notalarda Bergamot, Lavanta, Limon ve Portakal Çiçeği; orta notalarda Fesleğen, Vetiver, Biber ve Değerli Ağaçlar; alt notalarda Tütsü, Meşe Yosunu, Misk, Sandal Ağacı, Amber ve Deri bulunur.</t>
         </is>
       </c>
     </row>
@@ -7293,20 +5415,12 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Wanted Azzarofor men</t>
-        </is>
-      </c>
-      <c r="D230" t="n">
-        <v>87</v>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>['aromatik', 'sıcak baharatlı', 'turunçgil', 'kehribar', 'odunsu', 'taze baharatlı', 'taze', 'yeşil', 'vanilya', 'meyveli']</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>WantedbyAzzaro, erkekler için odunsu ve baharatlı bir kokudur. Wanted, 2016 yılında piyasaya sürüldü. Fabrice Pellegrin ve Olivier Cresp tarafından yaratıldı. Üst notalarda Limon, Zencefil, Lavanta ve Nane; orta notalarda Elma, Ardıç, Guatemala Kakule ve Sardunya; alt notalarda Tonka Fasulyesi, Amber Ağacı ve Haiti Vetiver'i bulunur.</t>
+          <t>['çiçeksi', 'beyaz çiçeksi', 'sarı çiçeksi', 'odunsu', 'yeşil', 'tatlı', 'pudramsı', 'taze', 'topraksı', 'turunçgil']</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Azzaro 9byAzzaro, kadınlar için çiçeksi bir kokudur. Azzaro 9, 1984 yılında piyasaya sürülmüştür. Üst notalarda Aldehitler, Ananas, Mandalina ve Bergamot; orta notalarda Mimoza, Mimoza Yaprakları, Lale, Morsalkım, Zambak, Sümbülteber, Boyacı Yeşil Otu, Ylang-Ylang, Sümbül, Yasemin, Karanfil, Vadi Zambağı, Gül, Menekşe Yaprağı, Portakal Çiçeği ve Fesleğen; alt notalarda Meşe Yosunu, Süsen, Tütsü, Ambrette (Misk Ebegümeci), Sandal Ağacı, Vetiver, Vanilya, Sedir ve Misk bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -7323,18 +5437,10 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Good Girl Carolina Herrerafor women</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
-        <v>91</v>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
           <t>['tatlı', 'beyaz çiçeksi', 'sıcak baharatlı', 'vanilya', 'kakao', 'kehribar', 'odunsu', 'sümbülteber', 'badem', 'pudramsı']</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr">
+      <c r="D231" t="inlineStr">
         <is>
           <t>Good Girl by Carolina Herrera, kadınlar için Amber Floral bir kokudur. Good Girl, 2016 yılında piyasaya sürülmüştür. Good Girl, Louise Turner ve Quentin Bisch tarafından yaratılmıştır. Üst notalarda Badem, Kahve, Bergamot ve Limon; orta notalarda Sümbülteber, Yasemin Sambac, Portakal Çiçeği, Süsen ve Bulgar Gülü; alt notalarda Tonka Fasulyesi, Kakao, Vanilya, Pralin, Sandal Ağacı, Misk, Amber, Kaşmir Ağacı, Tarçın, Paçuli ve Sedir bulunur.</t>
         </is>
@@ -7353,20 +5459,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Naseej Al Kiswah Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D232" t="n">
-        <v>86</v>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>['odunsu', 'kehribar', 'deri', 'ud', 'paçuli', 'hayvansal', 'vanilya', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>Naseej Al KiswahbyAfnani, Kadınlar ve Erkekler için Amber Woody Kokusudur. orta notalarda Woodsy Notes ve Sedir; temel notalar Amber, Deri ve Agarwood'dur (Ud).</t>
+          <t>['yeşil', 'aromatik', 'odunsu', 'balzamik', 'kehribar', 'yosunlu', 'çiçeksi', 'tatlı', 'beyaz çiçeksi', 'topraksı']</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>ArmanibyGiorgio Armani, kadınlar için bir Chypre Floral parfümüdür. Armani, 1981 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Ron Winnegrad'dır. Üst notalarda Galbanum, Kadife Çiçeği, Aldehitler, Ananas, Bergamot ve Nane; orta notalarda Nergis, Süsen Kökü, Sümbülteber, Gül, Yasemin, Siklamen, Vadi Zambağı ve Orkide; alt notalarda Meşe Yosunu, Benzoin, Sedir, Kehribar, Sandal Ağacı, Tonka Fasulyesi ve Misk bulunur.</t>
         </is>
       </c>
     </row>
@@ -7383,20 +5481,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>9am Dive Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D233" t="n">
-        <v>86</v>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'odunsu', 'yeşil', 'sıcak baharatlı', 'aromatik', 'turunçgil', 'taze', 'taze baharatlı', 'hafif baharatlı', 'kehribar']</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>9am DivebyAfna, kadınlar ve erkekler için Aromatik Su Kokusu'dur. Bu yeni bir kokudur. 9am Dive, 2022 yılında piyasaya sürüldü. Üst notalarda Limon, Nane, Siyah Frenk Üzümü ve Pembe Biber; orta notalarda Elma, Tütsü ve Sedir; alt notalarda Zencefil, Sandal Ağacı, Paçuli ve Yasemin bulunur.</t>
+          <t>['çiçeksi', 'hafif baharatlı', 'meyvemsi', 'tatlı', 'paçuli', 'taze', 'turunçgil', 'kehribar', 'taze baharatlı', 'misk']</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Gucci GuiltybyGucci, kadınlar için Amber Floral bir kokudur. Gucci Guilty, 2010 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Aurélien Guichard'dır. Üst notalarda Pembe Biber, Mandalina ve Bergamot; orta notalarda Leylak, Şeftali, Sardunya, Yasemin ve Siyah Frenk Üzümü; alt notalarda Paçuli, Amber, Beyaz Misk ve Vanilya bulunur.</t>
         </is>
       </c>
     </row>
@@ -7413,20 +5503,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>9am Afnanfor women</t>
-        </is>
-      </c>
-      <c r="D234" t="n">
-        <v>86</v>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'misk', 'odunsu', 'aromatik', 'sıcak baharatlı', 'lavanta', 'yosunlu', 'meyveli', 'topraksı', 'beyaz çiçeksi']</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>9ambyAfnani kadınlara özel bir parfüm. Üst notalarda Limon, Mandalina, Kakule ve Pembe Biber; orta notalarda Lavanta, Yeşil Elma, Portakal Çiçeği ve Gül; alt notalarda Misk, Yosun, Sedir ve Paçuli bulunuyor.</t>
+          <t>['vanilya', 'tatlı', 'badem', 'meyveli', 'fındıksı', 'pudralı', 'odunsu', 'hindistan cevizi', 'beyaz çiçeksi', 'balzamik']</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Dioris Hypnotic Poison, kadınlar için Amber Vanilya aromalı bir parfümdür. Hypnotic Poison, 1998 yılında piyasaya sürülmüştür. Annick Menardo ve Christian Dussoulier tarafından yaratılmıştır. Üst notalarda Hindistan Cevizi, Erik ve Kayısı; orta notalarda Brezilya Gül Ağacı, Yasemin, Kimyon, Sümbülteber, Gül ve Vadi Zambağı; alt notalarda Vanilya, Badem, Sandal Ağacı ve Misk bulunur.</t>
         </is>
       </c>
     </row>
@@ -7443,18 +5525,10 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Insense Ultramarine Givenchyfor men</t>
-        </is>
-      </c>
-      <c r="D235" t="n">
-        <v>91</v>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
           <t>['aromatik', 'çiçeksi', 'yeşil', 'meyvemsi', 'odunsu', 'ozonik', 'sucul', 'sıcak baharatlı', 'turunçgil', 'süsen']</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>Givench'in Insense Ultramarine'i erkekler için aromatik meyveli bir kokudur. Insense Ultramarine, 1994 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Christian Mathieu'dur. Üst notalarda Siyah Frenk Üzümü, Karpuz, Galbanum ve Bergamot; orta notalarda Süsen, Manolya, Nane, Karanfil, Vadi Zambağı, Kakule ve Adaçayı; alt notalarda Tütün, Vetiver ve Sedir bulunur.</t>
         </is>
@@ -7473,20 +5547,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Bvlgari Man In Black Bvlgarifor men</t>
-        </is>
-      </c>
-      <c r="D236" t="n">
-        <v>95</v>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>['sıcak baharatlı', 'odunsu', 'deri', 'rom', 'kehribar', 'tatlı', 'tütün', 'vanilya', 'hayvansal', 'süsen']</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>Bvlgari Man In BlackbyBvlgari, erkekler için Amber Floral bir kokudur. Bvlgari Man In Black, 2014 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Alberto Morillas. Üst notalarda baharatlar, rom ve tütün; orta notalarda deri, süsen ve sümbülteber; alt notalarda tonka fasulyesi, guaiac ağacı ve benzoin bulunur.</t>
+          <t>['deri', 'ud', 'sıcak baharatlı', 'rom', 'hayvansal', 'gül', 'sümbülteber', 'aromatik', 'dumanlı', 'beyaz çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Bvlgari Man Black Orient, erkekler için Amber Woody bir kokudur. Bvlgari Man Black Orient, 2016 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Alberto Morillas'tır. Üst notalarda Rom ve Kakule; orta notalarda Taif Gülü ve Sümbülteber; alt notalarda Deri ve Öd Ağacı bulunur.</t>
         </is>
       </c>
     </row>
@@ -7503,18 +5569,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Narciso Rodriguez For Her Hair Mist Narciso Rodriguezfor women</t>
-        </is>
-      </c>
-      <c r="D237" t="n">
-        <v>95</v>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>['pudramsı', 'misk', 'süsen', 'gül']</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr"/>
+          <t>['gül', 'misk', 'odunsu', 'pudramsı', 'turunçgil', 'hafif baharatlı', 'çiçeksi', 'paçuli', 'tatlı']</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Narciso Rodriguez Fleur Musc Eau De Toilette Florale, kadınlar için çiçeksi odunsu misk kokusudur. Narciso Rodriguez Fleur Musc Eau De Toilette Florale, 2020 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Sonia Constant'tır. Üst notalarda Pembe Biber ve Bergamot; orta notalarda Gül ve Misk; alt notalarda ise Odunsu Notalar, Paçuli ve Amber bulunur.</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -7529,20 +5591,12 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Narciso Narciso Rodriguezfor women</t>
-        </is>
-      </c>
-      <c r="D238" t="n">
-        <v>89</v>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>['odunsu', 'misk', 'beyaz çiçeksi', 'pudramsı', 'aromatik', 'laktonik', 'gül', 'hayvansal', 'topraksı']</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>NarcisobyNarciso Rodriguez, kadınlar için çiçeksi odunsu misk kokusudur. Narciso, 2014 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Aurélien Guichard'dır. Üst notalarda Gardenya ve Beyaz Gül; orta notalarda Misk; alt notalarda Beyaz Sedir Özü, Sedir ve Vetiver bulunur.</t>
+          <t>['gül', 'misk', 'odunsu', 'pudramsı', 'turunçgil', 'hafif baharatlı', 'çiçeksi', 'paçuli', 'tatlı']</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Narciso Rodriguez Fleur Musc Eau De Toilette Florale, kadınlar için çiçeksi odunsu misk kokusudur. Narciso Rodriguez Fleur Musc Eau De Toilette Florale, 2020 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Sonia Constant'tır. Üst notalarda Pembe Biber ve Bergamot; orta notalarda Gül ve Misk; alt notalarda ise Odunsu Notalar, Paçuli ve Amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -7559,20 +5613,12 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Le Male Jean Paul Gaultierfor men</t>
-        </is>
-      </c>
-      <c r="D239" t="n">
-        <v>87</v>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>['aromatik', 'vanilya', 'taze baharatlı', 'lavanta', 'sıcak baharatlı', 'yeşil', 'pudramsı', 'tatlı', 'kehribar', 'tarçın']</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>Le Maleby Jean Paul Gaultier, erkekler için bir Amber Fougere kokusudur. Le Male, 1995 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Francis Kurkdjian'dır. Üst notalarda Lavanta, Nane, Kakule, Bergamot ve Artemisia; orta notalarda Tarçın, Portakal Çiçeği ve Kimyon; alt notalarda Vanilya, Tonka Fasulyesi, Amber, Sandal Ağacı ve Sedir bulunur.</t>
+          <t>['beyaz çiçeksi', 'tatlı', 'turunçgil', 'vanilya', 'meyveli', 'misk']</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Jean Paul Gaultier imzalı Classique Eau Fraîche Gaultier Airlines, kadınlar için Amber Floral bir kokudur. Classique Eau Fraîche Gaultier Airlines, 2018 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Daphné Bugey'dir. Üst notalarda Şerbet, Şeker Kamışı, Limon ve Zencefil; orta notalarda Tiare Çiçeği, Portakal Çiçeği ve Yasemin; alt notalarda Vanilya, Misk ve Laden bulunur.</t>
         </is>
       </c>
     </row>
@@ -7589,20 +5635,12 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>212 Men Carolina Herrerafor men</t>
-        </is>
-      </c>
-      <c r="D240" t="n">
-        <v>89</v>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'yeşil', 'sıcak baharatlı', 'aromatik', 'odunsu', 'pudramsı', 'taze baharatlı', 'misk', 'lavanta', 'menekşe']</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>212 Men by Carolina Herrera, erkekler için odunsu ve çiçeksi bir misk kokusudur. 212 Men, 1999 yılında piyasaya sürülmüştür. Alberto Morillas, Rosendo Mateu ve Ann Gottlieb tarafından yaratılmıştır. Üst notalarda yeşil notalar, greyfurt, baharatlar, bergamot, lavanta ve turunçgiller; orta notalarda zencefil, menekşe, gardenya ve adaçayı; alt notalarda misk, sandal ağacı, tütsü, vetiver, guaiac ağacı ve labdanum bulunur.</t>
+          <t>['beyaz çiçeksi', 'sümbülteber', 'yeşil', 'hayvansı', 'odunsu', 'sarı çiçeksi', 'misk', 'pudramsı', 'çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Carolina Herrera by Carolina Herrera, kadınlar için çiçeksi bir kokudur. Carolina Herrera by Carolina Herrera, 1988 yılında piyasaya sürülmüştür. Carolina Herrera by Carolina Herrera, Carlos Benaim, Clement Gavarry ve Rosendo Mateu tarafından yaratılmıştır. Üst notalarda Kayısı, Portakal Çiçeği, Yeşil Notalar, Brezilya Gül Ağacı ve Bergamot; orta notalarda Hint Sümbülteberi, Yasemin, İspanyol Yasemini, Ylang-Ylang, Hanımeli, Nergis, Hiacynth ve Vadi Zambağı; alt notalarda Misk Kedisi, Misk, Meşe Yosunu, Kehribar, Sandal Ağacı, Vetiver ve Sedir bulunur.</t>
         </is>
       </c>
     </row>
@@ -7619,20 +5657,12 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Pi Givenchyfor men</t>
-        </is>
-      </c>
-      <c r="D241" t="n">
-        <v>86</v>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>['vanilya', 'kehribar', 'tatlı', 'badem', 'aromatik', 'fındıksı', 'meyvemsi', 'sıcak baharatlı', 'taze baharatlı', 'pudramsı']</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>PibyGivench, erkekler için Amber Woody bir kokudur. Piby 1998 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Alberto Morillas'tır. Üst notalarda Mandalina, Tarhun, Biberiye ve Fesleğen; orta notalarda Anason, Portakal Çiçeği, Sardunya ve Vadi Zambağı; alt notalarda Vanilya, Badem, Tonka Fasulyesi, Benzoin ve Sedir bulunur.</t>
+          <t>['meyvemsi', 'tatlı', 'taze', 'çiçeksi', 'misk', 'yeşil', 'tropikal', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Absolutely GivenchybyGivenchy, kadınlar için çiçeksi ve meyveli bir kokudur. Absolutely Givenchy, 2006 yılında piyasaya sürülmüştür.</t>
         </is>
       </c>
     </row>
@@ -7649,18 +5679,10 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Lui Rochas Rochasfor men</t>
-        </is>
-      </c>
-      <c r="D242" t="n">
-        <v>95</v>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
           <t>['odunsu', 'turunçgil', 'kehribar', 'paçuli', 'vanilya', 'pudramsı', 'aromatik', 'beyaz çiçeksi', 'taze', 'sıcak baharatlı']</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr"/>
+      <c r="D242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -7675,20 +5697,12 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Bombshell Victoria's Secretfor women</t>
-        </is>
-      </c>
-      <c r="D243" t="n">
-        <v>91</v>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'tatlı', 'taze', 'turunçgil', 'çiçeksi', 'tropikal', 'beyaz çiçeksi']</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>BombshellbyVictoria's Secret, kadınlar için çiçeksi ve meyveli bir kokudur. Bombshell, 2010 yılında piyasaya sürüldü. Bombshell, Adriana Medina-Baez ve Mark Knitowski tarafından yaratıldı. Üst notalarda Çarkıfelek Meyvesi, Greyfurt, Ananas, Mandalina ve Büyük Çilek; orta notalarda Şakayık, Vanilya Orkidesi, Kırmızı Meyveler, Yasemin ve Vadi Zambağı; alt notalarda Misk, Odunsu Notalar ve Meşe Yosunu bulunur.</t>
+          <t>['iris', 'pudramsı', 'topraksı', 'menekşe', 'çiçeksi', 'odunsu']</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Victoria's Secret Bombshell Italian Iris Victoria's Secret, kadınlara yönelik çiçeksi bir kokudur. Victoria's Secret Bombshell Italian Iris, 2013 yılında piyasaya sürülmüştür.</t>
         </is>
       </c>
     </row>
@@ -7705,20 +5719,12 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>9am Afnanfor women</t>
-        </is>
-      </c>
-      <c r="D244" t="n">
-        <v>86</v>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'misk', 'odunsu', 'aromatik', 'sıcak baharatlı', 'lavanta', 'yosunlu', 'meyveli', 'topraksı', 'beyaz çiçeksi']</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>9ambyAfnani kadınlara özel bir parfüm. Üst notalarda Limon, Mandalina, Kakule ve Pembe Biber; orta notalarda Lavanta, Yeşil Elma, Portakal Çiçeği ve Gül; alt notalarda Misk, Yosun, Sedir ve Paçuli bulunuyor.</t>
+          <t>['vanilya', 'çiçeksi', 'taze', 'turunçgil', 'meyveli', 'pudramsı', 'tatlı']</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Sexy Little Thing Ooh La Laby Victoria's Secret, kadınlara yönelik çiçeksi bir kokudur. Sexy Little Thing Ooh La Laby, 2008 yılında piyasaya sürülmüştür.</t>
         </is>
       </c>
     </row>
@@ -7735,20 +5741,12 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>9pm Afnanfor men</t>
-        </is>
-      </c>
-      <c r="D245" t="n">
-        <v>86</v>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>['vanilya', 'kehribar', 'sıcak baharatlı', 'tarçın', 'tatlı', 'meyvemsi', 'pudramsı', 'lavanta', 'aromatik', 'taze']</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>9pmbyAfnani erkekler için Amber Vanilya kokusu. 9pm, 2020 yılında piyasaya sürüldü. Üst notalarda Elma, Tarçın, Yabani Lavanta ve Bergamot; orta notalarda Portakal Çiçeği ve Vadi Zambağı; alt notalarda Vanilya, Tonka Fasulyesi, Amber ve Paçuli bulunuyor.</t>
+          <t>['odunsu', 'sıcak baharatlı', 'aromatik', 'turunçgil', 'taze baharatlı', 'paçuli', 'pudramsı', 'hafif baharatlı']</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Hugo Boss'un Boss In Motion Green'i erkekler için odunsu ve baharatlı bir kokudur. Boss In Motion Green 2005 yılında piyasaya sürülmüştür. Üst notalarda mandalina, misk adaçayı ve konyak; orta notalarda hindistan cevizi, kakule ve yenibahar; alt notalarda sandal ağacı, paçuli ve sedir bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -7765,18 +5763,10 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Bad Boy Carolina Herrerafor men</t>
-        </is>
-      </c>
-      <c r="D246" t="n">
-        <v>90</v>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
           <t>['sıcak baharatlı', 'taze baharatlı', 'kakao', 'vanilya', 'aromatik', 'tatlı', 'turunçgil', 'kehribar', 'odunsu']</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr">
+      <c r="D246" t="inlineStr">
         <is>
           <t>Bad Boy by Carolina Herrera, erkekler için Amber Spicy bir koku. Bad Boy, 2019 yılında piyasaya sürüldü. Quentin Bisch ve Louise Turner tarafından yaratılan Bad Boy'un üst notaları Beyaz Biber, Bergamot ve Pembe Biber; orta notaları Sedir Ağacı ve Misk Adaçayı; alt notaları Tonka Fasulyesi ve Kakao'dur.</t>
         </is>
@@ -7795,20 +5785,12 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Allure of Love Al-Rehabfor women</t>
-        </is>
-      </c>
-      <c r="D247" t="n">
-        <v>86</v>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'beyaz çiçeksi', 'odunsu', 'tatlı', 'meyveli', 'pudramsı', 'tropikal', 'taze', 'gül', 'kehribar']</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>Allure of LovebyAl-Rehabi, kadınlar için bir Citrus Gourmand kokusudur. Bu yeni bir kokudur. Allure of Love, 2024 yılında piyasaya sürülmüştür. Üst notalarda Portakal Yağı, Bergamot, Hindistan Cevizi, Şeftali ve İtalyan Mandalinası; orta notalarda Vadi Zambağı, Tropikal Meyveler, Portakal Çiçeği, Yasemin ve Gül; alt notalarda Sandal Ağacı, Paçuli, Sedir Ağacı, Amber ve Misk bulunur.</t>
+          <t>['meyvemsi', 'tatlı', 'paçuli', 'odunsu', 'gül', 'kiraz', 'sıcak baharatlı', 'çiçeksi', 'beyaz çiçeksi', 'aromatik']</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Giorgio Armani'nin Emporio Armani In Love With You parfümü, kadınlar için çiçeksi ve meyveli bir kokudur. Emporio Armani In Love With You, 2019 yılında piyasaya sürülmüştür. Üst notalarda Ahududu, Siyah Frenk Üzümü ve Kiraz; orta notalarda Gül, Yasemin ve Pelin; alt notalarda Paçuli bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -7825,18 +5807,10 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Climat (Vintage) Lancômefor women</t>
-        </is>
-      </c>
-      <c r="D248" t="n">
-        <v>86</v>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
           <t>['beyaz çiçeksi', 'taze', 'aldehitli', 'odunsu', 'pudramsı', 'aromatik', 'misk', 'yeşil', 'hayvansal', 'sarı çiçeksi']</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr">
+      <c r="D248" t="inlineStr">
         <is>
           <t>Lancôme'nin Climat (Vintage) parfümü, kadınlar için çiçeksi bir aldehit kokusudur. Climat (Vintage) 1967 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Gerard Goupy'dir. Üst notalarda Nergis, Müge, Menekşe, Yasemin, Gül, Şeftali ve Bergamot; orta notalarda Aldehitler, Biberiye ve Sümbülteber; alt notalarda ise Misk Kedisi, Misk, Vetiver, Sandal Ağacı, Bambu, Amber ve Tonka Fasulyesi bulunur.</t>
         </is>
@@ -7855,18 +5829,10 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Idole d'Armani Giorgio Armanifor women</t>
-        </is>
-      </c>
-      <c r="D249" t="n">
-        <v>86</v>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
           <t>['sıcak baharatlı', 'tatlı', 'turunçgil', 'meyveli', 'taze', 'odunsu', 'aromatik', 'topraksı', 'bal', 'beyaz çiçeksi']</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr">
+      <c r="D249" t="inlineStr">
         <is>
           <t>Idole d'ArmaniGiorgio Armani kadınlara yönelik bir parfümdür. Idole d'Armani 2009 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Bruno Jovanovic'tir. Üst notalarda Zencefil, Armut, Klementin, Bal, Acı Portakal, Badem ve Artemisia; orta notalarda Safran, Yasemin ve Gül; alt notalarda Vetiver, Paçuli ve Styrax bulunur.</t>
         </is>
@@ -7885,20 +5851,12 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Narciso Poudree Narciso Rodriguezfor women</t>
-        </is>
-      </c>
-      <c r="D250" t="n">
-        <v>91</v>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>['misk', 'beyaz çiçeksi', 'odunsu', 'aromatik', 'pudramsı', 'tatlı', 'gül', 'vanilya', 'balzamik', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>Narciso Poudree by Narciso Rodriguez, kadınlar için odunsu ve çiçeksi bir misk kokusudur. Narciso Poudree, 2016 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Aurélien Guichard'dır. Üst notalarda Yasemin, Bulgar Gülü ve Portakal Çiçeği; orta notalarda Misk; alt notalarda Kumarin, Sedir, Vetiver ve Paçuli bulunur.</t>
+          <t>['gül', 'misk', 'odunsu', 'pudramsı', 'turunçgil', 'hafif baharatlı', 'çiçeksi', 'paçuli', 'tatlı']</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Narciso Rodriguez Fleur Musc Eau De Toilette Florale, kadınlar için çiçeksi odunsu misk kokusudur. Narciso Rodriguez Fleur Musc Eau De Toilette Florale, 2020 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Sonia Constant'tır. Üst notalarda Pembe Biber ve Bergamot; orta notalarda Gül ve Misk; alt notalarda ise Odunsu Notalar, Paçuli ve Amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -7915,20 +5873,12 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>9am Dive Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D251" t="n">
-        <v>86</v>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'odunsu', 'yeşil', 'sıcak baharatlı', 'aromatik', 'turunçgil', 'taze', 'taze baharatlı', 'hafif baharatlı', 'kehribar']</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>9am DivebyAfna, kadınlar ve erkekler için Aromatik Su Kokusu'dur. Bu yeni bir kokudur. 9am Dive, 2022 yılında piyasaya sürüldü. Üst notalarda Limon, Nane, Siyah Frenk Üzümü ve Pembe Biber; orta notalarda Elma, Tütsü ve Sedir; alt notalarda Zencefil, Sandal Ağacı, Paçuli ve Yasemin bulunur.</t>
+          <t>['turunçgil', 'yeşil', 'çiçeksi', 'aromatik', 'taze baharatlı', 'beyaz çiçeksi', 'odunsu', 'bitkisel']</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Issey Miyake'den Bir KokuIssey Miyake, kadınlar için çiçeksi bir kokudur. Issey Miyake'den Bir Koku, 2009 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Daphné Bugey'dir.</t>
         </is>
       </c>
     </row>
@@ -7945,20 +5895,12 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>L'Aventure Blanche Al Haramain Perfumesfor women</t>
-        </is>
-      </c>
-      <c r="D252" t="n">
-        <v>86</v>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'beyaz çiçeksi', 'aromatik', 'odunsu', 'meyvemsi', 'çiçeksi', 'pudramsı', 'taze baharatlı', 'lavanta', 'süsen']</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>L'Aventure BlanchebyAl Haramain Perfumesis, kadınlara yönelik çiçeksi bir kokudur. L'Aventure Blanche, 2017 yılında piyasaya sürülmüştür. Üst notalarda Limon, Bergamot, Lavanta ve Gül; orta notalarda Siyah Frenk Üzümü, Yasemin, Süsen ve Vadi Zambağı; temel notalarda Sandal Ağacı ve Amber bulunmaktadır.</t>
+          <t>['aromatik', 'turunçgil', 'odunsu', 'taze baharatlı', 'bitkisel', 'sıcak baharatlı', 'lavanta']</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Yves Saint Laurent Pour HommebyYves Saint Laurent erkekler için odunsu aromatik bir koku. Yves Saint Laurent Pour Homme 1971 yılında piyasaya sürüldü. Bu kokunun arkasındaki burun Raymond Chaillan'dır. Üst notalarda Limon, Lavanta, Limon Verbena, Petitgrain ve Bergamot; orta notalarda Biberiye, Sardunya, Brezilya Gül Ağacı, Mercanköşk, Adaçayı ve Karanfil; alt notalarda Vetiver, Misk, Paçuli, Sandal Ağacı, Sedir, Tonka Fasulyesi ve Amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -7975,20 +5917,12 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Davidoff Cool Water Men Ice Fresh Davidofffor men</t>
-        </is>
-      </c>
-      <c r="D253" t="n">
-        <v>90</v>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'aromatik', 'yeşil', 'taze baharatlı', 'bitkisel']</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>Davidoff Cool Water Men Ice Fresh, erkekler için narenciye aromalı bir parfümdür. Davidoff Cool Water Men Ice Fresh, 2010 yılında piyasaya sürülmüştür. Üst notalarda Greyfurt, Amalfi Limonu ve Mandalina; orta notalarda Adaçayı ve Fesleğen; alt notalarda Yeşil Notalar bulunur.</t>
+          <t>['gül', 'odunsu', 'turunçgil', 'çiçeksi', 'meyvemsi', 'misk']</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Davidoff Cool Water Woman Sea Rose Caribbean Summer Edition, kadınlar için çiçeksi bir koku. Davidoff Cool Water Woman Sea Rose Caribbean Summer Edition, 2018 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Aurélien Guichard. Üst notalarda Mandalina ve Armut; orta notalarda Gül; alt notalarda Kaşmir Ağacı bulunuyor.</t>
         </is>
       </c>
     </row>
@@ -8005,20 +5939,12 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Chic Carolina Herrerafor women</t>
-        </is>
-      </c>
-      <c r="D254" t="n">
-        <v>86</v>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>['beyaz çiçeksi', 'çiçeksi', 'sümbülteber', 'gül', 'turunçgil', 'pudramsı', 'misk', 'yeşil']</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>ChicbyCarolina Herrera, kadınlar için çiçeksi bir kokudur. Chic, 2002 yılında piyasaya sürülmüştür. Alberto Morillas ve Jacques Cavallier tarafından yaratılmıştır. Üst notalarda kırmızı frezya, sümbülteber ve Bulgar gülü; orta notalarda frezya, müge, mandalina çiçeği ve portakal çiçeği; alt notalarda beyaz misk, sandal ağacı ve vanilya bulunur.</t>
+          <t>['beyaz çiçeksi', 'sümbülteber', 'yeşil', 'hayvansı', 'odunsu', 'sarı çiçeksi', 'misk', 'pudramsı', 'çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Carolina Herrera by Carolina Herrera, kadınlar için çiçeksi bir kokudur. Carolina Herrera by Carolina Herrera, 1988 yılında piyasaya sürülmüştür. Carolina Herrera by Carolina Herrera, Carlos Benaim, Clement Gavarry ve Rosendo Mateu tarafından yaratılmıştır. Üst notalarda Kayısı, Portakal Çiçeği, Yeşil Notalar, Brezilya Gül Ağacı ve Bergamot; orta notalarda Hint Sümbülteberi, Yasemin, İspanyol Yasemini, Ylang-Ylang, Hanımeli, Nergis, Hiacynth ve Vadi Zambağı; alt notalarda Misk Kedisi, Misk, Meşe Yosunu, Kehribar, Sandal Ağacı, Vetiver ve Sedir bulunur.</t>
         </is>
       </c>
     </row>
@@ -8035,20 +5961,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>9am Dive Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D255" t="n">
-        <v>86</v>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'odunsu', 'yeşil', 'sıcak baharatlı', 'aromatik', 'turunçgil', 'taze', 'taze baharatlı', 'hafif baharatlı', 'kehribar']</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>9am DivebyAfna, kadınlar ve erkekler için Aromatik Su Kokusu'dur. Bu yeni bir kokudur. 9am Dive, 2022 yılında piyasaya sürüldü. Üst notalarda Limon, Nane, Siyah Frenk Üzümü ve Pembe Biber; orta notalarda Elma, Tütsü ve Sedir; alt notalarda Zencefil, Sandal Ağacı, Paçuli ve Yasemin bulunur.</t>
+          <t>['turunçgil', 'yeşil', 'çiçeksi', 'aromatik', 'taze baharatlı', 'beyaz çiçeksi', 'odunsu', 'bitkisel']</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Issey Miyake'den Bir KokuIssey Miyake, kadınlar için çiçeksi bir kokudur. Issey Miyake'den Bir Koku, 2009 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Daphné Bugey'dir.</t>
         </is>
       </c>
     </row>
@@ -8065,20 +5983,12 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>9am Dive Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D256" t="n">
-        <v>86</v>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'odunsu', 'yeşil', 'sıcak baharatlı', 'aromatik', 'turunçgil', 'taze', 'taze baharatlı', 'hafif baharatlı', 'kehribar']</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>9am DivebyAfna, kadınlar ve erkekler için Aromatik Su Kokusu'dur. Bu yeni bir kokudur. 9am Dive, 2022 yılında piyasaya sürüldü. Üst notalarda Limon, Nane, Siyah Frenk Üzümü ve Pembe Biber; orta notalarda Elma, Tütsü ve Sedir; alt notalarda Zencefil, Sandal Ağacı, Paçuli ve Yasemin bulunur.</t>
+          <t>['bal', 'tatlı', 'beyaz çiçeksi', 'turunçgil', 'karamel', 'hayvansal', 'balmumu', 'paçuli', 'çiçeksi', 'odunsu']</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>ScandalbyJean Paul Gaultier, kadınlar için bir Chypre Floral parfümüdür. Scandal, 2017 yılında piyasaya sürülmüştür. Scandal, Daphné Bugey, Fabrice Pellegrin ve Christophe Raynaud tarafından yaratılmıştır. Üst notalarda Kan Portakalı ve Mandalina; orta notalarda Bal, Gardenya, Portakal Çiçeği, Yasemin ve Şeftali; alt notalarda Balmumu, Karamel, Paçuli ve Meyan Kökü bulunur.</t>
         </is>
       </c>
     </row>
@@ -8095,20 +6005,12 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Amber Oud Ultra Violet Al Haramain Perfumesfor women</t>
-        </is>
-      </c>
-      <c r="D257" t="n">
-        <v>86</v>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>['beyaz çiçeksi', 'sümbülteber', 'odunsu', 'sıcak baharatlı', 'hayvansal', 'gül', 'paçuli', 'turunçgil']</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>Al Haramain Perfumesis'in Amber Oud Ultra Violet'i, kadınlar için çiçeksi, odunsu misk kokusudur. Bu yeni bir kokudur. Amber Oud Ultra Violet, 2023 yılında piyasaya sürüldü. Üst notalarda Zencefil, Gül ve Bergamot; orta notalarda Sümbülteber, Yasemin ve Beyaz Çiçekler; alt notalarda Meşe, Paçuli ve Misk bulunmaktadır.</t>
+          <t>['vanilya', 'meyvemsi', 'tatlı', 'aromatik', 'tarçın', 'sıcak baharatlı', 'taze baharatlı', 'lavanta', 'pudramsı', 'yeşil']</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Jean Paul Gaultier'in Ultra Male'si, erkekler için bir Amber Fougere kokusudur. Ultra Male, 2015 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Francis Kurkdjian'dır. Üst notalarda Armut, Lavanta, Nane, Bergamot ve Limon; orta notalarda Tarçın, Adaçayı ve Kimyon; alt notalarda Siyah Vanilya Kabuğu, Amber, Paçuli ve Sedir bulunur.</t>
         </is>
       </c>
     </row>
@@ -8125,20 +6027,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Queen of the Night Al-Rehabfor women</t>
-        </is>
-      </c>
-      <c r="D258" t="n">
-        <v>86</v>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>['odunsu', 'beyaz çiçeksi', 'vanilya', 'turunçgil', 'lavanta', 'sıcak baharatlı', 'pudramsı', 'aromatik', 'taze baharatlı', 'çikolata']</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>Al-Rehabi'nin Queen of the Night'ı kadınlar için Amber Floral bir koku. Bu yeni bir koku. Queen of the Night, 2024 yılında piyasaya sürüldü. Üst notalarda Bergamot ve Lavanta; orta notalarda Beyaz Çiçekler ve Çikolata; alt notalarda Sandal Ağacı ve Vanilya bulunmaktadır.</t>
+          <t>['kehribar', 'turunçgil', 'deri', 'odunsu', 'pudramsı', 'hayvansal', 'menekşe', 'aromatik']</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Only The BravebyDiesel, erkekler için Amber Woody bir kokudur. Only The Brave, 2009 yılında piyasaya sürülmüştür. Only The Brave, Alienor Massenet, Olivier Polge ve Pierre Wargnye tarafından yaratılmıştır. Üst notalarda Amalfi Limonu ve Mandalina; orta notalarda Menekşe, Virginia Sediri ve Kişniş; alt notalarda Amber, Deri, Benzoin, Fransız labdanum ve Styrax bulunur.</t>
         </is>
       </c>
     </row>
@@ -8155,20 +6049,12 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Urbanist Homme Al Haramain Perfumesfor men</t>
-        </is>
-      </c>
-      <c r="D259" t="n">
-        <v>86</v>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>['aromatik', 'turunçgil', 'odunsu', 'taze baharatlı', 'kehribar', 'pudramsı', 'misk', 'beyaz çiçeksi', 'lavanta', 'tatlı']</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>Urbanist Hommeby Al Haramain Perfumesis, erkekler için Amber ve Baharatlı bir koku. Bu kokunun arkasındaki isim Christian Carbonnel. Üst notalarda Petitgrain, Portakal ve Limon; orta notalarda Lavanta, Biberiye ve Yasemin; alt notalarda Amber, Misk, Sandal Ağacı ve Tonka Fasulyesi bulunuyor.</t>
+          <t>['lavanta', 'hafif baharatlı', 'aromatik', 'pudramsı', 'meyvemsi', 'tatlı', 'anason', 'çiçeksi', 'vanilya', 'badem']</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Diesel Fuel For Life Erkek Kolonyası Diesel Fuel For Life Erkek Kolonyası, erkekler için odunsu aromatik bir kokudur. Diesel Fuel For Life Erkek Kolonyası, 2008 yılında piyasaya sürülmüştür. Diesel Fuel For Life Erkek Kolonyası, Annick Menardo ve Jacques Cavallier tarafından yaratılmıştır. Üst notalarda Yıldız Anason ve Pembe Biber; orta notalarda Lavanta ve Ahududu; alt notalarda Heliotrope ve Vetiver bulunur.</t>
         </is>
       </c>
     </row>
@@ -8185,22 +6071,10 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Le Parfum Viktor&amp;Rolffor women and men</t>
-        </is>
-      </c>
-      <c r="D260" t="n">
-        <v>86</v>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>Le Parfumby Viktor&amp;Rolf kadın ve erkeklere yönelik bir parfümdür. Le Parfum 1996 yılında piyasaya sürülmüştür.</t>
-        </is>
-      </c>
+          <t>['sıcak baharatlı', 'tarçın', 'tütün', 'tatlı', 'hafif baharatlı', 'deri', 'aromatik', 'turunçgil']</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8215,20 +6089,12 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>9pm Afnanfor men</t>
-        </is>
-      </c>
-      <c r="D261" t="n">
-        <v>86</v>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>['vanilya', 'kehribar', 'sıcak baharatlı', 'tarçın', 'tatlı', 'meyvemsi', 'pudramsı', 'lavanta', 'aromatik', 'taze']</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>9pmbyAfnani erkekler için Amber Vanilya kokusu. 9pm, 2020 yılında piyasaya sürüldü. Üst notalarda Elma, Tarçın, Yabani Lavanta ve Bergamot; orta notalarda Portakal Çiçeği ve Vadi Zambağı; alt notalarda Vanilya, Tonka Fasulyesi, Amber ve Paçuli bulunuyor.</t>
+          <t>['odunsu', 'tatlı', 'fındıksı', 'ballı', 'meyveli', 'turunçgil', 'ozonik', 'kehribar', 'çiçeksi', 'beyaz çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>1 Million LuckybyPaco Rabanne, erkekler için odunsu bir kokudur. 1 Million Lucky, 2018 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Natalie Gracia-Cetto'dur. Üst notalarda Erik, Ozon, Greyfurt ve Bergamot; orta notalarda Fındık, Bal, Sedir, Kaşmir Ağacı, Portakal Çiçeği ve Yasemin; alt notalarda Amber Ağacı, Paçuli, Meşe Yosunu ve Vetiver bulunur.</t>
         </is>
       </c>
     </row>
@@ -8245,20 +6111,12 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Phantom Paco Rabannefor men</t>
-        </is>
-      </c>
-      <c r="D262" t="n">
-        <v>89</v>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'vanilya', 'lavanta', 'topraksı', 'aromatik', 'odunsu', 'dumanlı', 'meyveli', 'taze', 'taze baharatlı']</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>PhantombyPaco Rabanne, erkekler için odunsu aromatik bir kokudur. Phantom, 2021 yılında piyasaya sürülmüştür. Anne Flipo, Dominique Ropion, Loc Dong ve Juliette Karagueuzoglou tarafından yaratılmıştır. Üst notalarda Lavanta, Limon Kabuğu Rendesi ve Amalfi Limonu; orta notalarda Lavanta, Topraksı Notalar, Elma, Duman ve Paçuli; alt notalarda Vanilya, Lavanta ve Vetiver bulunur.</t>
+          <t>['taze baharatlı', 'aromatik', 'turunçgil', 'odunsu', 'lavanta', 'kehribar', 'yeşil', 'topraksı', 'bitkisel', 'dumanlı']</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Eau Paco Rabanne, erkekler için aromatik bir Fougere kokusudur. Eau Paco Rabanne, 2002 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Olivier Cresp'tir. Üst notalarda Bergamot, Lavanta, Limon ve Portakal Çiçeği; orta notalarda Fesleğen, Vetiver, Biber ve Değerli Ağaçlar; alt notalarda Tütsü, Meşe Yosunu, Misk, Sandal Ağacı, Amber ve Deri bulunur.</t>
         </is>
       </c>
     </row>
@@ -8275,18 +6133,10 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Avon Beautiful Butterfly Avonfor women</t>
-        </is>
-      </c>
-      <c r="D263" t="n">
-        <v>86</v>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
           <t>['beyaz çiçeksi', 'taze', 'meyveli', 'yeşil', 'turunçgil', 'misk', 'pudramsı', 'tatlı']</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
+      <c r="D263" t="inlineStr">
         <is>
           <t>Avon Beautiful Butterfly, Avon'un kadınlara yönelik Çiçeksi Meyveli bir kokusudur. Avon Beautiful Butterfly, 2015 yılında piyasaya sürülmüştür. Üst notalarda Yeşil Elma, Nektarin ve Limon; orta notalarda Vadi Zambağı, Gardenya ve Yasemin; alt notalarda Misk, Odunsu Notalar ve Madagaskar Vanilyası bulunmaktadır.</t>
         </is>
@@ -8305,20 +6155,12 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>9am Dive Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D264" t="n">
-        <v>86</v>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'odunsu', 'yeşil', 'sıcak baharatlı', 'aromatik', 'turunçgil', 'taze', 'taze baharatlı', 'hafif baharatlı', 'kehribar']</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>9am DivebyAfna, kadınlar ve erkekler için Aromatik Su Kokusu'dur. Bu yeni bir kokudur. 9am Dive, 2022 yılında piyasaya sürüldü. Üst notalarda Limon, Nane, Siyah Frenk Üzümü ve Pembe Biber; orta notalarda Elma, Tütsü ve Sedir; alt notalarda Zencefil, Sandal Ağacı, Paçuli ve Yasemin bulunur.</t>
+          <t>['bal', 'tatlı', 'beyaz çiçeksi', 'turunçgil', 'karamel', 'hayvansal', 'balmumu', 'paçuli', 'çiçeksi', 'odunsu']</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>ScandalbyJean Paul Gaultier, kadınlar için bir Chypre Floral parfümüdür. Scandal, 2017 yılında piyasaya sürülmüştür. Scandal, Daphné Bugey, Fabrice Pellegrin ve Christophe Raynaud tarafından yaratılmıştır. Üst notalarda Kan Portakalı ve Mandalina; orta notalarda Bal, Gardenya, Portakal Çiçeği, Yasemin ve Şeftali; alt notalarda Balmumu, Karamel, Paçuli ve Meyan Kökü bulunur.</t>
         </is>
       </c>
     </row>
@@ -8335,20 +6177,12 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>The love in my Heart Al-Rehabfor women</t>
-        </is>
-      </c>
-      <c r="D265" t="n">
-        <v>86</v>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'vanilya', 'beyaz çiçeksi', 'tatlı', 'kehribar', 'turunçgil', 'sıcak baharatlı', 'paçuli', 'su', 'balzamik']</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>Al-Rehabi'nin The Love in My Heart parfümü, kadınlar için Amber Vanilya aromalı bir koku. Bu yeni bir parfüm. The Love in My Heart, 2023 yılında piyasaya sürüldü. Üst notalarda Armut, Mandalina ve Şeftali; orta notalarda Yasemin ve Zambak; alt notalarda Vanilya, Benzoin ve Paçuli bulunuyor.</t>
+          <t>['yeşil', 'aromatik', 'odunsu', 'balzamik', 'kehribar', 'yosunlu', 'çiçeksi', 'tatlı', 'beyaz çiçeksi', 'topraksı']</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>ArmanibyGiorgio Armani, kadınlar için bir Chypre Floral parfümüdür. Armani, 1981 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Ron Winnegrad'dır. Üst notalarda Galbanum, Kadife Çiçeği, Aldehitler, Ananas, Bergamot ve Nane; orta notalarda Nergis, Süsen Kökü, Sümbülteber, Gül, Yasemin, Siklamen, Vadi Zambağı ve Orkide; alt notalarda Meşe Yosunu, Benzoin, Sedir, Kehribar, Sandal Ağacı, Tonka Fasulyesi ve Misk bulunur.</t>
         </is>
       </c>
     </row>
@@ -8365,18 +6199,10 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Roberto Cavalli Eau de Parfum Roberto Cavallifor women</t>
-        </is>
-      </c>
-      <c r="D266" t="n">
-        <v>90</v>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
           <t>['vanilya', 'kehribar', 'beyaz çiçeksi', 'tatlı', 'sıcak baharatlı', 'turunçgil', 'hafif baharatlı', 'balzamik']</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr">
+      <c r="D266" t="inlineStr">
         <is>
           <t>Roberto Cavalli Eau de ParfumRoberto Cavalli, kadınlar için Amber Floral bir kokudur. Roberto Cavalli Eau de Parfum 2012 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki burun Louise Turner'dır. Üst nota Pembe Biber; orta nota Afrika Portakal Çiçeği; alt notalar Vanilya, Benzoin ve Tonka Fasulyesidir.</t>
         </is>
@@ -8395,20 +6221,12 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>A Thousand Wishes 2020 Edition Bath &amp; Body Worksfor women and men</t>
-        </is>
-      </c>
-      <c r="D267" t="n">
-        <v>86</v>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'çiçeksi', 'taze', 'kehribar', 'badem', 'şampanya', 'tatlı', 'gül', 'aldehitli', 'turunçgil']</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>Bath &amp; Body Works'ün A Thousand Wishes 2020 Edition'ı kadın ve erkeklere yönelik bir parfümdür. A Thousand Wishes 2020 Edition 2020 yılında piyasaya sürülmüştür.</t>
+          <t>['gül', 'çiçeksi', 'paçuli', 'deri', 'odunsu', 'misk', 'sıcak baharatlı', 'taze', 'topraksı']</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Givenchy Harvest 2007 Very Irresistible Damascena RoseGivenchy, kadınlara yönelik çiçeksi bir kokudur. Givenchy Harvest 2007 Very Irresistible Damascena Rose, 2007 yılında piyasaya sürülmüştür. Üst notalarda Şam Gülü; orta notalarda Çay Gülü, Şam Gülü, Şakayık ve Manolya; alt notalarda Süet ve Paçuli bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -8425,18 +6243,10 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Boss Intense Hugo Bossfor women</t>
-        </is>
-      </c>
-      <c r="D268" t="n">
-        <v>95</v>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
           <t>['sıcak baharatlı', 'odunsu', 'vanilya', 'pudramsı', 'beyaz çiçeksi', 'kehribar', 'gül', 'balzamik', 'paçuli', 'turunçgil']</t>
         </is>
       </c>
-      <c r="F268" t="inlineStr">
+      <c r="D268" t="inlineStr">
         <is>
           <t>Hugo Boss'un Boss Intense'i, kadınlar için Amber Woody bir kokudur. Boss Intense, 2003 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Ursula Wandel'dir. Üst notalarda baharatlar ve portakal çiçeği; orta notalarda vanilya ve gül; alt notalarda sandal ağacı, amber ve paçuli bulunur.</t>
         </is>
@@ -8455,20 +6265,12 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Musk Al Ghazal Eau de Parfum Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D269" t="n">
-        <v>86</v>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>['misk', 'sıcak baharatlı', 'taze baharatlı', 'tatlı', 'anason', 'pudramsı', 'çikolata', 'hafif baharatlı', 'aromatik', 'vanilya']</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>Musk Al Ghazal Eau de ParfumbyAl Haramain Perfumesis, kadınlar ve erkekler için bir Amber kokusudur. Üst notalarda kimyon ve anason; orta notalarda misk; alt notalarda baharatlar, bitter çikolata, odunsu notalar ve vanilya bulunur.</t>
+          <t>['beyaz çiçeksi', 'sümbülteber', 'tatlı', 'odunsu', 'turunçgil', 'paçuli', 'vanilya', 'meyveli', 'hayvansal', 'topraksı']</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>L'Interdit Eau de ParfumbyGivench, kadınlar için Amber Floral bir kokudur. L'Interdit Eau de Parfum, 2018 yılında piyasaya sürülmüştür. L'Interdit Eau de Parfum, Dominique Ropion, Anne Flipo ve Fanny Bal tarafından yaratılmıştır. Üst notalarda Armut ve Bergamot; orta notalarda Sümbülteber, Portakal Çiçeği ve Yasemin Sambac; alt notalarda Paçuli, Vanilya, Ambroxan ve Vetiver bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -8485,20 +6287,12 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Naseej Al Kiswah Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D270" t="n">
-        <v>86</v>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>['odunsu', 'kehribar', 'deri', 'ud', 'paçuli', 'hayvansal', 'vanilya', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>Naseej Al KiswahbyAfnani, Kadınlar ve Erkekler için Amber Woody Kokusudur. orta notalarda Woodsy Notes ve Sedir; temel notalar Amber, Deri ve Agarwood'dur (Ud).</t>
+          <t>['meyveli', 'çiçeksi', 'yeşil', 'gül', 'taze', 'odunsu', 'tatlı']</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Versace Pour Femme Dylan BluebyVersace, kadınlar için çiçeksi ve meyveli bir kokudur. Versace Pour Femme Dylan Blue, 2017 yılında piyasaya sürülmüştür. Versace Pour Femme Dylan Blue, Calice Becker ve Natalie Gracia-Cetto tarafından yaratılmıştır. Üst notalarda Granny Smith elması, siyah frenk üzümü, yonca, unutma beni ve Shiso; orta notalarda şeftali, petalia, kuşburnu, gül ve yasemin; alt notalarda misk, beyaz ağaçlar, styrax ve paçuli bulunur.</t>
         </is>
       </c>
     </row>
@@ -8515,20 +6309,12 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Dolce&amp;Gabbana Dolce&amp;Gabbanafor women</t>
-        </is>
-      </c>
-      <c r="D271" t="n">
-        <v>87</v>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>['aromatik', 'çiçeksi', 'taze', 'beyaz çiçeksi', 'aldehitli', 'turunçgil', 'taze baharatlı', 'sıcak baharatlı', 'odunsu', 'vanilya']</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>Dolce&amp;GabbanaDolce&amp;Gabbana, kadınlar için çiçeksi bir aldehit kokusudur. Dolce&amp;Gabbana, 1992 yılında piyasaya sürülmüştür. Dolce&amp;Gabbana, Jean-Pierre Mary ve Martine Pallix tarafından yaratılmıştır. Üst notalarda Aldehitler, Fesleğen, Turunçgiller, Sarmaşık, Mandalina, Frezya ve Bergamot; orta notalarda Karanfil, Kadife Çiçeği, Kişniş, Portakal Çiçeği, Zambak, Yasemin, Bulgar Gülü ve Müge; alt notalarda Sandal Ağacı, Vanilya, Misk ve Tonka Fasulyesi bulunur.</t>
+          <t>['aromatik', 'turunçgil', 'odunsu', 'taze baharatlı', 'sıcak baharatlı', 'taze', 'lavanta']</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>K by Dolce &amp; GabbanabyDolce&amp;Gabbana, erkekler için odunsu aromatik bir kokudur. K by Dolce &amp; Gabbana, 2019 yılında piyasaya sürülmüştür. K by Dolce &amp; Gabbana, Daphné Bugey ve Nathalie Lorson tarafından yaratılmıştır. Üst notalarda ardıç meyvesi, turunçgiller, kan portakalı ve Sicilya limonu; orta notalarda yenibahar, lavanta, misk adaçayı ve sardunya; alt notalarda ise vetiver, sedir ve paçuli bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -8545,18 +6331,10 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Prada Paradoxe Pradafor women</t>
-        </is>
-      </c>
-      <c r="D272" t="n">
-        <v>90</v>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
           <t>['beyaz çiçeksi', 'turunçgil', 'tatlı', 'kehribar', 'vanilya', 'pudramsı', 'meyvemsi', 'misk', 'taze', 'hayvansal']</t>
         </is>
       </c>
-      <c r="F272" t="inlineStr">
+      <c r="D272" t="inlineStr">
         <is>
           <t>Prada Paradoxe, kadınlar için Amber Floral bir koku. Bu yeni bir parfüm. Prada Paradoxe, 2022 yılında piyasaya sürüldü. Prada Paradoxe, Nadège Le Garlantezec, Antoine Maisondieu ve Shyamala Maisondieu tarafından yaratıldı. Üst notalarda Armut, Mandalina ve Bergamot; orta notalarda Portakal Çiçeği, Portakal Çiçeği Özü, Portakal Çiçeği ve Yasemin; alt notalarda Burbon Vanilya, Amber, Beyaz Misk ve Benzoin yer alıyor.</t>
         </is>
@@ -8575,22 +6353,10 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>All You Need is Desire Armaffor women and men</t>
-        </is>
-      </c>
-      <c r="D273" t="n">
-        <v>86</v>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>['odunsu', 'turunçgil', 'aromatik', 'taze baharatlı', 'lavanta', 'bitkisel', 'pudramsı', 'taze', 'hafif baharatlı']</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>Armafi'nin All You Need is Desire adlı parfümü kadınlar ve erkekler için narenciye aromalı bir kokudur. All You Need is Desire 2019 yılında piyasaya sürülmüştür. Üst notalarda turunçgiller ve bergamot; orta notalarda lavanta ve adaçayı; alt notalarda sandal ağacı ve sedir bulunmaktadır.</t>
-        </is>
-      </c>
+          <t>['gül', 'çiçeksi', 'misk', 'pudramsı', 'odunsu', 'taze baharatlı', 'aromatik', 'turunçgil', 'sıcak baharatlı']</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -8605,20 +6371,12 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Miss Dior Blooming Bouquet Diorfor women</t>
-        </is>
-      </c>
-      <c r="D274" t="n">
-        <v>91</v>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>['çiçeksi', 'gül', 'taze', 'meyvemsi', 'misk', 'turunçgil', 'pudramsı', 'tatlı']</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>Miss Dior Blooming Bouquet by Dioris, kadınlar için çiçeksi bir koku. Miss Dior Blooming Bouquet, 2014 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Louise Turner. Üst notalarda Sicilya Mandalinası; orta notalarda Pembe Şakayık, Şam Gülü, Kayısı ve Şeftali; alt notalarda ise Beyaz Misk bulunuyor.</t>
+          <t>['meyvemsi', 'gül', 'çiçeksi', 'pudramsı', 'misk', 'taze', 'tatlı', 'turunçgil', 'laktonik']</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Dioris'in Dior Miss Dior Blooming Bouquet Bobby Limited Edition parfümü, kadınlara yönelik çiçeksi bir kokudur. Dior Miss Dior Blooming Bouquet Bobby Limited Edition, 2021 yılında piyasaya sürülmüştür. Parfümün arkasındaki isim François Demachy'dir. Üst notalarda Mandalina; orta notalarda Kayısı, Pembe Şakayık, Şam Gülü ve Şeftali; alt notalarda Beyaz Misk bulunur.</t>
         </is>
       </c>
     </row>
@@ -8635,20 +6393,12 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Dolce Estasi Bvlgarifor women</t>
-        </is>
-      </c>
-      <c r="D275" t="n">
-        <v>86</v>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>['pudramsı', 'misk', 'vanilya', 'turunçgil', 'badem', 'çiçeksi', 'taze']</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>Bvlgari Dolce Estasi, kadınlar için çiçeksi bir kokudur. Dolce Estasi, 2021 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Jacques Cavallier. Üst notasında turunçgiller; orta notasında güneş çiçeği; alt notasında misk bulunuyor.</t>
+          <t>['çiçeksi', 'paçuli', 'gül', 'odunsu', 'sıcak baharatlı', 'topraksı']</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Dolce AurabyAvon, kadınlara yönelik çiçeksi bir kokudur. Dolce Auraby, 2001 yılında piyasaya sürülmüştür.</t>
         </is>
       </c>
     </row>
@@ -8665,20 +6415,12 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>L’Homme Ideal Eau de Parfum Guerlainfor men</t>
-        </is>
-      </c>
-      <c r="D276" t="n">
-        <v>87</v>
-      </c>
-      <c r="E276" t="inlineStr">
-        <is>
-          <t>['tatlı', 'kiraz', 'vanilya', 'badem', 'fındık', 'sıcak baharatlı', 'kehribar', 'meyveli', 'deri', 'aromatik']</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>L’Homme Ideal Eau de ParfumbyGuerlaini, erkekler için Amber Woody bir kokudur. L’Homme Ideal Eau de Parfum, 2016 yılında piyasaya sürüldü. L’Homme Ideal Eau de Parfum, Thierry Wasser ve Delphine Jelk tarafından yaratıldı. Üst notalarda Badem, Baharatlar, Lavanta, Bergamot, Kekik ve Biberiye; orta notalarda Kiraz, Vanilya, Tütsü ve Bulgar Gülü; alt notalarda Deri, Tonka Fasulyesi ve Sandal Ağacı bulunur.</t>
+          <t>['aromatik', 'taze baharatlı', 'turunçgil', 'odunsu', 'bitkisel', 'sıcak baharatlı']</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Agatha Parisis imzalı L'Homme Eau de Parfum, erkekler için aromatik bir Fougere kokusudur. L'Homme Eau de Parfum, 2018 yılında piyasaya sürülmüştür. Üst notalarda Limon, Bergamot ve Karabiber; orta notalarda Adaçayı ve Sardunya; alt notalarda Vetiver ve Sedir bulunur.</t>
         </is>
       </c>
     </row>
@@ -8695,20 +6437,12 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Acqua di Gio Giorgio Armanifor men</t>
-        </is>
-      </c>
-      <c r="D277" t="n">
-        <v>86</v>
-      </c>
-      <c r="E277" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'aromatik', 'deniz', 'taze baharatlı', 'çiçeksi', 'odunsu', 'taze']</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>Acqua di Gioby Giorgio Armanis, erkekler için aromatik bir su kokusudur. Üst notalarda limon, bergamot, yasemin, portakal, mandalina ve portakal çiçeği esansı; orta notalarda deniz notaları, yasemin, kalon, biberiye, şeftali, frezya, sümbül, siklamen, menekşe, kişniş, gül, hindistan cevizi ve mignonette; alt notalarda beyaz misk, sedir, meşe yosunu, paçuli ve amber bulunur.</t>
+          <t>['aromatik', 'taze baharatlı', 'deniz', 'odunsu', 'paçuli', 'sıcak baharatlı', 'kehribar', 'balzamik', 'dumanlı', 'bitkisel']</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Acqua di Gio Profumo Special Blend by Giorgio Armani erkekler için aromatik su kokusudur. Acqua di Gio Profumo Special Blend 2017 yılında piyasaya sürülmüştür. Üst notalarda deniz notaları ve bergamot; orta notalarda biberiye, adaçayı ve sardunya; alt notalarda paçuli ve tütsü bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -8725,18 +6459,10 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Le Male Elixir Jean Paul Gaultierfor men</t>
-        </is>
-      </c>
-      <c r="D278" t="n">
-        <v>91</v>
-      </c>
-      <c r="E278" t="inlineStr">
-        <is>
           <t>['vanilya', 'tatlı', 'bal', 'kehribar', 'aromatik', 'lavanta', 'tütün', 'yeşil', 'taze baharatlı', 'pudramsı']</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr">
+      <c r="D278" t="inlineStr">
         <is>
           <t>Jean Paul Gaultier'in Le Male Elixir'i, erkekler için bir Amber Fougere kokusudur. Bu yeni bir kokudur. Le Male Elixir, 2023 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Quentin Bisch. Üst notalarda Lavanta ve Nane; orta notalarda Vanilya ve Benzoin; alt notalarda Bal, Tonka Fasulyesi ve Tütün bulunur.</t>
         </is>
@@ -8755,20 +6481,12 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>L'Aventure Al Haramain Perfumesfor men</t>
-        </is>
-      </c>
-      <c r="D279" t="n">
-        <v>86</v>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'aromatik', 'odunsu', 'misk', 'taze baharatlı', 'pudramsı', 'beyaz çiçeksi']</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>L'Aventure by Al Haramain Perfumesis erkekler için Chypre Fruity bir kokudur. L'Aventure 2016 yılında piyasaya sürülmüştür. Üst notalarda Limon, Bergamot ve elemi; orta notalarda Odunsu Notalar, Yasemin ve Vadi Zambağı; alt notalarda Misk, Paçuli ve Amber bulunmaktadır.</t>
+          <t>['turunçgil', 'beyaz çiçeksi', 'paçuli', 'taze baharatlı', 'odunsu', 'tatlı']</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>MYSLF Eau de Parfum, Yves Saint Laurentis tarafından üretilen aromatik bir erkek parfümüdür. Bu yeni bir parfümdür. MYSLF Eau de Parfum, 2023 yılında piyasaya sürülmüştür. Christophe Raynaud, Antoine Maisondieu ve Daniela (Roche) Andrier tarafından yaratılmıştır. Üst notalarda Calabria bergamotu ve bergamot; orta notalarda Tunus Portakal Çiçeği; alt notalarda Ambrofix™ ve Paçuli bulunur.</t>
         </is>
       </c>
     </row>
@@ -8785,20 +6503,12 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>9am Dive Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D280" t="n">
-        <v>86</v>
-      </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'odunsu', 'yeşil', 'sıcak baharatlı', 'aromatik', 'turunçgil', 'taze', 'taze baharatlı', 'hafif baharatlı', 'kehribar']</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>9am DivebyAfna, kadınlar ve erkekler için Aromatik Su Kokusu'dur. Bu yeni bir kokudur. 9am Dive, 2022 yılında piyasaya sürüldü. Üst notalarda Limon, Nane, Siyah Frenk Üzümü ve Pembe Biber; orta notalarda Elma, Tütsü ve Sedir; alt notalarda Zencefil, Sandal Ağacı, Paçuli ve Yasemin bulunur.</t>
+          <t>['çiçeksi', 'beyaz çiçeksi', 'pudramsı', 'yeşil', 'odunsu', 'taze baharatlı', 'gül', 'tatlı', 'aromatik', 'sarı çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>YSL Paris L'Edition VeninibyYves Saint Laurent kadınlar için çiçeksi bir koku. YSL Paris L'Edition Venini, 2014 yılında piyasaya sürüldü. Bu kokunun arkasındaki burun Sophia Grojsman. Üst notalarda Gül, Frenk üzümü tomurcukları, Alıç, Yeşil Notalar, Mimoza, Portakal Çiçeği, Bergamot, Turunçgil, Sardunya ve Sümbül; orta notalarda Gül, Vadi Zambağı, Zambak, Yasemin, Menekşe, Limon (Ihlamur) Çiçeği, Süsen ve Ylang-Ylang; alt notalarda Misk, Süsen, Kehribar, Sedir, Kediotu, Meşe Yosunu ve Sandal Ağacı.</t>
         </is>
       </c>
     </row>
@@ -8815,18 +6525,10 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Emporio Armani Stronger With You Intensely Giorgio Armanifor men</t>
-        </is>
-      </c>
-      <c r="D281" t="n">
-        <v>88</v>
-      </c>
-      <c r="E281" t="inlineStr">
-        <is>
           <t>['vanilya', 'tatlı', 'kehribar', 'tarçın', 'sıcak baharatlı', 'tozlu', 'aromatik', 'hafif baharatlı', 'karamel']</t>
         </is>
       </c>
-      <c r="F281" t="inlineStr">
+      <c r="D281" t="inlineStr">
         <is>
           <t>Giorgio Armani'nin Emporio Armani Stronger With You Intensely'si erkekler için bir Amber Fougere kokusudur. Emporio Armani Stronger With You Intensely, 2019 yılında piyasaya sürülmüştür. Üst notalarda Pembe Biber, Ardıç ve Menekşe; orta notalarda Karamel, Tarçın, Lavanta ve Adaçayı; alt notalarda Vanilya, Amber, Tonka Fasulyesi ve Süet bulunmaktadır.</t>
         </is>
@@ -8845,20 +6547,12 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Musk Al Ghazal Eau de Parfum Al Haramain Perfumesfor women and men</t>
-        </is>
-      </c>
-      <c r="D282" t="n">
-        <v>86</v>
-      </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>['misk', 'sıcak baharatlı', 'taze baharatlı', 'tatlı', 'anason', 'pudramsı', 'çikolata', 'hafif baharatlı', 'aromatik', 'vanilya']</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>Musk Al Ghazal Eau de ParfumbyAl Haramain Perfumesis, kadınlar ve erkekler için bir Amber kokusudur. Üst notalarda kimyon ve anason; orta notalarda misk; alt notalarda baharatlar, bitter çikolata, odunsu notalar ve vanilya bulunur.</t>
+          <t>['aromatik', 'turunçgil', 'taze baharatlı', 'odunsu', 'topraksı', 'yosunlu', 'yeşil', 'çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Dioris'in Eau Sauvage adlı parfümü, erkekler için narenciye aromalı bir kokudur. Eau Sauvage, 1966 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Edmond Roudnitska'dır. Üst notalarda Limon, Bergamot, Fesleğen, Biberiye, Kimyon ve Meyveli Notalar; orta notalarda Yasemin, Kişniş, Karanfil, Paçuli, Süsen Kökü, Sandal Ağacı, Gül, Lavanta ve Hedione; alt notalarda Meşe Yosunu, Vetiver, Misk ve Amber bulunur.</t>
         </is>
       </c>
     </row>
@@ -8875,18 +6569,10 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Emporio Armani Stronger With You Absolutely Giorgio Armanifor men</t>
-        </is>
-      </c>
-      <c r="D283" t="n">
-        <v>88</v>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
           <t>['vanilya', 'odunsu', 'balzamik', 'rom', 'aromatik', 'sıcak baharatlı', 'fındıksı', 'pudramsı', 'lavanta', 'tatlı']</t>
         </is>
       </c>
-      <c r="F283" t="inlineStr">
+      <c r="D283" t="inlineStr">
         <is>
           <t>Giorgio Armani'nin Emporio Armani Stronger With You Absolutely adlı parfümü erkekler için bir Amber Fougere kokusudur. Emporio Armani Stronger With You Absolutely 2021 yılında piyasaya sürülmüştür. Üst notalarda Rom, Elemi ve Bergamot; orta notalarda Lavanta ve Davana; alt notalarda Madagaskar Vanilyası, Kestane, Sedir ve Paçuli bulunmaktadır.</t>
         </is>
@@ -8905,20 +6591,12 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Club De Nuit Urban Elixir Armaffor men</t>
-        </is>
-      </c>
-      <c r="D284" t="n">
-        <v>86</v>
-      </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>['kehribar', 'aromatik', 'turunçgil', 'taze baharatlı', 'misk', 'odunsu', 'lavanta', 'hafif baharatlı', 'sıcak baharatlı', 'bitkisel']</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>Club De Nuit Urban ElixirbyArmafis erkekler için bir parfüm. Bu yeni bir parfüm. Club De Nuit Urban Elixir 2022 yılında piyasaya sürüldü. Üst notalarda Bergamot, Pembe Biber, Yasemin ve Portakal Çiçeği; orta notalarda Lavanta, Elemi, Sardunya, Safran, Vetiver ve Tagetes; alt notalarda Ambroxan, Amber, Paçuli, Sedir ve Laden bulunur.</t>
+          <t>['sıcak baharatlı', 'taze baharatlı', 'odunsu', 'aromatik', 'lavanta', 'hafif baharatlı', 'tarçın', 'kehribar', 'pudramsı', 'balzamik']</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Sauvage Elixir by Dioris, erkekler için aromatik bir koku. Sauvage Elixir, 2021 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim François Demachy. Üst notalarda Hindistan cevizi, tarçın, kakule ve greyfurt; orta notalarda lavanta; alt notalarda ise meyan kökü, sandal ağacı, amber, paçuli ve Haiti vetiveri bulunuyor.</t>
         </is>
       </c>
     </row>
@@ -8935,20 +6613,12 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Le Parfait Azure Pour Femme Armaffor women</t>
-        </is>
-      </c>
-      <c r="D285" t="n">
-        <v>86</v>
-      </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'beyaz çiçeksi', 'meyvemsi', 'çiçeksi', 'taze baharatlı', 'aromatik', 'sıcak baharatlı', 'sümbülteber', 'pudramsı', 'tatlı']</t>
-        </is>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>Le Parfait Azure Pour FemmebyArmafis, kadınlar için Amber Floral bir koku. Üst notalarda Bergamot, Kakule, Şeftali ve Gül; orta notalarda Yasemin, Osmanthus, Sümbülteber, Erik ve Elma; alt notalarda Sandal Ağacı, Vanilya ve Tütün bulunmaktadır.</t>
+          <t>['yeşil', 'hindistan cevizi', 'tatlı', 'su', 'vanilya', 'odunsu', 'aromatik', 'sıcak baharatlı', 'meyveli', 'taze']</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Jean Paul Gaultier imzalı Le Beau Paradise Garden, erkeklere özel bir parfüm. Bu yeni bir parfüm. Le Beau Paradise Garden, 2024 yılında piyasaya sürüldü. Bu kokunun arkasındaki isim Quentin Bisch. Üst notalarda Yeşil Notalar, Sulu Notalar, Nane ve Zencefil; orta notalarda Hindistan Cevizi, İncir ve Tuz; alt notalarda Tonka Fasulyesi ve Sandal Ağacı bulunuyor.</t>
         </is>
       </c>
     </row>
@@ -8965,20 +6635,12 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Riviera Goddess Avonfor women</t>
-        </is>
-      </c>
-      <c r="D286" t="n">
-        <v>86</v>
-      </c>
-      <c r="E286" t="inlineStr">
-        <is>
-          <t>['beyaz çiçeksi', 'turunçgil', 'odunsu', 'tatlı', 'pudramsı', 'meyveli', 'çiçeksi', 'paçuli']</t>
-        </is>
-      </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>Riviera GoddessbyAvon, kadınlar için Chypre Meyveli bir kokudur. Riviera Goddess, 2013 yılında piyasaya sürülmüştür. Üst notalarda Şeftali ve Mandalina; orta notalarda Çiçeksi Notalar; alt notalarda Paçuli ve Misk bulunmaktadır.</t>
+          <t>['beyaz çiçeksi', 'çiçeksi', 'taze', 'yeşil', 'misk']</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>GoddessbyAvon, kadınlara yönelik çiçeksi bir kokudur. Goddess, 2004 yılında piyasaya sürülmüştür.</t>
         </is>
       </c>
     </row>
@@ -8995,20 +6657,12 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Mod Blush Ariana Grandefor women</t>
-        </is>
-      </c>
-      <c r="D287" t="n">
-        <v>86</v>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'tatlı', 'misk', 'gül', 'çiçeksi', 'turunçgil', 'tropikal', 'pudramsı', 'taze', 'kehribar']</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>Mod Blushby Ariana Grande, kadınlara özel bir parfüm. Bu yeni bir parfüm. Mod Blush, 2022'de piyasaya sürüldü. Bu kokunun arkasındaki isim Frank Voelkl. Üst notalarda Ahududu, Çarkıfelek Meyvesi, Pembe Biber ve Bergamot; orta notalarda Gül, Armut ve Manolya; alt notalarda Misk, Ambroxan, Rüya Ağacı ve Sandal Ağacı bulunuyor.</t>
+          <t>['çiçeksi', 'vanilya', 'turunçgil', 'taze', 'tatlı', 'sarı çiçeksi', 'gül', 'taze baharatlı', 'odunsu', 'aromatik']</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Good Girl Blush by Carolina Herrera, kadınlar için Chypre Floral bir koku. Bu yeni bir koku. Good Girl Blush, 2023 yılında piyasaya sürüldü. Quentin Bisch, Shyamala Maisondieu ve Christophe Raynaud tarafından yaratıldı. Üst notalarda Bergamot ve Acı Badem; orta notalarda Şakayık ve Ylang-Ylang; alt notalarda Vanilya ve Kumarin bulunur.</t>
         </is>
       </c>
     </row>
@@ -9025,20 +6679,12 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Gucci Rush 2 Guccifor women</t>
-        </is>
-      </c>
-      <c r="D288" t="n">
-        <v>90</v>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>['yeşil', 'beyaz çiçeksi', 'çiçeksi', 'meyveli', 'taze', 'misk', 'hafif baharatlı', 'sarı çiçeksi', 'yosunlu', 'gül']</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>Gucci Rush 2 by Gucci, kadınlar için çiçeksi odunsu misk notalı bir parfümdür. Gucci Rush 2, 2001 yılında piyasaya sürülmüştür. Bu parfümün arkasındaki isim Michel Almairac'tır. Üst notalarda Frezya, Vadi Zambağı ve Gül; orta notalarda Palmiye Ağacı, Nergis, Zambak ve Gardenya; alt notalarda Siyah Frenk Üzümü, Misk ve Meşe Yosunu bulunur.</t>
+          <t>['beyaz çiçeksi', 'paçuli', 'aromatik', 'odunsu', 'meyveli', 'çiçeksi', 'topraksı', 'vanilya', 'hafif baharatlı', 'tatlı']</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Gucci RushbyGucci, kadınlar için Chypre Fruity kokusudur. Gucci Rushby 1999 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Michel Almairac'tır. Üst notalarda Şeftali, Kaliforniya Gardenyası ve Afrika Frezya Yaprakları; orta notalarda Kişniş, Şam Gülü ve Yasemin; alt notalarda Paçuli, Doğal Vanilya ve Vetiver bulunur.</t>
         </is>
       </c>
     </row>
@@ -9055,20 +6701,12 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Queen of the Night Al-Rehabfor women</t>
-        </is>
-      </c>
-      <c r="D289" t="n">
-        <v>86</v>
-      </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>['odunsu', 'beyaz çiçeksi', 'vanilya', 'turunçgil', 'lavanta', 'sıcak baharatlı', 'pudramsı', 'aromatik', 'taze baharatlı', 'çikolata']</t>
-        </is>
-      </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>Al-Rehabi'nin Queen of the Night'ı kadınlar için Amber Floral bir koku. Bu yeni bir koku. Queen of the Night, 2024 yılında piyasaya sürüldü. Üst notalarda Bergamot ve Lavanta; orta notalarda Beyaz Çiçekler ve Çikolata; alt notalarda Sandal Ağacı ve Vanilya bulunmaktadır.</t>
+          <t>['sıcak baharatlı', 'kehribar', 'tatlı', 'odunsu', 'karamel', 'aromatik']</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Azzaro'nun The Most Wanted'ı erkekler için Amber Spicy bir kokudur. The Most Wanted 2021 yılında piyasaya sürülmüştür. Üst nota Kakule; orta nota Toffee; alt nota Amberwood'dur.</t>
         </is>
       </c>
     </row>
@@ -9085,20 +6723,12 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Naseej Al Kiswah Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D290" t="n">
-        <v>86</v>
-      </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>['odunsu', 'kehribar', 'deri', 'ud', 'paçuli', 'hayvansal', 'vanilya', 'sıcak baharatlı']</t>
-        </is>
-      </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>Naseej Al KiswahbyAfnani, Kadınlar ve Erkekler için Amber Woody Kokusudur. orta notalarda Woodsy Notes ve Sedir; temel notalar Amber, Deri ve Agarwood'dur (Ud).</t>
+          <t>['vanilya', 'meyvemsi', 'gül', 'tatlı', 'odunsu', 'aromatik', 'yeşil', 'pudramsı', 'balzamik', 'çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Paco Rabanne'ın 1 Million Elixir'i erkekler için odunsu aromatik bir kokudur. Bu yeni bir kokudur. 1 Million Elixir 2022'de piyasaya sürüldü. Üst notalarda Elma ve Davana; orta notalarda Şam Gülü, Sedir ve Osmanthus; alt notalarda Vanilya Absolute, Tonka Fasulyesi ve Paçuli bulunur.</t>
         </is>
       </c>
     </row>
@@ -9115,20 +6745,12 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Valentino Uomo Intense Valentinofor men</t>
-        </is>
-      </c>
-      <c r="D291" t="n">
-        <v>87</v>
-      </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>['vanilya', 'iris', 'pudramsı', 'deri', 'menekşe', 'tatlı', 'topraksı', 'aromatik', 'hayvansal', 'kehribar']</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>Valentino Uomo Intense, erkekler için bir deri kokusudur. Valentino Uomo Intense, 2016 yılında piyasaya sürülmüştür. Üst notalarda mandalina ve misk adaçayı; orta notalarda süsen ve tonka fasulyesi; alt notalarda vanilya ve deri bulunmaktadır.</t>
+          <t>['vanilya', 'lavanta', 'aromatik', 'odunsu', 'pudramsı', 'taze baharatlı', 'topraksı', 'tatlı']</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Valentino Uomo Born In Roma Intense, erkekler için Amber Vanilya aromalı bir parfümdür. Bu yeni bir parfümdür. Valentino Uomo Born In Roma Intense, 2023 yılında piyasaya sürüldü. Valentino Uomo Born In Roma Intense, Antoine Maisondieu ve Guillaume Flavigny tarafından yaratıldı. Üst notalarda Vanilya; orta notalarda Lavanta; alt notalarda Vetiver bulunur.</t>
         </is>
       </c>
     </row>
@@ -9145,20 +6767,12 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Energy Fusion for Men Avonfor men</t>
-        </is>
-      </c>
-      <c r="D292" t="n">
-        <v>86</v>
-      </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>['sıcak baharatlı', 'odunsu', 'kehribar', 'aromatik', 'dumanlı', 'topraksı', 'balzamik', 'taze']</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>Avoni'nin Energy Fusion for Men adlı parfümü erkekler için odunsu aromatik bir kokudur. Energy Fusion for Men 2016 yılında piyasaya sürülmüştür.</t>
+          <t>['turunçgil', 'misk', 'hafif baharatlı', 'kehribar', 'odunsu', 'meyvemsi', 'paçuli', 'topraksı', 'taze baharatlı']</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Versace'den Eros Energy, erkekler için narenciye aromalı bir kokudur. Bu yeni bir kokudur. Eros Energy, 2024 yılında piyasaya sürülmüştür. Üst notalarda Kan Portakalı, Limon, Greyfurt, Limon, Mandalina ve Sicilya Bergamotu; orta notalarda Pembe Biber, Beyaz Amber ve Siyah Frenk Üzümü; alt notalarda Misk, Paçuli ve Meşe Yosunu bulunur.</t>
         </is>
       </c>
     </row>
@@ -9175,20 +6789,12 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>9am Afnanfor women</t>
-        </is>
-      </c>
-      <c r="D293" t="n">
-        <v>86</v>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'misk', 'odunsu', 'aromatik', 'sıcak baharatlı', 'lavanta', 'yosunlu', 'meyveli', 'topraksı', 'beyaz çiçeksi']</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>9ambyAfnani kadınlara özel bir parfüm. Üst notalarda Limon, Mandalina, Kakule ve Pembe Biber; orta notalarda Lavanta, Yeşil Elma, Portakal Çiçeği ve Gül; alt notalarda Misk, Yosun, Sedir ve Paçuli bulunuyor.</t>
+          <t>['beyaz çiçeksi', 'misk', 'kehribar', 'gül', 'pudramsı', 'tatlı', 'meyvemsi', 'tropikal', 'turunçgil', 'hayvansal']</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Chinese New Year Beautiful Belle Red Eau de Parfum by Estée Laude, kadınlar için Amber Floral bir kokudur.Chinese New Year Beautiful Belle Red Eau de Parfum, 2019 yılında piyasaya sürülmüştür. Üst notalarda Litchi, Gül ve Mimoza; orta notalarda Portakal Çiçeği, Gardenya ve Sümbülteber; alt notalarda Ambroxan, Süsen, Süet, Badem Ezmesi ve Misk bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -9205,20 +6811,12 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>9am Dive Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D294" t="n">
-        <v>86</v>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'odunsu', 'yeşil', 'sıcak baharatlı', 'aromatik', 'turunçgil', 'taze', 'taze baharatlı', 'hafif baharatlı', 'kehribar']</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>9am DivebyAfna, kadınlar ve erkekler için Aromatik Su Kokusu'dur. Bu yeni bir kokudur. 9am Dive, 2022 yılında piyasaya sürüldü. Üst notalarda Limon, Nane, Siyah Frenk Üzümü ve Pembe Biber; orta notalarda Elma, Tütsü ve Sedir; alt notalarda Zencefil, Sandal Ağacı, Paçuli ve Yasemin bulunur.</t>
+          <t>['vanilya', 'sıcak baharatlı', 'kehribar', 'tarçın', 'balzamik', 'aromatik', 'çiçeksi', 'pudramsı', 'tatlı', 'odunsu']</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Divine Vanille by Essential Parfum, kadınlar ve erkekler için Amber Vanilya kokusudur. Divine Vanille, 2019 yılında piyasaya sürüldü. Bu kokunun arkasındaki burun Olivier Pescheux'dür. Üst notalarda Tarçın, Karabiber ve Misk; orta notalarda Tütsü, Osmanthus ve Nar; alt notalarda Madagaskar Vanilyası, Tonka Fasulyesi, Siam Benzoini, Paçuli, Teksas Sediri ve Misk bulunur.</t>
         </is>
       </c>
     </row>
@@ -9235,20 +6833,12 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>9am Afnanfor women</t>
-        </is>
-      </c>
-      <c r="D295" t="n">
-        <v>86</v>
-      </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'misk', 'odunsu', 'aromatik', 'sıcak baharatlı', 'lavanta', 'yosunlu', 'meyveli', 'topraksı', 'beyaz çiçeksi']</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>9ambyAfnani kadınlara özel bir parfüm. Üst notalarda Limon, Mandalina, Kakule ve Pembe Biber; orta notalarda Lavanta, Yeşil Elma, Portakal Çiçeği ve Gül; alt notalarda Misk, Yosun, Sedir ve Paçuli bulunuyor.</t>
+          <t>['beyaz çiçeksi', 'odunsu', 'pudramsı', 'turunçgil', 'taze baharatlı', 'çiçeksi', 'süsen', 'gül', 'sarı çiçeksi', 'misk']</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Chanel No 46 by Chanel, kadınlar için çiçeksi odunsu misk kokusudur. Chanel No 46, 1946 yılında piyasaya sürülmüştür. Üst notalarda Bergamot, Portakal Çiçeği ve Portakal; orta notalarda Ylang-Ylang, Gül, Yasemin ve Vadi Zambağı; alt notalarda Süsen Kökü, Misk, Sandal Ağacı, Vanilya, Kimyon ve Vetiver bulunur.</t>
         </is>
       </c>
     </row>
@@ -9265,20 +6855,12 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Tease Victoria's Secretfor women</t>
-        </is>
-      </c>
-      <c r="D296" t="n">
-        <v>87</v>
-      </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'vanilya', 'tatlı', 'çiçeksi', 'beyaz çiçeksi', 'kehribar', 'pudramsı', 'sıcak baharatlı', 'taze', 'turunçgil']</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>TeasebyVictoria's Secret, kadınlar için çiçeksi ve meyveli bir kokudur. Tease, 2017 yılında piyasaya sürülmüştür. Üst notalarda Armut, Litchi, Kırmızı Elma ve Mandalina; orta notalarda Gardenya, Manolya, Yasemin, Frezya ve Tatlı Bezelye; alt notalarda Siyah Vanilya Kabuğu, Benzoin, Çikolata, Amber, Sandal Ağacı ve Misk bulunmaktadır.</t>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>One SecretbyAl-Rehabi erkeklere özel bir parfüm.</t>
         </is>
       </c>
     </row>
@@ -9295,20 +6877,12 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>L'Aventure Intense Al Haramain Perfumesfor men</t>
-        </is>
-      </c>
-      <c r="D297" t="n">
-        <v>86</v>
-      </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'odunsu', 'aromatik', 'taze baharatlı', 'misk']</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>Al Haramain Perfumesi tarafından üretilen L'Aventure Intense, erkekler için Chypre Floral bir kokudur. L'Aventure Intense, 2019 yılında piyasaya sürülmüştür. Üst notalarda Bergamot, Limon ve Elemi; orta notalarda Odunsu Notalar, Yasemin ve Vadi Zambağı; alt notalarda Misk, Amber ve Paçuli bulunmaktadır.</t>
+          <t>['taze baharatlı', 'gül', 'sıcak baharatlı', 'paçuli', 'odunsu', 'kehribar', 'çiçeksi', 'topraksı', 'aromatik']</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Club De Nuit Intense Kadın Parfüm YağıArmafis kadınlara özel bir parfüm. Bu yeni bir parfüm. Club De Nuit Intense Kadın Parfüm Yağı 2022 yılında piyasaya sürüldü. Üst notalarda Gül, Safran ve Sardunya; orta notalarda Hindistan Cevizi, Kimyon, Biber ve Menekşe; alt notalarda Paçuli, Amber, Ud ve Vanilya bulunmaktadır.</t>
         </is>
       </c>
     </row>
@@ -9325,22 +6899,10 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>9am Dive Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D298" t="n">
-        <v>86</v>
-      </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'odunsu', 'yeşil', 'sıcak baharatlı', 'aromatik', 'turunçgil', 'taze', 'taze baharatlı', 'hafif baharatlı', 'kehribar']</t>
-        </is>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>9am DivebyAfna, kadınlar ve erkekler için Aromatik Su Kokusu'dur. Bu yeni bir kokudur. 9am Dive, 2022 yılında piyasaya sürüldü. Üst notalarda Limon, Nane, Siyah Frenk Üzümü ve Pembe Biber; orta notalarda Elma, Tütsü ve Sedir; alt notalarda Zencefil, Sandal Ağacı, Paçuli ve Yasemin bulunur.</t>
-        </is>
-      </c>
+          <t>['odunsu', 'sıcak baharatlı', 'tatlı', 'çiçeksi', 'kehribar', 'topraksı', 'paçuli', 'aromatik', 'vanilya', 'pudramsı']</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -9355,20 +6917,12 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>9am Dive Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D299" t="n">
-        <v>86</v>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'odunsu', 'yeşil', 'sıcak baharatlı', 'aromatik', 'turunçgil', 'taze', 'taze baharatlı', 'hafif baharatlı', 'kehribar']</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>9am DivebyAfna, kadınlar ve erkekler için Aromatik Su Kokusu'dur. Bu yeni bir kokudur. 9am Dive, 2022 yılında piyasaya sürüldü. Üst notalarda Limon, Nane, Siyah Frenk Üzümü ve Pembe Biber; orta notalarda Elma, Tütsü ve Sedir; alt notalarda Zencefil, Sandal Ağacı, Paçuli ve Yasemin bulunur.</t>
+          <t>['sıcak baharatlı', 'turunçgil', 'deri', 'tütün', 'aromatik', 'tarçın', 'taze baharatlı', 'odunsu', 'tatlı', 'topraksı']</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Bomba Di SpeziebyFragrenza, kadın ve erkeklere yönelik bir parfümdür. Üst notalarda Bergamot, Greyfurt ve Pembe Biber; orta notalarda Acı Biber, Safran ve Tarçın; alt notalarda Deri, Tütün ve Vetiver bulunur.</t>
         </is>
       </c>
     </row>
@@ -9385,20 +6939,12 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Hero Burberryfor men</t>
-        </is>
-      </c>
-      <c r="D300" t="n">
-        <v>86</v>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>['odunsu', 'taze baharatlı', 'aromatik', 'turunçgil']</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>HerobyBurberry, erkekler için odunsu ve baharatlı bir kokudur. Heroby, 2021 yılında piyasaya sürülmüştür. Bu kokunun arkasındaki isim Aurélien Guichard'dır. Üst notalarda Bergamot; orta notalarda Ardıç ve Karabiber; alt notalarda Atlas Sediri, Virginia Sediri ve Himalaya Sediri bulunur.</t>
+          <t>['pudramsı', 'odunsu', 'menekşe', 'meyvemsi', 'taze', 'tatlı', 'su', 'sıcak baharatlı', 'çiçeksi']</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>1 Pulse for HerbyAvon, kadınlara yönelik çiçeksi ve meyveli bir kokudur. 1 Pulse for Her, 2017 yılında piyasaya sürülmüştür.</t>
         </is>
       </c>
     </row>
@@ -9415,18 +6961,10 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Valentino Donna Born In Roma Valentinofor women</t>
-        </is>
-      </c>
-      <c r="D301" t="n">
-        <v>95</v>
-      </c>
-      <c r="E301" t="inlineStr">
-        <is>
           <t>['odunsu', 'vanilya', 'meyvemsi', 'hafif baharatlı', 'beyaz çiçeksi', 'pudramsı', 'çiçeksi', 'misk', 'yeşil', 'taze']</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr">
+      <c r="D301" t="inlineStr">
         <is>
           <t>Valentino Donna Born In Roma Valentino, kadınlar için Amber Floral bir kokudur. Valentino Donna Born In Roma, 2019 yılında piyasaya sürülmüştür. Üst notalarda Siyah Frenk Üzümü, Pembe Biber ve Bergamot; orta notalarda Yasemin, Yasemin Sambac ve Yasemin Çayı; alt notalarda Burbon Vanilya, Kaşmiran ve Guaiac Ağacı bulunmaktadır.</t>
         </is>
@@ -9445,20 +6983,12 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>9am Afnanfor women</t>
-        </is>
-      </c>
-      <c r="D302" t="n">
-        <v>86</v>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'misk', 'odunsu', 'aromatik', 'sıcak baharatlı', 'lavanta', 'yosunlu', 'meyveli', 'topraksı', 'beyaz çiçeksi']</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>9ambyAfnani kadınlara özel bir parfüm. Üst notalarda Limon, Mandalina, Kakule ve Pembe Biber; orta notalarda Lavanta, Yeşil Elma, Portakal Çiçeği ve Gül; alt notalarda Misk, Yosun, Sedir ve Paçuli bulunuyor.</t>
+          <t>['misk', 'odunsu', 'pudramsı', 'sarı çiçeksi', 'turunçgil', 'tatlı', 'aromatik']</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Skin CouturebyArmafis, kadınlar için çiçeksi ve meyveli bir koku. Üst notalarda Bergamot, Frenk üzümü, Limon ve Ahududu; orta notalarda Ylang-Ylang, Menekşe Yaprağı ve Vadi Zambağı; alt notalarda Misk ve Beyaz Ağaçlar bulunur.</t>
         </is>
       </c>
     </row>
@@ -9475,20 +7005,12 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>9am Dive Afnanfor women and men</t>
-        </is>
-      </c>
-      <c r="D303" t="n">
-        <v>86</v>
-      </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>['meyvemsi', 'odunsu', 'yeşil', 'sıcak baharatlı', 'aromatik', 'turunçgil', 'taze', 'taze baharatlı', 'hafif baharatlı', 'kehribar']</t>
-        </is>
-      </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>9am DivebyAfna, kadınlar ve erkekler için Aromatik Su Kokusu'dur. Bu yeni bir kokudur. 9am Dive, 2022 yılında piyasaya sürüldü. Üst notalarda Limon, Nane, Siyah Frenk Üzümü ve Pembe Biber; orta notalarda Elma, Tütsü ve Sedir; alt notalarda Zencefil, Sandal Ağacı, Paçuli ve Yasemin bulunur.</t>
+          <t>['odunsu', 'deri', 'meyvemsi', 'su', 'taze', 'dumanlı', 'beyaz çiçeksi', 'tatlı', 'çiçeksi', 'misk']</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Chloe Collection 2005byChloé, kadınlar için odunsu çiçeksi misk notaları içeren bir parfümdür. Chloe Collection 2005, 2005 yılında piyasaya sürülmüştür. Chloe Collection 2005, Clement Gavarry ve Carlos Benaim tarafından yaratılmıştır. Üst notalarda armut ve nilüfer; orta notalarda gardenya, çarkıfelek meyvesi ve sümbülteber; alt notalarda huş ağacı, misk ve odunsu notalar bulunur.</t>
         </is>
       </c>
     </row>
@@ -9505,18 +7027,10 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Azzaro Pour Elle Azzarofor women</t>
-        </is>
-      </c>
-      <c r="D304" t="n">
-        <v>95</v>
-      </c>
-      <c r="E304" t="inlineStr">
-        <is>
           <t>['odunsu', 'sıcak baharatlı', 'turunçgil', 'kehribar', 'aromatik', 'balzamik', 'Şampanya', 'taze baharatlı', 'misk', 'beyaz çiçeksi']</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr">
+      <c r="D304" t="inlineStr">
         <is>
           <t>Azzaro Pour Elle, kadınlar için Amber Floral bir kokudur. Azzaro Pour Elle, 2015 yılında piyasaya sürüldü. Azzaro Pour Elle, Fabrice Pellegrin ve Nathalie Lorson tarafından yaratıldı. Üst notalarda Kakule, Şampanya, Portakal ve Mandalina; orta notalarda Gül, Zambak ve Şeftali; alt notalarda Kaşmir Ağacı, Olibanum, Sandal Ağacı ve Vanilya bulunur.</t>
         </is>
@@ -9535,20 +7049,12 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>9am Afnanfor women</t>
-        </is>
-      </c>
-      <c r="D305" t="n">
-        <v>86</v>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>['turunçgil', 'misk', 'odunsu', 'aromatik', 'sıcak baharatlı', 'lavanta', 'yosunlu', 'meyveli', 'topraksı', 'beyaz çiçeksi']</t>
-        </is>
-      </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>9ambyAfnani kadınlara özel bir parfüm. Üst notalarda Limon, Mandalina, Kakule ve Pembe Biber; orta notalarda Lavanta, Yeşil Elma, Portakal Çiçeği ve Gül; alt notalarda Misk, Yosun, Sedir ve Paçuli bulunuyor.</t>
+          <t>['beyaz çiçeksi', 'turunçgil', 'tatlı', 'kehribar', 'vanilya', 'pudramsı', 'meyvemsi', 'misk', 'taze', 'hayvansal']</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Prada Paradoxe, kadınlar için Amber Floral bir koku. Bu yeni bir parfüm. Prada Paradoxe, 2022 yılında piyasaya sürüldü. Prada Paradoxe, Nadège Le Garlantezec, Antoine Maisondieu ve Shyamala Maisondieu tarafından yaratıldı. Üst notalarda Armut, Mandalina ve Bergamot; orta notalarda Portakal Çiçeği, Portakal Çiçeği Özü, Portakal Çiçeği ve Yasemin; alt notalarda Burbon Vanilya, Amber, Beyaz Misk ve Benzoin yer alıyor.</t>
         </is>
       </c>
     </row>
@@ -9565,20 +7071,12 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Urbanist Homme Al Haramain Perfumesfor men</t>
-        </is>
-      </c>
-      <c r="D306" t="n">
-        <v>86</v>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>['aromatik', 'turunçgil', 'odunsu', 'taze baharatlı', 'kehribar', 'pudramsı', 'misk', 'beyaz çiçeksi', 'lavanta', 'tatlı']</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>Urbanist Hommeby Al Haramain Perfumesis, erkekler için Amber ve Baharatlı bir koku. Bu kokunun arkasındaki isim Christian Carbonnel. Üst notalarda Petitgrain, Portakal ve Limon; orta notalarda Lavanta, Biberiye ve Yasemin; alt notalarda Amber, Misk, Sandal Ağacı ve Tonka Fasulyesi bulunuyor.</t>
+          <t>['turunçgil', 'misk', 'aromatik', 'kehribar', 'odunsu', 'sıcak baharatlı', 'pudramsı', 'taze baharatlı']</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Caballo Pour HommebyArmafi erkeklere yönelik bir parfümdür. Bu yeni bir parfümdür. Caballo Pour Homme 2022 yılında piyasaya sürüldü. Üst notalarda Greyfurt, Limon ve Bergamot; orta notalarda Zencefil, Menekşe ve Ambrette (Ebegümeci Miski); alt notalarda Ambroxan, Misk, Vetiver ve Paçuli bulunur.</t>
         </is>
       </c>
     </row>
@@ -9595,20 +7093,12 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>9pm Afnanfor men</t>
-        </is>
-      </c>
-      <c r="D307" t="n">
-        <v>86</v>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>['vanilya', 'kehribar', 'sıcak baharatlı', 'tarçın', 'tatlı', 'meyvemsi', 'pudramsı', 'lavanta', 'aromatik', 'taze']</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>9pmbyAfnani erkekler için Amber Vanilya kokusu. 9pm, 2020 yılında piyasaya sürüldü. Üst notalarda Elma, Tarçın, Yabani Lavanta ve Bergamot; orta notalarda Portakal Çiçeği ve Vadi Zambağı; alt notalarda Vanilya, Tonka Fasulyesi, Amber ve Paçuli bulunuyor.</t>
+          <t>['odunsu', 'meyvemsi', 'vanilya', 'sıcak baharatlı', 'tarçın', 'aromatik', 'pudramsı', 'turunçgil', 'taze', 'yeşil']</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Boss Bottled by Hugo Boss, erkekler için odunsu ve baharatlı bir kokudur. Boss Bottled, 1998 yılında piyasaya sürülmüştür. Boss Bottled, Annick Menardo ve Christian Dussoulier tarafından yaratılmıştır. Üst notalarda Elma, Erik, Limon, Bergamot, Meşe Yosunu ve Sardunya; orta notalarda Tarçın, Maun ve Karanfil; alt notalarda Vanilya, Sandal Ağacı, Sedir, Vetiver ve Zeytin Ağacı bulunur.</t>
         </is>
       </c>
     </row>
